--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -64,37 +64,37 @@
     <t xml:space="preserve">StartHour</t>
   </si>
   <si>
+    <t xml:space="preserve">MISSION00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-Agent Test (Multi-Camera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENVIRONMENT00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GROUP02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-150.0, 150.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(30.0, 150.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PX4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(13/12/2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(16:30:00)</t>
+  </si>
+  <si>
     <t xml:space="preserve">X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISSION00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single-Agent Test (Multi-Camera)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENVIRONMENT00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GROUP02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(-150.0, 150.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(30.0, 150.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PX4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(13/12/2024)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(16:30:00)</t>
   </si>
   <si>
     <t xml:space="preserve">MISSION01</t>
@@ -869,10 +869,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="h:mm:ss"/>
     <numFmt numFmtId="166" formatCode="0"/>
+    <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -944,8 +945,9 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1041,7 +1043,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1094,6 +1096,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1118,10 +1124,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1131,6 +1133,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1614,13 +1620,13 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="21" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="21" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="54.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="2" width="26.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="29.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="29.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="30.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="2" width="20.92"/>
@@ -1679,38 +1685,36 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="J3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
@@ -1759,7 +1763,9 @@
       <c r="BD3" s="12"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
+      <c r="A4" s="13" t="s">
+        <v>21</v>
+      </c>
       <c r="B4" s="9" t="s">
         <v>22</v>
       </c>
@@ -1767,28 +1773,28 @@
         <v>23</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>15</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="J4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="K4" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
@@ -1845,28 +1851,28 @@
         <v>26</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>14</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>15</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>27</v>
       </c>
       <c r="G5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="I5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="J5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="K5" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L5" s="12"/>
       <c r="M5" s="12"/>
@@ -1923,28 +1929,28 @@
         <v>29</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>14</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>15</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="I6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="J6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="K6" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
@@ -2028,7 +2034,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD16"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="2" width="29.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="40.25"/>
@@ -2100,21 +2106,21 @@
       <c r="B3" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="C3" s="22" t="b">
+      <c r="C3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D3" s="22" t="s">
         <v>275</v>
       </c>
-      <c r="E3" s="22" t="b">
+      <c r="E3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>276</v>
       </c>
-      <c r="G3" s="22" t="b">
+      <c r="G3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -2167,7 +2173,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="33.54"/>
@@ -2180,12 +2186,12 @@
   </cols>
   <sheetData>
     <row r="1" s="7" customFormat="true" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
       <c r="E1" s="12"/>
       <c r="XFB1" s="3"/>
       <c r="XFC1" s="3"/>
@@ -2207,7 +2213,7 @@
     </row>
     <row r="3" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>33</v>
@@ -2215,7 +2221,7 @@
       <c r="C3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="15" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2229,7 +2235,7 @@
       <c r="C4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="15" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2258,7 +2264,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:BM1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="38.38"/>
@@ -2269,15 +2275,15 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
@@ -2373,7 +2379,7 @@
       <c r="D3" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="15" t="n">
+      <c r="E3" s="16" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="9" t="s">
@@ -2454,7 +2460,7 @@
       <c r="D4" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="16" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="9" t="s">
@@ -2530,12 +2536,12 @@
         <v>54</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="16" t="n">
         <v>8</v>
       </c>
       <c r="F5" s="9" t="s">
@@ -2616,7 +2622,7 @@
       <c r="D6" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="16" t="n">
         <v>16</v>
       </c>
       <c r="F6" s="9" t="s">
@@ -2710,7 +2716,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="38.28"/>
@@ -2720,7 +2726,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="29.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="36.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="2" width="26.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="29.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="29.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="26.66"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="12" style="12" width="11"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16379" min="17" style="2" width="11"/>
@@ -2729,50 +2735,50 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
       <c r="XFC1" s="3"/>
       <c r="XFD1" s="3"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="18" t="s">
         <v>67</v>
       </c>
       <c r="L2" s="12"/>
@@ -2787,260 +2793,260 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="18" t="s">
+      <c r="C3" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H3" s="18" t="n">
+      <c r="H3" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I3" s="18" t="n">
+      <c r="I3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J3" s="19" t="n">
         <v>12000</v>
       </c>
       <c r="XFC3" s="3"/>
       <c r="XFD3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="H4" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="I4" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J4" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="H5" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J5" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H6" s="18" t="n">
+      <c r="H6" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="J6" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="18" t="n">
+      <c r="H7" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J7" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H8" s="18" t="n">
+      <c r="H8" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J8" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H9" s="18" t="n">
+      <c r="H9" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J9" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="18" t="n">
+      <c r="H10" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="J10" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -3077,7 +3083,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD23"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="38.28"/>
@@ -3093,32 +3099,32 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>94</v>
       </c>
       <c r="H2" s="12"/>
@@ -3134,22 +3140,22 @@
       <c r="XFD2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G3" s="2"/>
@@ -3159,22 +3165,22 @@
       <c r="XEY3" s="3"/>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G4" s="2"/>
@@ -3184,22 +3190,22 @@
       <c r="XEY4" s="3"/>
     </row>
     <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G5" s="2"/>
@@ -3209,22 +3215,22 @@
       <c r="XEY5" s="3"/>
     </row>
     <row r="6" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G6" s="2"/>
@@ -3234,22 +3240,22 @@
       <c r="XEY6" s="3"/>
     </row>
     <row r="7" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G7" s="2"/>
@@ -3259,22 +3265,22 @@
       <c r="XEY7" s="3"/>
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G8" s="2"/>
@@ -3284,22 +3290,22 @@
       <c r="XEY8" s="3"/>
     </row>
     <row r="9" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G9" s="2"/>
@@ -3309,22 +3315,22 @@
       <c r="XEY9" s="3"/>
     </row>
     <row r="10" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G10" s="2"/>
@@ -3369,7 +3375,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="45.28"/>
@@ -3383,53 +3389,53 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
       <c r="L1" s="2"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="18" t="s">
         <v>116</v>
       </c>
       <c r="M2" s="12"/>
@@ -3437,878 +3443,868 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="I3" s="18" t="n">
+      <c r="I3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K3" s="18" t="n">
+      <c r="K3" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="I4" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J4" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K4" s="18" t="n">
+      <c r="K4" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J5" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K5" s="18" t="n">
+      <c r="K5" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="J6" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K6" s="18" t="n">
+      <c r="K6" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J7" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K7" s="18" t="n">
+      <c r="K7" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L7" s="2"/>
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="H8" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J8" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="18" t="n">
+      <c r="K8" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L8" s="2"/>
       <c r="XFD8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J9" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="18" t="n">
+      <c r="K9" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="J10" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K10" s="18" t="n">
+      <c r="K10" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="H11" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J11" s="18" t="n">
+      <c r="J11" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K11" s="18" t="n">
+      <c r="K11" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="H12" s="18" t="s">
+      <c r="H12" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J12" s="18" t="n">
+      <c r="J12" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K12" s="18" t="n">
+      <c r="K12" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="H13" s="18" t="s">
+      <c r="H13" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J13" s="18" t="n">
+      <c r="J13" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K13" s="18" t="n">
+      <c r="K13" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="H14" s="18" t="s">
+      <c r="H14" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="I14" s="18" t="n">
+      <c r="I14" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J14" s="18" t="n">
+      <c r="J14" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K14" s="18" t="n">
+      <c r="K14" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L14" s="2"/>
-      <c r="XFD14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="G15" s="18" t="s">
+      <c r="G15" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="H15" s="18" t="s">
+      <c r="H15" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="I15" s="18" t="n">
+      <c r="I15" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J15" s="18" t="n">
+      <c r="J15" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K15" s="18" t="n">
+      <c r="K15" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L15" s="2"/>
-      <c r="XFD15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F16" s="18" t="s">
+      <c r="F16" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="H16" s="18" t="s">
+      <c r="H16" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="I16" s="18" t="n">
+      <c r="I16" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J16" s="18" t="n">
+      <c r="J16" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K16" s="18" t="n">
+      <c r="K16" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L16" s="2"/>
-      <c r="XFD16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="F17" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="G17" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="H17" s="18" t="s">
+      <c r="H17" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="I17" s="18" t="n">
+      <c r="I17" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J17" s="18" t="n">
+      <c r="J17" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K17" s="18" t="n">
+      <c r="K17" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L17" s="2"/>
-      <c r="XFD17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="H18" s="18" t="s">
+      <c r="H18" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="I18" s="18" t="n">
+      <c r="I18" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J18" s="18" t="n">
+      <c r="J18" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K18" s="18" t="n">
+      <c r="K18" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L18" s="2"/>
-      <c r="XFD18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="19" t="s">
         <v>165</v>
       </c>
       <c r="C19" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="F19" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="G19" s="18" t="s">
+      <c r="G19" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="H19" s="18" t="s">
+      <c r="H19" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="I19" s="18" t="n">
+      <c r="I19" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J19" s="18" t="n">
+      <c r="J19" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K19" s="18" t="n">
+      <c r="K19" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L19" s="2"/>
-      <c r="XFD19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="19" t="s">
         <v>167</v>
       </c>
       <c r="C20" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F20" s="18" t="s">
+      <c r="F20" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="G20" s="18" t="s">
+      <c r="G20" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="H20" s="18" t="s">
+      <c r="H20" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="I20" s="18" t="n">
+      <c r="I20" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J20" s="18" t="n">
+      <c r="J20" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K20" s="18" t="n">
+      <c r="K20" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L20" s="2"/>
-      <c r="XFD20" s="0"/>
     </row>
     <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="19" t="s">
         <v>169</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="G21" s="18" t="s">
+      <c r="G21" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="H21" s="18" t="s">
+      <c r="H21" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="I21" s="18" t="n">
+      <c r="I21" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J21" s="18" t="n">
+      <c r="J21" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K21" s="18" t="n">
+      <c r="K21" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L21" s="2"/>
-      <c r="XFD21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="19" t="s">
         <v>171</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="F22" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="H22" s="18" t="s">
+      <c r="H22" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="I22" s="18" t="n">
+      <c r="I22" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J22" s="18" t="n">
+      <c r="J22" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K22" s="18" t="n">
+      <c r="K22" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L22" s="2"/>
-      <c r="XFD22" s="0"/>
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="19" t="s">
         <v>173</v>
       </c>
       <c r="C23" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F23" s="18" t="s">
+      <c r="F23" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="H23" s="18" t="s">
+      <c r="H23" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="I23" s="18" t="n">
+      <c r="I23" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J23" s="18" t="n">
+      <c r="J23" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K23" s="18" t="n">
+      <c r="K23" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L23" s="2"/>
-      <c r="XFD23" s="0"/>
     </row>
     <row r="24" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="F24" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="G24" s="18" t="s">
+      <c r="G24" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="H24" s="18" t="s">
+      <c r="H24" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="I24" s="18" t="n">
+      <c r="I24" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J24" s="18" t="n">
+      <c r="J24" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K24" s="18" t="n">
+      <c r="K24" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L24" s="2"/>
       <c r="XFD24" s="3"/>
     </row>
     <row r="25" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F25" s="18" t="s">
+      <c r="F25" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="G25" s="18" t="s">
+      <c r="G25" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="H25" s="18" t="s">
+      <c r="H25" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="I25" s="18" t="n">
+      <c r="I25" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J25" s="18" t="n">
+      <c r="J25" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K25" s="18" t="n">
+      <c r="K25" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L25" s="2"/>
       <c r="XFD25" s="3"/>
     </row>
     <row r="26" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F26" s="18" t="s">
+      <c r="F26" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="G26" s="18" t="s">
+      <c r="G26" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="H26" s="18" t="s">
+      <c r="H26" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="I26" s="18" t="n">
+      <c r="I26" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J26" s="18" t="n">
+      <c r="J26" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K26" s="18" t="n">
+      <c r="K26" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L26" s="2"/>
@@ -4347,7 +4343,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="45.28"/>
@@ -4360,36 +4356,36 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>183</v>
       </c>
       <c r="XEV2" s="3"/>
@@ -4403,7 +4399,7 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>184</v>
       </c>
       <c r="B3" s="19" t="s">
@@ -4412,21 +4408,21 @@
       <c r="C3" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="18" t="n">
+      <c r="G3" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>187</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -4435,30 +4431,21 @@
       <c r="C4" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="G4" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV4" s="0"/>
-      <c r="XEW4" s="0"/>
-      <c r="XEX4" s="0"/>
-      <c r="XEY4" s="0"/>
-      <c r="XEZ4" s="0"/>
-      <c r="XFA4" s="0"/>
-      <c r="XFB4" s="0"/>
-      <c r="XFC4" s="0"/>
-      <c r="XFD4" s="0"/>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>189</v>
       </c>
       <c r="B5" s="19" t="s">
@@ -4467,30 +4454,21 @@
       <c r="C5" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV5" s="0"/>
-      <c r="XEW5" s="0"/>
-      <c r="XEX5" s="0"/>
-      <c r="XEY5" s="0"/>
-      <c r="XEZ5" s="0"/>
-      <c r="XFA5" s="0"/>
-      <c r="XFB5" s="0"/>
-      <c r="XFC5" s="0"/>
-      <c r="XFD5" s="0"/>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>191</v>
       </c>
       <c r="B6" s="19" t="s">
@@ -4499,30 +4477,21 @@
       <c r="C6" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV6" s="0"/>
-      <c r="XEW6" s="0"/>
-      <c r="XEX6" s="0"/>
-      <c r="XEY6" s="0"/>
-      <c r="XEZ6" s="0"/>
-      <c r="XFA6" s="0"/>
-      <c r="XFB6" s="0"/>
-      <c r="XFC6" s="0"/>
-      <c r="XFD6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>193</v>
       </c>
       <c r="B7" s="19" t="s">
@@ -4531,21 +4500,21 @@
       <c r="C7" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>195</v>
       </c>
       <c r="B8" s="19" t="s">
@@ -4554,30 +4523,21 @@
       <c r="C8" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="G8" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV8" s="0"/>
-      <c r="XEW8" s="0"/>
-      <c r="XEX8" s="0"/>
-      <c r="XEY8" s="0"/>
-      <c r="XEZ8" s="0"/>
-      <c r="XFA8" s="0"/>
-      <c r="XFB8" s="0"/>
-      <c r="XFC8" s="0"/>
-      <c r="XFD8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
         <v>197</v>
       </c>
       <c r="B9" s="19" t="s">
@@ -4586,30 +4546,21 @@
       <c r="C9" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="18" t="n">
+      <c r="G9" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV9" s="0"/>
-      <c r="XEW9" s="0"/>
-      <c r="XEX9" s="0"/>
-      <c r="XEY9" s="0"/>
-      <c r="XEZ9" s="0"/>
-      <c r="XFA9" s="0"/>
-      <c r="XFB9" s="0"/>
-      <c r="XFC9" s="0"/>
-      <c r="XFD9" s="0"/>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>199</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -4618,30 +4569,21 @@
       <c r="C10" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="18" t="n">
+      <c r="G10" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV10" s="0"/>
-      <c r="XEW10" s="0"/>
-      <c r="XEX10" s="0"/>
-      <c r="XEY10" s="0"/>
-      <c r="XEZ10" s="0"/>
-      <c r="XFA10" s="0"/>
-      <c r="XFB10" s="0"/>
-      <c r="XFC10" s="0"/>
-      <c r="XFD10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="19" t="s">
         <v>201</v>
       </c>
       <c r="B11" s="19" t="s">
@@ -4650,21 +4592,21 @@
       <c r="C11" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="G11" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="19" t="s">
         <v>203</v>
       </c>
       <c r="B12" s="19" t="s">
@@ -4673,30 +4615,21 @@
       <c r="C12" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV12" s="0"/>
-      <c r="XEW12" s="0"/>
-      <c r="XEX12" s="0"/>
-      <c r="XEY12" s="0"/>
-      <c r="XEZ12" s="0"/>
-      <c r="XFA12" s="0"/>
-      <c r="XFB12" s="0"/>
-      <c r="XFC12" s="0"/>
-      <c r="XFD12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="19" t="s">
         <v>205</v>
       </c>
       <c r="B13" s="19" t="s">
@@ -4705,30 +4638,21 @@
       <c r="C13" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV13" s="0"/>
-      <c r="XEW13" s="0"/>
-      <c r="XEX13" s="0"/>
-      <c r="XEY13" s="0"/>
-      <c r="XEZ13" s="0"/>
-      <c r="XFA13" s="0"/>
-      <c r="XFB13" s="0"/>
-      <c r="XFC13" s="0"/>
-      <c r="XFD13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="19" t="s">
         <v>207</v>
       </c>
       <c r="B14" s="19" t="s">
@@ -4737,30 +4661,21 @@
       <c r="C14" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV14" s="0"/>
-      <c r="XEW14" s="0"/>
-      <c r="XEX14" s="0"/>
-      <c r="XEY14" s="0"/>
-      <c r="XEZ14" s="0"/>
-      <c r="XFA14" s="0"/>
-      <c r="XFB14" s="0"/>
-      <c r="XFC14" s="0"/>
-      <c r="XFD14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="19" t="s">
         <v>209</v>
       </c>
       <c r="B15" s="19" t="s">
@@ -4769,21 +4684,21 @@
       <c r="C15" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="F15" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="19" t="s">
         <v>211</v>
       </c>
       <c r="B16" s="19" t="s">
@@ -4792,30 +4707,21 @@
       <c r="C16" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV16" s="0"/>
-      <c r="XEW16" s="0"/>
-      <c r="XEX16" s="0"/>
-      <c r="XEY16" s="0"/>
-      <c r="XEZ16" s="0"/>
-      <c r="XFA16" s="0"/>
-      <c r="XFB16" s="0"/>
-      <c r="XFC16" s="0"/>
-      <c r="XFD16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="19" t="s">
         <v>213</v>
       </c>
       <c r="B17" s="19" t="s">
@@ -4824,30 +4730,21 @@
       <c r="C17" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F17" s="18" t="n">
+      <c r="F17" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV17" s="0"/>
-      <c r="XEW17" s="0"/>
-      <c r="XEX17" s="0"/>
-      <c r="XEY17" s="0"/>
-      <c r="XEZ17" s="0"/>
-      <c r="XFA17" s="0"/>
-      <c r="XFB17" s="0"/>
-      <c r="XFC17" s="0"/>
-      <c r="XFD17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="19" t="s">
         <v>215</v>
       </c>
       <c r="B18" s="19" t="s">
@@ -4856,27 +4753,18 @@
       <c r="C18" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="18" t="n">
+      <c r="G18" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV18" s="0"/>
-      <c r="XEW18" s="0"/>
-      <c r="XEX18" s="0"/>
-      <c r="XEY18" s="0"/>
-      <c r="XEZ18" s="0"/>
-      <c r="XFA18" s="0"/>
-      <c r="XFB18" s="0"/>
-      <c r="XFC18" s="0"/>
-      <c r="XFD18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -4909,12 +4797,12 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:R1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="2" width="26.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="34.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="34.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="35.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="28.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="28.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="64.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="29.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="12" width="51.08"/>
@@ -5020,28 +4908,28 @@
       <c r="E3" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="22" t="b">
+      <c r="F3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="G3" s="22" t="s">
         <v>234</v>
       </c>
-      <c r="H3" s="22" t="b">
+      <c r="H3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I3" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="J3" s="22" t="b">
+      <c r="J3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K3" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="L3" s="22" t="b">
+      <c r="L3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5080,28 +4968,28 @@
       <c r="E4" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="F4" s="22" t="b">
+      <c r="F4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="G4" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="H4" s="22" t="b">
+      <c r="H4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I4" s="22" t="s">
         <v>240</v>
       </c>
-      <c r="J4" s="22" t="b">
+      <c r="J4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K4" s="22" t="s">
         <v>241</v>
       </c>
-      <c r="L4" s="22" t="b">
+      <c r="L4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5163,7 +5051,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD21"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="63.93"/>
@@ -5250,7 +5138,7 @@
       <c r="F3" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="G3" s="22" t="b">
+      <c r="G3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5286,7 +5174,7 @@
       <c r="F4" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="G4" s="22" t="b">
+      <c r="G4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5322,7 +5210,7 @@
       <c r="F5" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="G5" s="22" t="b">
+      <c r="G5" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5358,7 +5246,7 @@
       <c r="F6" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="G6" s="22" t="b">
+      <c r="G6" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5394,7 +5282,7 @@
       <c r="F7" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="G7" s="22" t="b">
+      <c r="G7" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5430,7 +5318,7 @@
       <c r="F8" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="G8" s="22" t="b">
+      <c r="G8" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>

--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="281">
   <si>
     <t xml:space="preserve">GENERAL CONFIGURATION</t>
   </si>
@@ -94,27 +94,27 @@
     <t xml:space="preserve">(16:30:00)</t>
   </si>
   <si>
+    <t xml:space="preserve">MISSION01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-Agent Test (Multi-Window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISSION02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Agent Test (Multi-Camera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM02</t>
+  </si>
+  <si>
     <t xml:space="preserve">X</t>
   </si>
   <si>
-    <t xml:space="preserve">MISSION01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single-Agent Test (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISSION02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Agent Test (Multi-Camera)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM02</t>
-  </si>
-  <si>
     <t xml:space="preserve">MISSION03</t>
   </si>
   <si>
@@ -292,16 +292,25 @@
     <t xml:space="preserve">TRACKING05</t>
   </si>
   <si>
+    <t xml:space="preserve">(X=10.0, Y=0.0, Z=0.0)</t>
+  </si>
+  <si>
     <t xml:space="preserve">AGENT06</t>
   </si>
   <si>
     <t xml:space="preserve">TRACKING06</t>
   </si>
   <si>
+    <t xml:space="preserve">(X=-10.0, Y=0.0, Z=0.0)</t>
+  </si>
+  <si>
     <t xml:space="preserve">AGENT07</t>
   </si>
   <si>
     <t xml:space="preserve">TRACKING07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(X=0.0, Y=10.0, Z=0.0)</t>
   </si>
   <si>
     <t xml:space="preserve">ObservationSetID</t>
@@ -938,18 +947,18 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="2" tint="-0.75"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1076,7 +1085,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1088,7 +1097,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1096,7 +1105,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1763,14 +1772,12 @@
       <c r="BD3" s="12"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="13"/>
+      <c r="B4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>13</v>
@@ -1779,7 +1786,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>16</v>
@@ -1845,10 +1852,10 @@
     <row r="5" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8"/>
       <c r="B5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>25</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>26</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>13</v>
@@ -1857,7 +1864,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>16</v>
@@ -1921,7 +1928,9 @@
       <c r="BD5" s="12"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8"/>
+      <c r="A6" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="B6" s="9" t="s">
         <v>28</v>
       </c>
@@ -2049,7 +2058,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -2070,62 +2079,62 @@
         <v>2</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I3" s="22" t="n">
         <v>0.4</v>
@@ -2715,7 +2724,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:XFD1048576"/>
+  <dimension ref="A1:XFD19"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
@@ -2834,7 +2843,7 @@
         <v>75</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>76</v>
@@ -2866,7 +2875,7 @@
         <v>78</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>79</v>
@@ -2898,7 +2907,7 @@
         <v>78</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>81</v>
@@ -2930,7 +2939,7 @@
         <v>78</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>83</v>
@@ -2971,7 +2980,7 @@
         <v>71</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="G8" s="19" t="s">
         <v>73</v>
@@ -2988,7 +2997,7 @@
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>85</v>
@@ -2997,13 +3006,13 @@
         <v>30</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E9" s="19" t="s">
         <v>71</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G9" s="19" t="s">
         <v>73</v>
@@ -3020,7 +3029,7 @@
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>85</v>
@@ -3029,13 +3038,13 @@
         <v>30</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E10" s="19" t="s">
         <v>71</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="G10" s="19" t="s">
         <v>73</v>
@@ -3059,7 +3068,6 @@
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
@@ -3116,16 +3124,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
@@ -3144,10 +3152,10 @@
         <v>70</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D3" s="19" t="n">
         <v>0.2</v>
@@ -3169,10 +3177,10 @@
         <v>76</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D4" s="19" t="n">
         <v>0.2</v>
@@ -3194,10 +3202,10 @@
         <v>79</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D5" s="19" t="n">
         <v>0.2</v>
@@ -3219,10 +3227,10 @@
         <v>81</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D6" s="19" t="n">
         <v>0.2</v>
@@ -3244,10 +3252,10 @@
         <v>83</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D7" s="19" t="n">
         <v>0.2</v>
@@ -3269,10 +3277,10 @@
         <v>86</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D8" s="19" t="n">
         <v>0.2</v>
@@ -3291,13 +3299,13 @@
     </row>
     <row r="9" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D9" s="19" t="n">
         <v>0.2</v>
@@ -3316,13 +3324,13 @@
     </row>
     <row r="10" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D10" s="19" t="n">
         <v>0.2</v>
@@ -3374,7 +3382,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:XFD1048576"/>
+  <dimension ref="A1:XFD35"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
@@ -3412,16 +3420,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G2" s="18" t="s">
         <v>63</v>
@@ -3430,13 +3438,13 @@
         <v>64</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K2" s="18" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
@@ -3444,28 +3452,28 @@
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I3" s="19" t="n">
         <v>3</v>
@@ -3480,28 +3488,28 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I4" s="19" t="n">
         <v>8</v>
@@ -3516,28 +3524,28 @@
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="F5" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" s="19" t="s">
+      <c r="G5" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="H5" s="19" t="s">
         <v>126</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>123</v>
       </c>
       <c r="I5" s="19" t="n">
         <v>8</v>
@@ -3552,28 +3560,28 @@
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I6" s="19" t="n">
         <v>8</v>
@@ -3588,28 +3596,28 @@
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I7" s="19" t="n">
         <v>8</v>
@@ -3624,28 +3632,28 @@
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I8" s="19" t="n">
         <v>3</v>
@@ -3661,28 +3669,28 @@
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I9" s="19" t="n">
         <v>3</v>
@@ -3697,28 +3705,28 @@
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I10" s="19" t="n">
         <v>8</v>
@@ -3733,28 +3741,28 @@
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D11" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="H11" s="19" t="s">
         <v>126</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>123</v>
       </c>
       <c r="I11" s="19" t="n">
         <v>8</v>
@@ -3769,28 +3777,28 @@
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I12" s="19" t="n">
         <v>8</v>
@@ -3805,28 +3813,28 @@
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I13" s="19" t="n">
         <v>8</v>
@@ -3841,28 +3849,28 @@
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I14" s="19" t="n">
         <v>3</v>
@@ -3877,28 +3885,28 @@
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I15" s="19" t="n">
         <v>8</v>
@@ -3913,28 +3921,28 @@
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D16" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="H16" s="19" t="s">
         <v>126</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>123</v>
       </c>
       <c r="I16" s="19" t="n">
         <v>8</v>
@@ -3949,28 +3957,28 @@
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I17" s="19" t="n">
         <v>8</v>
@@ -3985,28 +3993,28 @@
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H18" s="19" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I18" s="19" t="n">
         <v>8</v>
@@ -4021,28 +4029,28 @@
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I19" s="19" t="n">
         <v>3</v>
@@ -4057,28 +4065,28 @@
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I20" s="19" t="n">
         <v>8</v>
@@ -4093,28 +4101,28 @@
     </row>
     <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D21" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="H21" s="19" t="s">
         <v>126</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="G21" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>123</v>
       </c>
       <c r="I21" s="19" t="n">
         <v>8</v>
@@ -4129,28 +4137,28 @@
     </row>
     <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I22" s="19" t="n">
         <v>8</v>
@@ -4165,28 +4173,28 @@
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I23" s="19" t="n">
         <v>8</v>
@@ -4201,28 +4209,28 @@
     </row>
     <row r="24" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H24" s="19" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I24" s="19" t="n">
         <v>3</v>
@@ -4238,28 +4246,28 @@
     </row>
     <row r="25" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H25" s="19" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I25" s="19" t="n">
         <v>3</v>
@@ -4275,28 +4283,28 @@
     </row>
     <row r="26" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H26" s="19" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I26" s="19" t="n">
         <v>3</v>
@@ -4319,7 +4327,6 @@
     <row r="33" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="34" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="35" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
@@ -4374,19 +4381,19 @@
         <v>2</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="XEV2" s="3"/>
       <c r="XEW2" s="3"/>
@@ -4400,16 +4407,16 @@
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E3" s="19" t="n">
         <v>0.167</v>
@@ -4423,16 +4430,16 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E4" s="19" t="n">
         <v>0.167</v>
@@ -4446,16 +4453,16 @@
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>189</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>186</v>
       </c>
       <c r="E5" s="19" t="n">
         <v>0.167</v>
@@ -4469,16 +4476,16 @@
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E6" s="19" t="n">
         <v>0.167</v>
@@ -4492,16 +4499,16 @@
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E7" s="19" t="n">
         <v>0.167</v>
@@ -4515,16 +4522,16 @@
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E8" s="19" t="n">
         <v>0.167</v>
@@ -4538,16 +4545,16 @@
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E9" s="19" t="n">
         <v>0.167</v>
@@ -4561,16 +4568,16 @@
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E10" s="19" t="n">
         <v>0.167</v>
@@ -4584,16 +4591,16 @@
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E11" s="19" t="n">
         <v>0.167</v>
@@ -4607,16 +4614,16 @@
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E12" s="19" t="n">
         <v>0.167</v>
@@ -4630,16 +4637,16 @@
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E13" s="19" t="n">
         <v>0.167</v>
@@ -4653,16 +4660,16 @@
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E14" s="19" t="n">
         <v>0.167</v>
@@ -4676,16 +4683,16 @@
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E15" s="19" t="n">
         <v>0.167</v>
@@ -4699,16 +4706,16 @@
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E16" s="19" t="n">
         <v>0.167</v>
@@ -4722,16 +4729,16 @@
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E17" s="19" t="n">
         <v>0.167</v>
@@ -4745,16 +4752,16 @@
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E18" s="19" t="n">
         <v>0.167</v>
@@ -4816,7 +4823,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -4847,49 +4854,49 @@
         <v>39</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="M2" s="21" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N2" s="21" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O2" s="21" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="P2" s="21" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q2" s="21" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R2" s="21" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4900,7 +4907,7 @@
         <v>33</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D3" s="22" t="n">
         <v>8</v>
@@ -4913,28 +4920,28 @@
         <v>1</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="J3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K3" s="22" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="L3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="M3" s="22" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="N3" s="22" t="n">
         <v>6.5</v>
@@ -4954,13 +4961,13 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="22" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>37</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D4" s="22" t="n">
         <v>8</v>
@@ -4973,28 +4980,28 @@
         <v>1</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="J4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K4" s="22" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="M4" s="22" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="N4" s="22" t="n">
         <v>6.5</v>
@@ -5068,7 +5075,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -5092,28 +5099,28 @@
         <v>39</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="XFB2" s="3"/>
       <c r="XFC2" s="3"/>
@@ -5121,29 +5128,29 @@
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="I3" s="22" t="n">
         <v>0.5</v>
@@ -5157,29 +5164,29 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="22" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B4" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="E4" s="22" t="s">
         <v>256</v>
       </c>
-      <c r="C4" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="D4" s="22" t="s">
+      <c r="F4" s="22" t="s">
         <v>257</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>254</v>
       </c>
       <c r="G4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="I4" s="22" t="n">
         <v>0.5</v>
@@ -5193,29 +5200,29 @@
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G5" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="I5" s="22" t="n">
         <v>0.5</v>
@@ -5229,29 +5236,29 @@
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B6" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="F6" s="22" t="s">
         <v>263</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>260</v>
       </c>
       <c r="G6" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="I6" s="22" t="n">
         <v>0.5</v>
@@ -5265,29 +5272,29 @@
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G7" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="I7" s="22" t="n">
         <v>0.8</v>
@@ -5301,29 +5308,29 @@
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G8" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="I8" s="22" t="n">
         <v>0.8</v>

--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="257">
   <si>
     <t xml:space="preserve">GENERAL CONFIGURATION</t>
   </si>
@@ -109,6 +109,9 @@
     <t xml:space="preserve">Multi-Agent Test (Multi-Camera)</t>
   </si>
   <si>
+    <t xml:space="preserve">GROUP03</t>
+  </si>
+  <si>
     <t xml:space="preserve">TEAM02</t>
   </si>
   <si>
@@ -205,9 +208,6 @@
     <t xml:space="preserve">Target Configuration L4</t>
   </si>
   <si>
-    <t xml:space="preserve">GROUP03</t>
-  </si>
-  <si>
     <t xml:space="preserve">TargetConfigurationL4</t>
   </si>
   <si>
@@ -493,90 +493,54 @@
     <t xml:space="preserve">MULTICAMERA9</t>
   </si>
   <si>
-    <t xml:space="preserve">Tracking Head 3 Multi-Camera 1 (Multi)</t>
+    <t xml:space="preserve">Central Head Multi-Camera 2 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTICAMERA10</t>
   </si>
   <si>
-    <t xml:space="preserve">Tracking Head 4 Multi-Camera 1 (Multi)</t>
+    <t xml:space="preserve">Tracking Head 1 Multi-Camera 2 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTICAMERA11</t>
   </si>
   <si>
-    <t xml:space="preserve">Central Head Multi-Camera 2 (Multi)</t>
+    <t xml:space="preserve">Tracking Head 2 Multi-Camera 2 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTICAMERA12</t>
   </si>
   <si>
-    <t xml:space="preserve">Tracking Head 1 Multi-Camera 2 (Multi)</t>
+    <t xml:space="preserve">Central Head Multi-Camera 3 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTICAMERA13</t>
   </si>
   <si>
-    <t xml:space="preserve">Tracking Head 2 Multi-Camera 2 (Multi)</t>
+    <t xml:space="preserve">Tracking Head 1 Multi-Camera 3 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTICAMERA14</t>
   </si>
   <si>
-    <t xml:space="preserve">Tracking Head 3 Multi-Camera 2 (Multi)</t>
+    <t xml:space="preserve">Tracking Head 2 Multi-Camera 3 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTICAMERA15</t>
   </si>
   <si>
-    <t xml:space="preserve">Tracking Head 4 Multi-Camera 2 (Multi)</t>
+    <t xml:space="preserve">Central Head Multi-Window 1 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTICAMERA16</t>
   </si>
   <si>
-    <t xml:space="preserve">Central Head Multi-Camera 3 (Multi)</t>
+    <t xml:space="preserve">Central Head Multi-Window 2 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTICAMERA17</t>
   </si>
   <si>
-    <t xml:space="preserve">Tracking Head 1 Multi-Camera 3 (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTICAMERA18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Head 2 Multi-Camera 3 (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTICAMERA19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Head 3 Multi-Camera 3 (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTICAMERA20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Head 4 Multi-Camera 3 (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTICAMERA21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central Head Multi-Window 1 (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTICAMERA22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central Head Multi-Window 2 (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTICAMERA23</t>
-  </si>
-  <si>
     <t xml:space="preserve">Central Head Multi-Window 3 (Multi)</t>
   </si>
   <si>
@@ -634,61 +598,25 @@
     <t xml:space="preserve">MULTIWINDOW06</t>
   </si>
   <si>
-    <t xml:space="preserve">Tracking Window 3 Multi-Window 1 (Multi)</t>
+    <t xml:space="preserve">Tracking Window 1 Multi-Window 2 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTIWINDOW07</t>
   </si>
   <si>
-    <t xml:space="preserve">Tracking Window 4 Multi-Window 1 (Multi)</t>
+    <t xml:space="preserve">Tracking Window 2 Multi-Window 2 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTIWINDOW08</t>
   </si>
   <si>
-    <t xml:space="preserve">Tracking Window 1 Multi-Window 2 (Multi)</t>
+    <t xml:space="preserve">Tracking Window 1 Multi-Window 3 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTIWINDOW09</t>
   </si>
   <si>
-    <t xml:space="preserve">Tracking Window 2 Multi-Window 2 (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Window 3 Multi-Window 2 (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Window 4 Multi-Window 2 (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Window 1 Multi-Window 3 (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW13</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tracking Window 2 Multi-Window 3 (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Window 3 Multi-Window 3 (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIWINDOW15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Window 4 Multi-Window 3 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">HARDWARE CATALOGS</t>
@@ -884,7 +812,7 @@
     <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -945,13 +873,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1052,7 +973,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1085,7 +1006,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1097,16 +1018,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1314,8 +1231,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table210" displayName="Table210" ref="A2:J17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A2:J17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table210" displayName="Table210" ref="A2:J14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A2:J14"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Name"/>
@@ -1772,7 +1689,7 @@
       <c r="BD3" s="12"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13"/>
+      <c r="A4" s="8"/>
       <c r="B4" s="9" t="s">
         <v>21</v>
       </c>
@@ -1861,10 +1778,10 @@
         <v>13</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>16</v>
@@ -1929,22 +1846,22 @@
     </row>
     <row r="6" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>16</v>
@@ -2057,92 +1974,92 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="A1" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>273</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>274</v>
-      </c>
-      <c r="G2" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="I2" s="21" t="s">
+      <c r="C2" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="F2" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>252</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>228</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="C3" s="23" t="b">
+      <c r="B3" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D3" s="22" t="s">
-        <v>278</v>
-      </c>
-      <c r="E3" s="23" t="b">
+      <c r="D3" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="E3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F3" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="G3" s="23" t="b">
+      <c r="F3" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="22" t="s">
-        <v>280</v>
-      </c>
-      <c r="I3" s="22" t="n">
+      <c r="H3" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="I3" s="21" t="n">
         <v>0.4</v>
       </c>
-      <c r="J3" s="22" t="n">
+      <c r="J3" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="22" t="n">
+      <c r="K3" s="21" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2195,12 +2112,12 @@
   </cols>
   <sheetData>
     <row r="1" s="7" customFormat="true" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
       <c r="E1" s="12"/>
       <c r="XFB1" s="3"/>
       <c r="XFC1" s="3"/>
@@ -2214,10 +2131,10 @@
         <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2225,27 +2142,27 @@
         <v>13</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="15" t="s">
         <v>35</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2284,15 +2201,15 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
@@ -2305,16 +2222,16 @@
         <v>4</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
@@ -2377,25 +2294,25 @@
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="16" t="n">
+        <v>47</v>
+      </c>
+      <c r="E3" s="15" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
@@ -2458,25 +2375,25 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="16" t="n">
+        <v>47</v>
+      </c>
+      <c r="E4" s="15" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
@@ -2539,25 +2456,25 @@
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="16" t="n">
+        <v>47</v>
+      </c>
+      <c r="E5" s="15" t="n">
         <v>8</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
@@ -2620,22 +2537,22 @@
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="16" t="n">
+        <v>47</v>
+      </c>
+      <c r="E6" s="15" t="n">
         <v>16</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>59</v>
@@ -2744,50 +2661,50 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
       <c r="XFC1" s="3"/>
       <c r="XFD1" s="3"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>67</v>
       </c>
       <c r="L2" s="12"/>
@@ -2802,260 +2719,260 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H3" s="19" t="n">
+      <c r="H3" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I3" s="19" t="n">
+      <c r="I3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="J3" s="18" t="n">
         <v>12000</v>
       </c>
       <c r="XFC3" s="3"/>
       <c r="XFD3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H4" s="19" t="n">
+      <c r="H4" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="I4" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="19" t="s">
+      <c r="C5" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="19" t="s">
+      <c r="C6" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H6" s="19" t="n">
+      <c r="H6" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="I6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J6" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="19" t="s">
+      <c r="C7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H7" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I7" s="19" t="n">
+      <c r="I7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J7" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="19" t="s">
+      <c r="C8" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H8" s="19" t="n">
+      <c r="H8" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I8" s="19" t="n">
+      <c r="I8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J8" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="19" t="s">
+      <c r="C9" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="19" t="s">
+      <c r="C10" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -3107,32 +3024,32 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>97</v>
       </c>
       <c r="H2" s="12"/>
@@ -3148,22 +3065,22 @@
       <c r="XFD2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="D3" s="19" t="n">
+      <c r="D3" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="19" t="n">
+      <c r="E3" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G3" s="2"/>
@@ -3173,22 +3090,22 @@
       <c r="XEY3" s="3"/>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D4" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G4" s="2"/>
@@ -3198,22 +3115,22 @@
       <c r="XEY4" s="3"/>
     </row>
     <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G5" s="2"/>
@@ -3223,22 +3140,22 @@
       <c r="XEY5" s="3"/>
     </row>
     <row r="6" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G6" s="2"/>
@@ -3248,22 +3165,22 @@
       <c r="XEY6" s="3"/>
     </row>
     <row r="7" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G7" s="2"/>
@@ -3273,22 +3190,22 @@
       <c r="XEY7" s="3"/>
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G8" s="2"/>
@@ -3298,22 +3215,22 @@
       <c r="XEY8" s="3"/>
     </row>
     <row r="9" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G9" s="2"/>
@@ -3323,22 +3240,22 @@
       <c r="XEY9" s="3"/>
     </row>
     <row r="10" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G10" s="2"/>
@@ -3382,7 +3299,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:XFD35"/>
+  <dimension ref="A1:XFD29"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
@@ -3397,53 +3314,53 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
       <c r="L1" s="2"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="17" t="s">
         <v>119</v>
       </c>
       <c r="M2" s="12"/>
@@ -3451,882 +3368,666 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="19" t="n">
+      <c r="I3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="J3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K3" s="19" t="n">
+      <c r="K3" s="18" t="n">
         <v>3</v>
       </c>
       <c r="L3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="I4" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K4" s="19" t="n">
+      <c r="K4" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K5" s="19" t="n">
+      <c r="K5" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="I6" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J6" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K6" s="19" t="n">
+      <c r="K6" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="I7" s="19" t="n">
+      <c r="I7" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J7" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K7" s="19" t="n">
+      <c r="K7" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L7" s="2"/>
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="I8" s="19" t="n">
+      <c r="I8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="19" t="n">
+      <c r="K8" s="18" t="n">
         <v>3</v>
       </c>
       <c r="L8" s="2"/>
       <c r="XFD8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="19" t="n">
+      <c r="K9" s="18" t="n">
         <v>3</v>
       </c>
       <c r="L9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K10" s="19" t="n">
+      <c r="K10" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K11" s="19" t="n">
+      <c r="K11" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="C12" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" s="19" t="s">
+      <c r="C12" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E13" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F13" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="G12" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="I12" s="19" t="n">
+      <c r="G13" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="I13" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J12" s="19" t="n">
+      <c r="J13" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K12" s="19" t="n">
+      <c r="K13" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D13" s="19" t="s">
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E14" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F14" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="G13" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="I13" s="19" t="n">
+      <c r="G14" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="I14" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J13" s="19" t="n">
+      <c r="J14" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K13" s="19" t="n">
+      <c r="K14" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" s="19" t="s">
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E15" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F15" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G15" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="H15" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="I14" s="19" t="n">
+      <c r="I15" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J14" s="19" t="n">
+      <c r="J15" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K14" s="19" t="n">
+      <c r="K15" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" s="19" t="s">
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E16" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F16" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G16" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="H16" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="I15" s="19" t="n">
+      <c r="I16" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J15" s="19" t="n">
+      <c r="J16" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K15" s="19" t="n">
+      <c r="K16" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D16" s="19" t="s">
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E17" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F17" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G17" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="H17" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="I16" s="19" t="n">
+      <c r="I17" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J16" s="19" t="n">
+      <c r="J17" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K16" s="19" t="n">
+      <c r="K17" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L16" s="2"/>
-    </row>
-    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="E17" s="19" t="s">
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="E18" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F17" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="H17" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J17" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K17" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="E18" s="19" t="s">
+      <c r="F18" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="XFD18" s="3"/>
+    </row>
+    <row r="19" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="E19" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F18" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="H18" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="I18" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J18" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K18" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L18" s="2"/>
-    </row>
-    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="E19" s="19" t="s">
+      <c r="F19" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="XFD19" s="3"/>
+    </row>
+    <row r="20" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="E20" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F20" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G20" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H19" s="19" t="s">
+      <c r="H20" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="I19" s="19" t="n">
+      <c r="I20" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J19" s="19" t="n">
+      <c r="J20" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K19" s="19" t="n">
+      <c r="K20" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="H20" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="I20" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J20" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K20" s="19" t="n">
-        <v>10</v>
-      </c>
       <c r="L20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="G21" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="I21" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J21" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K21" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="I22" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J22" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K22" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L22" s="2"/>
-    </row>
-    <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="H23" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="I23" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J23" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K23" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L23" s="2"/>
-    </row>
-    <row r="24" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="F24" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="G24" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="H24" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="I24" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L24" s="2"/>
-      <c r="XFD24" s="3"/>
-    </row>
-    <row r="25" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="F25" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="H25" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="I25" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J25" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L25" s="2"/>
-      <c r="XFD25" s="3"/>
-    </row>
-    <row r="26" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="D26" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="F26" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="G26" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="H26" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="I26" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J26" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K26" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L26" s="2"/>
-      <c r="XFD26" s="3"/>
-    </row>
+      <c r="XFD20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="28" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="29" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="30" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="33" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="34" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="35" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
@@ -4349,7 +4050,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:XFD1048576"/>
+  <dimension ref="A1:XFD13"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
@@ -4363,37 +4064,37 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>186</v>
+      <c r="D2" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>174</v>
       </c>
       <c r="XEV2" s="3"/>
       <c r="XEW2" s="3"/>
@@ -4406,381 +4107,236 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="E3" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F3" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="18" t="n">
+        <v>0.583</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F4" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>0.583</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0.583</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>0.583</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>0.583</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="C8" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>0.583</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D3" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="E3" s="19" t="n">
+      <c r="C9" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="E9" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="19" t="n">
+      <c r="G9" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E4" s="19" t="n">
+      <c r="C10" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="E10" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="19" t="n">
+      <c r="G10" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E5" s="19" t="n">
+      <c r="C11" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="E11" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F11" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G11" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E6" s="19" t="n">
+      <c r="C12" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="E12" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F12" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G12" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E8" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E16" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F16" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E17" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F17" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E18" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F18" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="19" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
@@ -4822,200 +4378,200 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
+      <c r="A1" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>223</v>
-      </c>
-      <c r="G2" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="I2" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="J2" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="K2" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="L2" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="M2" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="N2" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="O2" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="P2" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q2" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="R2" s="21" t="s">
-        <v>235</v>
+      <c r="C2" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="M2" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="N2" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="O2" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="P2" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q2" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="R2" s="20" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="D3" s="22" t="n">
+      <c r="B3" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="D3" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="22" t="n">
+      <c r="E3" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="23" t="b">
+      <c r="F3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G3" s="22" t="s">
-        <v>237</v>
-      </c>
-      <c r="H3" s="23" t="b">
+      <c r="G3" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="H3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I3" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="J3" s="23" t="b">
+      <c r="I3" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="J3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K3" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="L3" s="23" t="b">
+      <c r="K3" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="L3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M3" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="N3" s="22" t="n">
+      <c r="M3" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="N3" s="21" t="n">
         <v>6.5</v>
       </c>
-      <c r="O3" s="22" t="n">
+      <c r="O3" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="P3" s="22" t="n">
+      <c r="P3" s="21" t="n">
         <v>400</v>
       </c>
-      <c r="Q3" s="22" t="n">
+      <c r="Q3" s="21" t="n">
         <v>350</v>
       </c>
-      <c r="R3" s="22" t="n">
+      <c r="R3" s="21" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
-        <v>241</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="D4" s="22" t="n">
+      <c r="A4" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="D4" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="22" t="n">
+      <c r="E4" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F4" s="23" t="b">
+      <c r="F4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G4" s="22" t="s">
-        <v>242</v>
-      </c>
-      <c r="H4" s="23" t="b">
+      <c r="G4" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="H4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I4" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="J4" s="23" t="b">
+      <c r="I4" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="J4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K4" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="L4" s="23" t="b">
+      <c r="K4" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="L4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M4" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="N4" s="22" t="n">
+      <c r="M4" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="N4" s="21" t="n">
         <v>6.5</v>
       </c>
-      <c r="O4" s="22" t="n">
+      <c r="O4" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="P4" s="22" t="n">
+      <c r="P4" s="21" t="n">
         <v>400</v>
       </c>
-      <c r="Q4" s="22" t="n">
+      <c r="Q4" s="21" t="n">
         <v>350</v>
       </c>
-      <c r="R4" s="22" t="n">
+      <c r="R4" s="21" t="n">
         <v>25</v>
       </c>
     </row>
@@ -5074,271 +4630,271 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="A1" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="G2" s="21" t="s">
-        <v>248</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="I2" s="21" t="s">
-        <v>250</v>
-      </c>
-      <c r="J2" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="K2" s="21" t="s">
-        <v>252</v>
+      <c r="C2" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>228</v>
       </c>
       <c r="XFB2" s="3"/>
       <c r="XFC2" s="3"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>255</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="G3" s="23" t="b">
+      <c r="B3" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="I3" s="22" t="n">
+      <c r="H3" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="I3" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J3" s="22" t="n">
+      <c r="J3" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K3" s="22" t="n">
+      <c r="K3" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="22" t="s">
-        <v>259</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="G4" s="23" t="b">
+      <c r="B4" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="I4" s="22" t="n">
+      <c r="H4" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="I4" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" s="22" t="n">
+      <c r="J4" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K4" s="22" t="n">
+      <c r="K4" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
-        <v>261</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>262</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>255</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="G5" s="23" t="b">
+      <c r="A5" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="G5" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H5" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="I5" s="22" t="n">
+      <c r="H5" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="I5" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="22" t="n">
+      <c r="J5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="22" t="n">
+      <c r="K5" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
-        <v>265</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>266</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="G6" s="23" t="b">
+      <c r="A6" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="G6" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H6" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="I6" s="22" t="n">
+      <c r="H6" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="I6" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J6" s="22" t="n">
+      <c r="J6" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="22" t="n">
+      <c r="K6" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>268</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="G7" s="23" t="b">
+      <c r="B7" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="G7" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H7" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="I7" s="22" t="n">
+      <c r="H7" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="I7" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="J7" s="22" t="n">
+      <c r="J7" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="22" t="n">
+      <c r="K7" s="21" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
-        <v>269</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>268</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="G8" s="23" t="b">
+      <c r="A8" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="G8" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H8" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="I8" s="22" t="n">
+      <c r="H8" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="I8" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="J8" s="22" t="n">
+      <c r="J8" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="22" t="n">
+      <c r="K8" s="21" t="n">
         <v>6</v>
       </c>
     </row>

--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="320">
   <si>
     <t xml:space="preserve">GENERAL CONFIGURATION</t>
   </si>
@@ -94,6 +94,9 @@
     <t xml:space="preserve">(16:30:00)</t>
   </si>
   <si>
+    <t xml:space="preserve">X</t>
+  </si>
+  <si>
     <t xml:space="preserve">MISSION01</t>
   </si>
   <si>
@@ -106,25 +109,68 @@
     <t xml:space="preserve">MISSION02</t>
   </si>
   <si>
+    <t xml:space="preserve">Single-Agent Test (Multi-Hybrid)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISSION03</t>
+  </si>
+  <si>
     <t xml:space="preserve">Multi-Agent Test (Multi-Camera)</t>
   </si>
   <si>
     <t xml:space="preserve">GROUP03</t>
   </si>
   <si>
-    <t xml:space="preserve">TEAM02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISSION03</t>
+    <t xml:space="preserve">TEAM03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISSION04</t>
   </si>
   <si>
     <t xml:space="preserve">Multi-Agent Test (Multi-Window)</t>
   </si>
   <si>
-    <t xml:space="preserve">TEAM03</t>
+    <t xml:space="preserve">TEAM04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISSION05</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Multi-Agent Test (Multi-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hybrid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM05</t>
   </si>
   <si>
     <t xml:space="preserve">Geopoint</t>
@@ -220,168 +266,275 @@
     <t xml:space="preserve">DroneID</t>
   </si>
   <si>
+    <t xml:space="preserve">(X=10.0, Y=0.0, Z=0.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orientation [°]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxAltitude [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SafetyRadius [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BatteryCapacity [mAh]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENT00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Camera Agent (Single)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRACKING00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRONE00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Roll=0.0, Pitch=0.0, Yaw=0.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENT01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Window Agent (Single)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRACKING01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENT02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Hybrid Agent (Single)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRACKING02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENT03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Camera Agent (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRACKING03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENT04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRACKING04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(X=-10.0, Y=0.0, Z=0.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENT05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRACKING05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(X=0.0, Y=10.0, Z=0.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENT06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Window Agent (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRACKING06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENT07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRACKING07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENT08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRACKING08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENT09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Hybrid Agent (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRACKING09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENT10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRACKING10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENT11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRACKING11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ObservationSetID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MinTargetSize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxTargetSize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RefTargetSize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Camera Tracking (Single)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Window Tracking (Single)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Hybrid Tracking (Single)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Camera Tracking 1 (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Camera Tracking 2 (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Camera Tracking 3 (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Window Tracking 1 (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Window Tracking 2 (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Window Tracking 3 (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Hybrid Tracking 1 (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET09</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Multi-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hybrid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Tracking 2 (Multi)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SET10</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Multi-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hybrid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Tracking 3 (Multi)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SET11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CameraID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GimbalID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
     <t xml:space="preserve">Position [m]</t>
   </si>
   <si>
-    <t xml:space="preserve">Orientation [°]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxAltitude [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SafetyRadius [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BatteryCapacity [mAh]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGENT00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Camera Agent (Single)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRACKING00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRONE00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(X=0.0, Y=0.0, Z=0.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Roll=0.0, Pitch=0.0, Yaw=0.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGENT01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Window Agent (Single)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRACKING01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGENT02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Camera Agent (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRACKING02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGENT03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRACKING03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGENT04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRACKING04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGENT05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Window Agent (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRACKING05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(X=10.0, Y=0.0, Z=0.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGENT06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRACKING06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(X=-10.0, Y=0.0, Z=0.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGENT07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRACKING07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(X=0.0, Y=10.0, Z=0.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ObservationSetID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MinTargetSize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxTargetSize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RefTargetSize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Camera Tracking (Single)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SET00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Window Tracking (Single)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SET01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Camera Tracking 1 (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SET02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Camera Tracking 2 (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SET03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Camera Tracking 3 (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SET04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Window Tracking 1 (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SET05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Window Tracking 2 (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SET06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Window Tracking 3 (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SET07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CameraID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GimbalID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
     <t xml:space="preserve">MinFocal [mm]</t>
   </si>
   <si>
@@ -475,75 +628,485 @@
     <t xml:space="preserve">MULTICAMERA6</t>
   </si>
   <si>
+    <t xml:space="preserve">Central Head Multi-Hybrid (Single)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTICAMERA7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tracking Head 1 Multi-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hybrid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (Single)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTICAMERA8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tracking Head 2 Multi-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hybrid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (Single)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTICAMERA9</t>
+  </si>
+  <si>
     <t xml:space="preserve">Central Head Multi-Camera 1 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA7</t>
+    <t xml:space="preserve">MULTICAMERA10</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 1 Multi-Camera 1 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA8</t>
+    <t xml:space="preserve">MULTICAMERA11</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 2 Multi-Camera 1 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA9</t>
+    <t xml:space="preserve">MULTICAMERA12</t>
   </si>
   <si>
     <t xml:space="preserve">Central Head Multi-Camera 2 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA10</t>
+    <t xml:space="preserve">MULTICAMERA13</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 1 Multi-Camera 2 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA11</t>
+    <t xml:space="preserve">MULTICAMERA14</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 2 Multi-Camera 2 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA12</t>
+    <t xml:space="preserve">MULTICAMERA15</t>
   </si>
   <si>
     <t xml:space="preserve">Central Head Multi-Camera 3 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA13</t>
+    <t xml:space="preserve">MULTICAMERA16</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 1 Multi-Camera 3 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA14</t>
+    <t xml:space="preserve">MULTICAMERA17</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 2 Multi-Camera 3 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA15</t>
+    <t xml:space="preserve">MULTICAMERA18</t>
   </si>
   <si>
     <t xml:space="preserve">Central Head Multi-Window 1 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA16</t>
+    <t xml:space="preserve">MULTICAMERA19</t>
   </si>
   <si>
     <t xml:space="preserve">Central Head Multi-Window 2 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA17</t>
+    <t xml:space="preserve">MULTICAMERA20</t>
   </si>
   <si>
     <t xml:space="preserve">Central Head Multi-Window 3 (Multi)</t>
   </si>
   <si>
+    <t xml:space="preserve">MULTICAMERA21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central Head Multi-Hybrid 1 (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTICAMERA22</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tracking Head 1 Multi-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hybrid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 1 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Multi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTICAMERA23</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tracking Head 2 Multi-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hybrid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 1 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Multi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTICAMERA24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central Head Multi-Hybrid 2 (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTICAMERA25</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tracking Head 1 Multi-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hybrid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 2 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Multi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTICAMERA26</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tracking Head 2 Multi-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hybrid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 2 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Multi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTICAMERA27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central Head Multi-Hybrid 3 (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTICAMERA28</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tracking Head 1 Multi-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hybrid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 3 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Multi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTICAMERA29</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tracking Head 2 Multi-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hybrid 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Multi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Resolution [pix]</t>
   </si>
   <si>
@@ -586,37 +1149,197 @@
     <t xml:space="preserve">MULTIWINDOW04</t>
   </si>
   <si>
+    <t xml:space="preserve">Tracking Window 1 Multi-Hybrid (Single)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW05</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tracking Window 2 Multi-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hybrid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (Single)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW06</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tracking Window 1 Multi-Window 1 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTIWINDOW05</t>
+    <t xml:space="preserve">MULTIWINDOW07</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Window 2 Multi-Window 1 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTIWINDOW06</t>
+    <t xml:space="preserve">MULTIWINDOW08</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Window 1 Multi-Window 2 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTIWINDOW07</t>
+    <t xml:space="preserve">MULTIWINDOW09</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Window 2 Multi-Window 2 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTIWINDOW08</t>
+    <t xml:space="preserve">MULTIWINDOW10</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Window 1 Multi-Window 3 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTIWINDOW09</t>
+    <t xml:space="preserve">MULTIWINDOW11</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Window 2 Multi-Window 3 (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 1 Multi-Hybrid 1 (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW13</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tracking Window 2 Multi-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hybrid 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (Multi)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 1 Multi-Hybrid 2 (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW15</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tracking Window 2 Multi-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hybrid 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (Multi)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 1 Multi-Hybrid 3 (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW17</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tracking Window 2 Multi-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hybrid 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (Multi)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">HARDWARE CATALOGS</t>
@@ -812,7 +1535,7 @@
     <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -880,6 +1603,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -973,7 +1709,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1024,6 +1760,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1205,7 +1945,7 @@
     <tableColumn id="3" name="AgentTeamID"/>
     <tableColumn id="4" name="TrackingID"/>
     <tableColumn id="5" name="DroneID"/>
-    <tableColumn id="6" name="Position [m]"/>
+    <tableColumn id="6" name="(X=10.0, Y=0.0, Z=0.0)"/>
     <tableColumn id="7" name="Orientation [°]"/>
     <tableColumn id="8" name="MaxAltitude [m]"/>
     <tableColumn id="9" name="SafetyRadius [m]"/>
@@ -1231,8 +1971,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table210" displayName="Table210" ref="A2:J14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A2:J14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table210" displayName="Table210" ref="A2:J17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A2:J17"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Name"/>
@@ -1689,12 +2429,14 @@
       <c r="BD3" s="12"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
+      <c r="A4" s="13" t="s">
+        <v>21</v>
+      </c>
       <c r="B4" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>13</v>
@@ -1703,7 +2445,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>16</v>
@@ -1767,18 +2509,18 @@
       <c r="BD4" s="12"/>
     </row>
     <row r="5" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>27</v>
@@ -1843,22 +2585,22 @@
       <c r="BB5" s="12"/>
       <c r="BC5" s="12"/>
       <c r="BD5" s="12"/>
+      <c r="XFC5" s="0"/>
+      <c r="XFD5" s="0"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="C6" s="10" t="s">
         <v>29</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>30</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>31</v>
@@ -1924,13 +2666,167 @@
       <c r="BC6" s="12"/>
       <c r="BD6" s="12"/>
     </row>
-    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="7" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="12"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="12"/>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12"/>
+      <c r="AA7" s="12"/>
+      <c r="AB7" s="12"/>
+      <c r="AC7" s="12"/>
+      <c r="AD7" s="12"/>
+      <c r="AE7" s="12"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+      <c r="BC7" s="12"/>
+      <c r="BD7" s="12"/>
+    </row>
+    <row r="8" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8"/>
+      <c r="B8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="12"/>
+      <c r="X8" s="12"/>
+      <c r="Y8" s="12"/>
+      <c r="Z8" s="12"/>
+      <c r="AA8" s="12"/>
+      <c r="AB8" s="12"/>
+      <c r="AC8" s="12"/>
+      <c r="AD8" s="12"/>
+      <c r="AE8" s="12"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+    </row>
     <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -1974,92 +2870,92 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="A1" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>247</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>228</v>
+      <c r="C2" s="21" t="s">
+        <v>310</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>291</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>253</v>
-      </c>
-      <c r="C3" s="22" t="b">
+      <c r="A3" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>316</v>
+      </c>
+      <c r="C3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>254</v>
-      </c>
-      <c r="E3" s="22" t="b">
+      <c r="D3" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="E3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F3" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="G3" s="22" t="b">
+      <c r="F3" s="22" t="s">
+        <v>318</v>
+      </c>
+      <c r="G3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="I3" s="21" t="n">
+      <c r="H3" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="I3" s="22" t="n">
         <v>0.4</v>
       </c>
-      <c r="J3" s="21" t="n">
+      <c r="J3" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="21" t="n">
+      <c r="K3" s="22" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2112,12 +3008,12 @@
   </cols>
   <sheetData>
     <row r="1" s="7" customFormat="true" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
       <c r="E1" s="12"/>
       <c r="XFB1" s="3"/>
       <c r="XFC1" s="3"/>
@@ -2131,10 +3027,10 @@
         <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2142,27 +3038,27 @@
         <v>13</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>36</v>
+        <v>41</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2201,15 +3097,15 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
@@ -2222,16 +3118,16 @@
         <v>4</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
@@ -2294,25 +3190,25 @@
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="15" t="n">
+        <v>53</v>
+      </c>
+      <c r="E3" s="16" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
@@ -2375,25 +3271,25 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="15" t="n">
+        <v>53</v>
+      </c>
+      <c r="E4" s="16" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
@@ -2456,25 +3352,25 @@
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="15" t="n">
+        <v>53</v>
+      </c>
+      <c r="E5" s="16" t="n">
         <v>8</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
@@ -2537,25 +3433,25 @@
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="15" t="n">
+        <v>53</v>
+      </c>
+      <c r="E6" s="16" t="n">
         <v>16</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
@@ -2641,7 +3537,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:XFD19"/>
+  <dimension ref="A1:XFD20"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
@@ -2661,51 +3557,51 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="A1" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
       <c r="XFC1" s="3"/>
       <c r="XFD1" s="3"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="J2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>67</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>73</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="12"/>
@@ -2719,272 +3615,399 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="H3" s="18" t="n">
+      <c r="G3" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I3" s="18" t="n">
+      <c r="I3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J3" s="19" t="n">
         <v>12000</v>
       </c>
       <c r="XFC3" s="3"/>
       <c r="XFD3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="H4" s="18" t="n">
+      <c r="A4" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="I4" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J4" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="F5" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="H5" s="18" t="n">
+      <c r="H5" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J5" s="19" t="n">
         <v>12000</v>
       </c>
+      <c r="XFC5" s="0"/>
+      <c r="XFD5" s="0"/>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" s="18" t="s">
+      <c r="A6" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="H6" s="18" t="n">
+      <c r="H6" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="J6" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" s="18" t="s">
+      <c r="A7" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="H7" s="18" t="n">
+      <c r="H7" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J7" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="18" t="s">
+      <c r="A8" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="H8" s="18" t="n">
+      <c r="D8" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J8" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F9" s="18" t="s">
+      <c r="A9" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="G9" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="H9" s="18" t="n">
+      <c r="G10" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I10" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J10" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="18" t="s">
+    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="G10" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="H10" s="18" t="n">
+      <c r="G11" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I11" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="J11" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>12000</v>
+      </c>
+    </row>
     <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
@@ -3007,7 +4030,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:XFD23"/>
+  <dimension ref="A1:XFD24"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
@@ -3024,33 +4047,33 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="A1" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>97</v>
+      <c r="C2" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>111</v>
       </c>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
@@ -3065,22 +4088,22 @@
       <c r="XFD2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="D3" s="18" t="n">
+      <c r="A3" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G3" s="2"/>
@@ -3090,22 +4113,22 @@
       <c r="XEY3" s="3"/>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D4" s="18" t="n">
+      <c r="A4" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G4" s="2"/>
@@ -3115,22 +4138,22 @@
       <c r="XEY4" s="3"/>
     </row>
     <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D5" s="18" t="n">
+      <c r="A5" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G5" s="2"/>
@@ -3138,24 +4161,29 @@
       <c r="XEW5" s="2"/>
       <c r="XEX5" s="2"/>
       <c r="XEY5" s="3"/>
+      <c r="XEZ5" s="0"/>
+      <c r="XFA5" s="0"/>
+      <c r="XFB5" s="0"/>
+      <c r="XFC5" s="0"/>
+      <c r="XFD5" s="0"/>
     </row>
     <row r="6" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" s="18" t="n">
+      <c r="A6" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G6" s="2"/>
@@ -3165,22 +4193,22 @@
       <c r="XEY6" s="3"/>
     </row>
     <row r="7" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D7" s="18" t="n">
+      <c r="A7" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G7" s="2"/>
@@ -3190,22 +4218,22 @@
       <c r="XEY7" s="3"/>
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="18" t="n">
+      <c r="A8" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G8" s="2"/>
@@ -3215,22 +4243,22 @@
       <c r="XEY8" s="3"/>
     </row>
     <row r="9" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="D9" s="18" t="n">
+      <c r="A9" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="D9" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G9" s="2"/>
@@ -3240,22 +4268,22 @@
       <c r="XEY9" s="3"/>
     </row>
     <row r="10" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D10" s="18" t="n">
+      <c r="A10" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G10" s="2"/>
@@ -3264,10 +4292,106 @@
       <c r="XEX10" s="2"/>
       <c r="XEY10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="XEV11" s="2"/>
+      <c r="XEW11" s="2"/>
+      <c r="XEX11" s="2"/>
+      <c r="XEY11" s="3"/>
+    </row>
+    <row r="12" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="XEV12" s="2"/>
+      <c r="XEW12" s="2"/>
+      <c r="XEX12" s="2"/>
+      <c r="XEY12" s="3"/>
+    </row>
+    <row r="13" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="XEV13" s="2"/>
+      <c r="XEW13" s="2"/>
+      <c r="XEX13" s="2"/>
+      <c r="XEY13" s="3"/>
+    </row>
+    <row r="14" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="XEV14" s="2"/>
+      <c r="XEW14" s="2"/>
+      <c r="XEX14" s="2"/>
+      <c r="XEY14" s="3"/>
+    </row>
     <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3277,6 +4401,7 @@
     <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
@@ -3299,7 +4424,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:XFD29"/>
+  <dimension ref="A1:XFD32"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
@@ -3314,720 +4439,1144 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
+      <c r="A1" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
       <c r="L1" s="2"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>119</v>
+      <c r="C2" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>142</v>
       </c>
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="I3" s="18" t="n">
+      <c r="A3" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K3" s="18" t="n">
+      <c r="K3" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="I4" s="18" t="n">
+      <c r="A4" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J4" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K4" s="18" t="n">
+      <c r="K4" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="I5" s="18" t="n">
+      <c r="A5" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I5" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J5" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K5" s="18" t="n">
+      <c r="K5" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="I6" s="18" t="n">
+      <c r="A6" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I6" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="J6" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K6" s="18" t="n">
+      <c r="K6" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="I7" s="18" t="n">
+      <c r="A7" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I7" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J7" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K7" s="18" t="n">
+      <c r="K7" s="19" t="n">
         <v>10</v>
       </c>
       <c r="L7" s="2"/>
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" s="18" t="s">
+      <c r="A8" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="E8" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="E8" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="I8" s="18" t="n">
+      <c r="F8" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I8" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J8" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="18" t="n">
+      <c r="K8" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L8" s="2"/>
       <c r="XFD8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F9" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="G9" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9" s="18" t="s">
+      <c r="H9" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="2"/>
+      <c r="XFD12" s="0"/>
+    </row>
+    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K14" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K16" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J17" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K17" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="F9" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="G9" s="18" t="s">
+      <c r="D18" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J19" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K19" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K20" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C21" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="H9" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="I9" s="18" t="n">
+      <c r="D21" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I21" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J21" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="18" t="n">
+      <c r="K21" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="L9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="L21" s="2"/>
+      <c r="XFD21" s="3"/>
+    </row>
+    <row r="22" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H22" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" s="18" t="s">
+      <c r="I22" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="2"/>
+      <c r="XFD22" s="3"/>
+    </row>
+    <row r="23" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="E10" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="G10" s="18" t="s">
+      <c r="D23" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" s="2"/>
+      <c r="XFD23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="C24" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="H10" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="I10" s="18" t="n">
+      <c r="D24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="I25" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="J25" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K10" s="18" t="n">
+      <c r="K25" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="L10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="B11" s="18" t="s">
+      <c r="L25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="G11" s="18" t="s">
+      <c r="E26" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J26" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K26" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="I28" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J28" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K28" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K29" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="H11" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="I11" s="18" t="n">
+      <c r="D30" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I30" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="I31" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J11" s="18" t="n">
+      <c r="J31" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K11" s="18" t="n">
+      <c r="K31" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
+      <c r="L31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F32" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="I13" s="18" t="n">
+      <c r="G32" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I32" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J13" s="18" t="n">
+      <c r="J32" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K13" s="18" t="n">
+      <c r="K32" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="L13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L16" s="2"/>
-    </row>
-    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J17" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K17" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L17" s="2"/>
-    </row>
-    <row r="18" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" s="2"/>
-      <c r="XFD18" s="3"/>
-    </row>
-    <row r="19" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="I19" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" s="2"/>
-      <c r="XFD19" s="3"/>
-    </row>
-    <row r="20" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="I20" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J20" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" s="2"/>
-      <c r="XFD20" s="3"/>
-    </row>
-    <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="27" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="L32" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
@@ -4050,7 +5599,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:XFD13"/>
+  <dimension ref="A1:XFD20"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
@@ -4064,37 +5613,37 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="A1" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>174</v>
+      <c r="C2" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>221</v>
       </c>
       <c r="XEV2" s="3"/>
       <c r="XEW2" s="3"/>
@@ -4107,236 +5656,491 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="E3" s="18" t="n">
+      <c r="A3" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E3" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="18" t="n">
+      <c r="G3" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="E4" s="18" t="n">
+      <c r="A4" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E4" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="G4" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="E5" s="18" t="n">
+      <c r="A5" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E5" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="E6" s="18" t="n">
+      <c r="A6" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E6" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="E7" s="18" t="n">
+      <c r="A7" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E7" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="19" t="n">
         <v>0.583</v>
       </c>
+      <c r="XEV7" s="0"/>
+      <c r="XEW7" s="0"/>
+      <c r="XEX7" s="0"/>
+      <c r="XEY7" s="0"/>
+      <c r="XEZ7" s="0"/>
+      <c r="XFA7" s="0"/>
+      <c r="XFB7" s="0"/>
+      <c r="XFC7" s="0"/>
+      <c r="XFD7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="E8" s="18" t="n">
+      <c r="A8" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E8" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="G8" s="19" t="n">
         <v>0.583</v>
       </c>
+      <c r="XEV8" s="0"/>
+      <c r="XEW8" s="0"/>
+      <c r="XEX8" s="0"/>
+      <c r="XEY8" s="0"/>
+      <c r="XEZ8" s="0"/>
+      <c r="XFA8" s="0"/>
+      <c r="XFB8" s="0"/>
+      <c r="XFC8" s="0"/>
+      <c r="XFD8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="E9" s="18" t="n">
+      <c r="A9" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E9" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="18" t="n">
+      <c r="G9" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="E10" s="18" t="n">
+      <c r="A10" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E10" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="18" t="n">
+      <c r="G10" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="E11" s="18" t="n">
+      <c r="A11" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E11" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="G11" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="E12" s="18" t="n">
+      <c r="A12" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E12" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>0.583</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.583</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="XEV15" s="0"/>
+      <c r="XEW15" s="0"/>
+      <c r="XEX15" s="0"/>
+      <c r="XEY15" s="0"/>
+      <c r="XEZ15" s="0"/>
+      <c r="XFA15" s="0"/>
+      <c r="XFB15" s="0"/>
+      <c r="XFC15" s="0"/>
+      <c r="XFD15" s="0"/>
+    </row>
+    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="XEV16" s="0"/>
+      <c r="XEW16" s="0"/>
+      <c r="XEX16" s="0"/>
+      <c r="XEY16" s="0"/>
+      <c r="XEZ16" s="0"/>
+      <c r="XFA16" s="0"/>
+      <c r="XFB16" s="0"/>
+      <c r="XFC16" s="0"/>
+      <c r="XFD16" s="0"/>
+    </row>
+    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="XEV17" s="0"/>
+      <c r="XEW17" s="0"/>
+      <c r="XEX17" s="0"/>
+      <c r="XEY17" s="0"/>
+      <c r="XEZ17" s="0"/>
+      <c r="XFA17" s="0"/>
+      <c r="XFB17" s="0"/>
+      <c r="XFC17" s="0"/>
+      <c r="XFD17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="XEV18" s="0"/>
+      <c r="XEW18" s="0"/>
+      <c r="XEX18" s="0"/>
+      <c r="XEY18" s="0"/>
+      <c r="XEZ18" s="0"/>
+      <c r="XFA18" s="0"/>
+      <c r="XFB18" s="0"/>
+      <c r="XFC18" s="0"/>
+      <c r="XFD18" s="0"/>
+    </row>
+    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="XEV19" s="0"/>
+      <c r="XEW19" s="0"/>
+      <c r="XEX19" s="0"/>
+      <c r="XEY19" s="0"/>
+      <c r="XEZ19" s="0"/>
+      <c r="XFA19" s="0"/>
+      <c r="XFB19" s="0"/>
+      <c r="XFC19" s="0"/>
+      <c r="XFD19" s="0"/>
+    </row>
+    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="XEV20" s="0"/>
+      <c r="XEW20" s="0"/>
+      <c r="XEX20" s="0"/>
+      <c r="XEY20" s="0"/>
+      <c r="XEZ20" s="0"/>
+      <c r="XFA20" s="0"/>
+      <c r="XFB20" s="0"/>
+      <c r="XFC20" s="0"/>
+      <c r="XFD20" s="0"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
@@ -4378,200 +6182,200 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
+      <c r="A1" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="L2" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="M2" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="N2" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="O2" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="P2" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q2" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="R2" s="21" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="L2" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="M2" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="N2" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="O2" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="P2" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q2" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="R2" s="20" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="D3" s="21" t="n">
+      <c r="C3" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="D3" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="21" t="n">
+      <c r="E3" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="22" t="b">
+      <c r="F3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G3" s="21" t="s">
-        <v>213</v>
-      </c>
-      <c r="H3" s="22" t="b">
+      <c r="G3" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="H3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I3" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="J3" s="22" t="b">
+      <c r="I3" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="J3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K3" s="21" t="s">
-        <v>215</v>
-      </c>
-      <c r="L3" s="22" t="b">
+      <c r="K3" s="22" t="s">
+        <v>278</v>
+      </c>
+      <c r="L3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M3" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="N3" s="21" t="n">
+      <c r="M3" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="N3" s="22" t="n">
         <v>6.5</v>
       </c>
-      <c r="O3" s="21" t="n">
+      <c r="O3" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="P3" s="21" t="n">
+      <c r="P3" s="22" t="n">
         <v>400</v>
       </c>
-      <c r="Q3" s="21" t="n">
+      <c r="Q3" s="22" t="n">
         <v>350</v>
       </c>
-      <c r="R3" s="21" t="n">
+      <c r="R3" s="22" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="D4" s="21" t="n">
+      <c r="A4" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="D4" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="21" t="n">
+      <c r="E4" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="F4" s="22" t="b">
+      <c r="F4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G4" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="H4" s="22" t="b">
+      <c r="G4" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I4" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="J4" s="22" t="b">
+      <c r="I4" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="J4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K4" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="L4" s="22" t="b">
+      <c r="K4" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="L4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M4" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="N4" s="21" t="n">
+      <c r="M4" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="N4" s="22" t="n">
         <v>6.5</v>
       </c>
-      <c r="O4" s="21" t="n">
+      <c r="O4" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="P4" s="21" t="n">
+      <c r="P4" s="22" t="n">
         <v>400</v>
       </c>
-      <c r="Q4" s="21" t="n">
+      <c r="Q4" s="22" t="n">
         <v>350</v>
       </c>
-      <c r="R4" s="21" t="n">
+      <c r="R4" s="22" t="n">
         <v>25</v>
       </c>
     </row>
@@ -4630,271 +6434,271 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="A1" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>228</v>
+      <c r="C2" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>291</v>
       </c>
       <c r="XFB2" s="3"/>
       <c r="XFC2" s="3"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="G3" s="22" t="b">
+      <c r="A3" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="G3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="I3" s="21" t="n">
+      <c r="H3" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="I3" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J3" s="21" t="n">
+      <c r="J3" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K3" s="21" t="n">
+      <c r="K3" s="22" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>235</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="G4" s="22" t="b">
+      <c r="A4" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="G4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="I4" s="21" t="n">
+      <c r="H4" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="I4" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" s="21" t="n">
+      <c r="J4" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K4" s="21" t="n">
+      <c r="K4" s="22" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="G5" s="22" t="b">
+      <c r="A5" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="G5" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H5" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="I5" s="21" t="n">
+      <c r="H5" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="I5" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="21" t="n">
+      <c r="J5" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="21" t="n">
+      <c r="K5" s="22" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="G6" s="22" t="b">
+      <c r="A6" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="G6" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H6" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="I6" s="21" t="n">
+      <c r="H6" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="I6" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J6" s="21" t="n">
+      <c r="J6" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="21" t="n">
+      <c r="K6" s="22" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="G7" s="22" t="b">
+      <c r="A7" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="G7" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H7" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="I7" s="21" t="n">
+      <c r="H7" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="I7" s="22" t="n">
         <v>0.8</v>
       </c>
-      <c r="J7" s="21" t="n">
+      <c r="J7" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="21" t="n">
+      <c r="K7" s="22" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
-        <v>245</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="G8" s="22" t="b">
+      <c r="A8" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="G8" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H8" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="I8" s="21" t="n">
+      <c r="H8" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="I8" s="22" t="n">
         <v>0.8</v>
       </c>
-      <c r="J8" s="21" t="n">
+      <c r="J8" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="21" t="n">
+      <c r="K8" s="22" t="n">
         <v>6</v>
       </c>
     </row>

--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -139,35 +139,7 @@
     <t xml:space="preserve">MISSION05</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Multi-Agent Test (Multi-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Hybrid</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">Multi-Agent Test (Multi-Hybrid)</t>
   </si>
   <si>
     <t xml:space="preserve">TEAM05</t>
@@ -455,69 +427,13 @@
     <t xml:space="preserve">SET09</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Multi-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Hybrid</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Tracking 2 (Multi)</t>
-    </r>
+    <t xml:space="preserve">Multi-Hybrid Tracking 2 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">SET10</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Multi-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Hybrid</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Tracking 3 (Multi)</t>
-    </r>
+    <t xml:space="preserve">Multi-Hybrid Tracking 3 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">SET11</t>
@@ -634,69 +550,13 @@
     <t xml:space="preserve">MULTICAMERA7</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tracking Head 1 Multi-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Hybrid</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (Single)</t>
-    </r>
+    <t xml:space="preserve">Tracking Head 1 Multi-Hybrid (Single)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTICAMERA8</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tracking Head 2 Multi-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Hybrid</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (Single)</t>
-    </r>
+    <t xml:space="preserve">Tracking Head 2 Multi-Hybrid (Single)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTICAMERA9</t>
@@ -780,107 +640,13 @@
     <t xml:space="preserve">MULTICAMERA22</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tracking Head 1 Multi-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Hybrid</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> 1 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Multi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">Tracking Head 1 Multi-Hybrid 1 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTICAMERA23</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tracking Head 2 Multi-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Hybrid</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> 1 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Multi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">Tracking Head 2 Multi-Hybrid 1 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTICAMERA24</t>
@@ -892,107 +658,13 @@
     <t xml:space="preserve">MULTICAMERA25</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tracking Head 1 Multi-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Hybrid</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> 2 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Multi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">Tracking Head 1 Multi-Hybrid 2 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTICAMERA26</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tracking Head 2 Multi-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Hybrid</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> 2 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Multi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">Tracking Head 2 Multi-Hybrid 2 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTICAMERA27</t>
@@ -1004,107 +676,13 @@
     <t xml:space="preserve">MULTICAMERA28</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tracking Head 1 Multi-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Hybrid</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> 3 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Multi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">Tracking Head 1 Multi-Hybrid 3 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTICAMERA29</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tracking Head 2 Multi-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Hybrid 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Multi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">Tracking Head 2 Multi-Hybrid 3 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">Resolution [pix]</t>
@@ -1155,35 +733,7 @@
     <t xml:space="preserve">MULTIWINDOW05</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tracking Window 2 Multi-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Hybrid</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (Single)</t>
-    </r>
+    <t xml:space="preserve">Tracking Window 2 Multi-Hybrid (Single)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTIWINDOW06</t>
@@ -1231,35 +781,7 @@
     <t xml:space="preserve">MULTIWINDOW13</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tracking Window 2 Multi-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Hybrid 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (Multi)</t>
-    </r>
+    <t xml:space="preserve">Tracking Window 2 Multi-Hybrid 1 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTIWINDOW14</t>
@@ -1271,35 +793,7 @@
     <t xml:space="preserve">MULTIWINDOW15</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tracking Window 2 Multi-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Hybrid 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (Multi)</t>
-    </r>
+    <t xml:space="preserve">Tracking Window 2 Multi-Hybrid 2 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTIWINDOW16</t>
@@ -1311,35 +805,7 @@
     <t xml:space="preserve">MULTIWINDOW17</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tracking Window 2 Multi-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Hybrid 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (Multi)</t>
-    </r>
+    <t xml:space="preserve">Tracking Window 2 Multi-Hybrid 3 (Multi)</t>
   </si>
   <si>
     <t xml:space="preserve">HARDWARE CATALOGS</t>
@@ -1529,13 +995,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="h:mm:ss"/>
     <numFmt numFmtId="166" formatCode="0"/>
-    <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1603,19 +1068,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1709,7 +1161,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1762,10 +1214,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1799,10 +1247,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2286,7 +1730,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="21" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="21" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.44"/>
@@ -2429,7 +1873,7 @@
       <c r="BD3" s="12"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="8" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -2509,7 +1953,7 @@
       <c r="BD4" s="12"/>
     </row>
     <row r="5" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13"/>
+      <c r="A5" s="8"/>
       <c r="B5" s="9" t="s">
         <v>25</v>
       </c>
@@ -2585,8 +2029,6 @@
       <c r="BB5" s="12"/>
       <c r="BC5" s="12"/>
       <c r="BD5" s="12"/>
-      <c r="XFC5" s="0"/>
-      <c r="XFD5" s="0"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8"/>
@@ -2856,7 +2298,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD16"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="2" width="29.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="40.25"/>
@@ -2870,92 +2312,92 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>310</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>312</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>314</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>291</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="C3" s="23" t="b">
+      <c r="C3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="E3" s="23" t="b">
+      <c r="E3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="21" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="23" t="b">
+      <c r="G3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="I3" s="22" t="n">
+      <c r="I3" s="21" t="n">
         <v>0.4</v>
       </c>
-      <c r="J3" s="22" t="n">
+      <c r="J3" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="22" t="n">
+      <c r="K3" s="21" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2995,7 +2437,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="33.54"/>
@@ -3008,12 +2450,12 @@
   </cols>
   <sheetData>
     <row r="1" s="7" customFormat="true" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
       <c r="E1" s="12"/>
       <c r="XFB1" s="3"/>
       <c r="XFC1" s="3"/>
@@ -3043,7 +2485,7 @@
       <c r="C3" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="14" t="s">
         <v>42</v>
       </c>
     </row>
@@ -3057,7 +2499,7 @@
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="14" t="s">
         <v>45</v>
       </c>
     </row>
@@ -3086,7 +2528,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:BM1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="38.38"/>
@@ -3097,15 +2539,15 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
@@ -3201,7 +2643,7 @@
       <c r="D3" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="15" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="9" t="s">
@@ -3282,7 +2724,7 @@
       <c r="D4" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="15" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="9" t="s">
@@ -3363,7 +2805,7 @@
       <c r="D5" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="15" t="n">
         <v>8</v>
       </c>
       <c r="F5" s="9" t="s">
@@ -3444,7 +2886,7 @@
       <c r="D6" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="15" t="n">
         <v>16</v>
       </c>
       <c r="F6" s="9" t="s">
@@ -3538,7 +2980,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD20"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="38.28"/>
@@ -3557,50 +2999,50 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
       <c r="XFC1" s="3"/>
       <c r="XFD1" s="3"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>73</v>
       </c>
       <c r="L2" s="12"/>
@@ -3615,390 +3057,390 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H3" s="19" t="n">
+      <c r="H3" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I3" s="19" t="n">
+      <c r="I3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="J3" s="18" t="n">
         <v>12000</v>
       </c>
       <c r="XFC3" s="3"/>
       <c r="XFD3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H4" s="19" t="n">
+      <c r="H4" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="I4" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="XFC5" s="0"/>
-      <c r="XFD5" s="0"/>
+      <c r="XFC5" s="3"/>
+      <c r="XFD5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="19" t="n">
+      <c r="H6" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="I6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J6" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H7" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I7" s="19" t="n">
+      <c r="I7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J7" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H8" s="19" t="n">
+      <c r="H8" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I8" s="19" t="n">
+      <c r="I8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J8" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H12" s="19" t="n">
+      <c r="H12" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I12" s="19" t="n">
+      <c r="I12" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="19" t="n">
+      <c r="J12" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H13" s="19" t="n">
+      <c r="H13" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I13" s="19" t="n">
+      <c r="I13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="19" t="n">
+      <c r="J13" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H14" s="19" t="n">
+      <c r="H14" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I14" s="19" t="n">
+      <c r="I14" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J14" s="19" t="n">
+      <c r="J14" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -4031,7 +3473,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD24"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="38.28"/>
@@ -4047,32 +3489,32 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>111</v>
       </c>
       <c r="H2" s="12"/>
@@ -4088,22 +3530,22 @@
       <c r="XFD2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="19" t="n">
+      <c r="D3" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="19" t="n">
+      <c r="E3" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G3" s="2"/>
@@ -4113,22 +3555,22 @@
       <c r="XEY3" s="3"/>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D4" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G4" s="2"/>
@@ -4138,22 +3580,22 @@
       <c r="XEY4" s="3"/>
     </row>
     <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G5" s="2"/>
@@ -4161,29 +3603,29 @@
       <c r="XEW5" s="2"/>
       <c r="XEX5" s="2"/>
       <c r="XEY5" s="3"/>
-      <c r="XEZ5" s="0"/>
-      <c r="XFA5" s="0"/>
-      <c r="XFB5" s="0"/>
-      <c r="XFC5" s="0"/>
-      <c r="XFD5" s="0"/>
+      <c r="XEZ5" s="3"/>
+      <c r="XFA5" s="3"/>
+      <c r="XFB5" s="3"/>
+      <c r="XFC5" s="3"/>
+      <c r="XFD5" s="3"/>
     </row>
     <row r="6" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G6" s="2"/>
@@ -4193,22 +3635,22 @@
       <c r="XEY6" s="3"/>
     </row>
     <row r="7" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G7" s="2"/>
@@ -4218,22 +3660,22 @@
       <c r="XEY7" s="3"/>
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G8" s="2"/>
@@ -4243,22 +3685,22 @@
       <c r="XEY8" s="3"/>
     </row>
     <row r="9" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G9" s="2"/>
@@ -4268,22 +3710,22 @@
       <c r="XEY9" s="3"/>
     </row>
     <row r="10" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G10" s="2"/>
@@ -4293,22 +3735,22 @@
       <c r="XEY10" s="3"/>
     </row>
     <row r="11" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G11" s="2"/>
@@ -4318,22 +3760,22 @@
       <c r="XEY11" s="3"/>
     </row>
     <row r="12" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G12" s="2"/>
@@ -4343,22 +3785,22 @@
       <c r="XEY12" s="3"/>
     </row>
     <row r="13" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G13" s="2"/>
@@ -4368,22 +3810,22 @@
       <c r="XEY13" s="3"/>
     </row>
     <row r="14" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G14" s="2"/>
@@ -4425,7 +3867,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD32"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="45.28"/>
@@ -4439,53 +3881,53 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
       <c r="L1" s="2"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="17" t="s">
         <v>142</v>
       </c>
       <c r="M2" s="12"/>
@@ -4493,1086 +3935,1085 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I3" s="19" t="n">
+      <c r="I3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="J3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K3" s="19" t="n">
+      <c r="K3" s="18" t="n">
         <v>3</v>
       </c>
       <c r="L3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="I4" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K4" s="19" t="n">
+      <c r="K4" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K5" s="19" t="n">
+      <c r="K5" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="I6" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J6" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K6" s="19" t="n">
+      <c r="K6" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I7" s="19" t="n">
+      <c r="I7" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J7" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K7" s="19" t="n">
+      <c r="K7" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L7" s="2"/>
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I8" s="19" t="n">
+      <c r="I8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="19" t="n">
+      <c r="K8" s="18" t="n">
         <v>3</v>
       </c>
       <c r="L8" s="2"/>
       <c r="XFD8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="19" t="n">
+      <c r="K9" s="18" t="n">
         <v>3</v>
       </c>
       <c r="L9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K10" s="19" t="n">
+      <c r="K10" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K11" s="19" t="n">
+      <c r="K11" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="H12" s="19" t="s">
+      <c r="H12" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I12" s="19" t="n">
+      <c r="I12" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="19" t="n">
+      <c r="J12" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K12" s="19" t="n">
+      <c r="K12" s="18" t="n">
         <v>3</v>
       </c>
       <c r="L12" s="2"/>
-      <c r="XFD12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="H13" s="19" t="s">
+      <c r="H13" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="I13" s="19" t="n">
+      <c r="I13" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J13" s="19" t="n">
+      <c r="J13" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K13" s="19" t="n">
+      <c r="K13" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="H14" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I14" s="19" t="n">
+      <c r="I14" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J14" s="19" t="n">
+      <c r="J14" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K14" s="19" t="n">
+      <c r="K14" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="H15" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I15" s="19" t="n">
+      <c r="I15" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J15" s="19" t="n">
+      <c r="J15" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K15" s="19" t="n">
+      <c r="K15" s="18" t="n">
         <v>3</v>
       </c>
       <c r="L15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="H16" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="I16" s="19" t="n">
+      <c r="I16" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J16" s="19" t="n">
+      <c r="J16" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K16" s="19" t="n">
+      <c r="K16" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="H17" s="19" t="s">
+      <c r="H17" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I17" s="19" t="n">
+      <c r="I17" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J17" s="19" t="n">
+      <c r="J17" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K17" s="19" t="n">
+      <c r="K17" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="H18" s="19" t="s">
+      <c r="H18" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I18" s="19" t="n">
+      <c r="I18" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J18" s="19" t="n">
+      <c r="J18" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K18" s="19" t="n">
+      <c r="K18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="L18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="H19" s="19" t="s">
+      <c r="H19" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="I19" s="19" t="n">
+      <c r="I19" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J19" s="19" t="n">
+      <c r="J19" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K19" s="19" t="n">
+      <c r="K19" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="H20" s="19" t="s">
+      <c r="H20" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I20" s="19" t="n">
+      <c r="I20" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J20" s="19" t="n">
+      <c r="J20" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K20" s="19" t="n">
+      <c r="K20" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L20" s="2"/>
     </row>
     <row r="21" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F21" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="H21" s="19" t="s">
+      <c r="H21" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I21" s="19" t="n">
+      <c r="I21" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="19" t="n">
+      <c r="J21" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K21" s="19" t="n">
+      <c r="K21" s="18" t="n">
         <v>3</v>
       </c>
       <c r="L21" s="2"/>
       <c r="XFD21" s="3"/>
     </row>
     <row r="22" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F22" s="19" t="s">
+      <c r="F22" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="H22" s="19" t="s">
+      <c r="H22" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I22" s="19" t="n">
+      <c r="I22" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J22" s="19" t="n">
+      <c r="J22" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K22" s="19" t="n">
+      <c r="K22" s="18" t="n">
         <v>3</v>
       </c>
       <c r="L22" s="2"/>
       <c r="XFD22" s="3"/>
     </row>
     <row r="23" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F23" s="19" t="s">
+      <c r="F23" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="H23" s="19" t="s">
+      <c r="H23" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I23" s="19" t="n">
+      <c r="I23" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="19" t="n">
+      <c r="J23" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K23" s="19" t="n">
+      <c r="K23" s="18" t="n">
         <v>3</v>
       </c>
       <c r="L23" s="2"/>
       <c r="XFD23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F24" s="19" t="s">
+      <c r="F24" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="H24" s="19" t="s">
+      <c r="H24" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I24" s="19" t="n">
+      <c r="I24" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J24" s="19" t="n">
+      <c r="J24" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K24" s="19" t="n">
+      <c r="K24" s="18" t="n">
         <v>3</v>
       </c>
       <c r="L24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F25" s="19" t="s">
+      <c r="F25" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G25" s="19" t="s">
+      <c r="G25" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="H25" s="19" t="s">
+      <c r="H25" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="I25" s="19" t="n">
+      <c r="I25" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="19" t="n">
+      <c r="J25" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K25" s="19" t="n">
+      <c r="K25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F26" s="19" t="s">
+      <c r="F26" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G26" s="19" t="s">
+      <c r="G26" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="H26" s="19" t="s">
+      <c r="H26" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I26" s="19" t="n">
+      <c r="I26" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J26" s="19" t="n">
+      <c r="J26" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K26" s="19" t="n">
+      <c r="K26" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="E27" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F27" s="19" t="s">
+      <c r="F27" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G27" s="19" t="s">
+      <c r="G27" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="H27" s="19" t="s">
+      <c r="H27" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I27" s="19" t="n">
+      <c r="I27" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J27" s="19" t="n">
+      <c r="J27" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K27" s="19" t="n">
+      <c r="K27" s="18" t="n">
         <v>3</v>
       </c>
       <c r="L27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F28" s="19" t="s">
+      <c r="F28" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G28" s="19" t="s">
+      <c r="G28" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="H28" s="19" t="s">
+      <c r="H28" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="I28" s="19" t="n">
+      <c r="I28" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J28" s="19" t="n">
+      <c r="J28" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K28" s="19" t="n">
+      <c r="K28" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F29" s="19" t="s">
+      <c r="F29" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G29" s="19" t="s">
+      <c r="G29" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="H29" s="19" t="s">
+      <c r="H29" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I29" s="19" t="n">
+      <c r="I29" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J29" s="19" t="n">
+      <c r="J29" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K29" s="19" t="n">
+      <c r="K29" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="E30" s="19" t="s">
+      <c r="E30" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F30" s="19" t="s">
+      <c r="F30" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G30" s="19" t="s">
+      <c r="G30" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="H30" s="19" t="s">
+      <c r="H30" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I30" s="19" t="n">
+      <c r="I30" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J30" s="19" t="n">
+      <c r="J30" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K30" s="19" t="n">
+      <c r="K30" s="18" t="n">
         <v>3</v>
       </c>
       <c r="L30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="E31" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F31" s="19" t="s">
+      <c r="F31" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G31" s="19" t="s">
+      <c r="G31" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="H31" s="19" t="s">
+      <c r="H31" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="I31" s="19" t="n">
+      <c r="I31" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J31" s="19" t="n">
+      <c r="J31" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K31" s="19" t="n">
+      <c r="K31" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F32" s="19" t="s">
+      <c r="F32" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G32" s="19" t="s">
+      <c r="G32" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="H32" s="19" t="s">
+      <c r="H32" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I32" s="19" t="n">
+      <c r="I32" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J32" s="19" t="n">
+      <c r="J32" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K32" s="19" t="n">
+      <c r="K32" s="18" t="n">
         <v>10</v>
       </c>
       <c r="L32" s="2"/>
@@ -5600,7 +5041,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD20"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="45.28"/>
@@ -5613,36 +5054,36 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>221</v>
       </c>
       <c r="XEV2" s="3"/>
@@ -5656,490 +5097,418 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E3" s="19" t="n">
+      <c r="E3" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="19" t="n">
+      <c r="G3" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="19" t="n">
+      <c r="G4" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV7" s="0"/>
-      <c r="XEW7" s="0"/>
-      <c r="XEX7" s="0"/>
-      <c r="XEY7" s="0"/>
-      <c r="XEZ7" s="0"/>
-      <c r="XFA7" s="0"/>
-      <c r="XFB7" s="0"/>
-      <c r="XFC7" s="0"/>
-      <c r="XFD7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV8" s="0"/>
-      <c r="XEW8" s="0"/>
-      <c r="XEX8" s="0"/>
-      <c r="XEY8" s="0"/>
-      <c r="XEZ8" s="0"/>
-      <c r="XFA8" s="0"/>
-      <c r="XFB8" s="0"/>
-      <c r="XFC8" s="0"/>
-      <c r="XFD8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>237</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G12" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>243</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="19" t="n">
+      <c r="G13" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G14" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="19" t="n">
+      <c r="G15" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV15" s="0"/>
-      <c r="XEW15" s="0"/>
-      <c r="XEX15" s="0"/>
-      <c r="XEY15" s="0"/>
-      <c r="XEZ15" s="0"/>
-      <c r="XFA15" s="0"/>
-      <c r="XFB15" s="0"/>
-      <c r="XFC15" s="0"/>
-      <c r="XFD15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="19" t="n">
+      <c r="G16" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV16" s="0"/>
-      <c r="XEW16" s="0"/>
-      <c r="XEX16" s="0"/>
-      <c r="XEY16" s="0"/>
-      <c r="XEZ16" s="0"/>
-      <c r="XFA16" s="0"/>
-      <c r="XFB16" s="0"/>
-      <c r="XFC16" s="0"/>
-      <c r="XFD16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="18" t="s">
         <v>252</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E17" s="19" t="n">
+      <c r="E17" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F17" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="19" t="n">
+      <c r="G17" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV17" s="0"/>
-      <c r="XEW17" s="0"/>
-      <c r="XEX17" s="0"/>
-      <c r="XEY17" s="0"/>
-      <c r="XEZ17" s="0"/>
-      <c r="XFA17" s="0"/>
-      <c r="XFB17" s="0"/>
-      <c r="XFC17" s="0"/>
-      <c r="XFD17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E18" s="19" t="n">
+      <c r="E18" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F18" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="19" t="n">
+      <c r="G18" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV18" s="0"/>
-      <c r="XEW18" s="0"/>
-      <c r="XEX18" s="0"/>
-      <c r="XEY18" s="0"/>
-      <c r="XEZ18" s="0"/>
-      <c r="XFA18" s="0"/>
-      <c r="XFB18" s="0"/>
-      <c r="XFC18" s="0"/>
-      <c r="XFD18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="18" t="s">
         <v>255</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E19" s="19" t="n">
+      <c r="E19" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="19" t="n">
+      <c r="G19" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV19" s="0"/>
-      <c r="XEW19" s="0"/>
-      <c r="XEX19" s="0"/>
-      <c r="XEY19" s="0"/>
-      <c r="XEZ19" s="0"/>
-      <c r="XFA19" s="0"/>
-      <c r="XFB19" s="0"/>
-      <c r="XFC19" s="0"/>
-      <c r="XFD19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E20" s="19" t="n">
+      <c r="E20" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F20" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="19" t="n">
+      <c r="G20" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="XEV20" s="0"/>
-      <c r="XEW20" s="0"/>
-      <c r="XEX20" s="0"/>
-      <c r="XEY20" s="0"/>
-      <c r="XEZ20" s="0"/>
-      <c r="XFA20" s="0"/>
-      <c r="XFB20" s="0"/>
-      <c r="XFC20" s="0"/>
-      <c r="XFD20" s="0"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6164,7 +5533,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:R1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="34.63"/>
@@ -6182,200 +5551,200 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="L2" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="N2" s="21" t="s">
+      <c r="N2" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="O2" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="P2" s="21" t="s">
+      <c r="P2" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="Q2" s="21" t="s">
+      <c r="Q2" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="R2" s="21" t="s">
+      <c r="R2" s="20" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="D3" s="22" t="n">
+      <c r="D3" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="22" t="n">
+      <c r="E3" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="23" t="b">
+      <c r="F3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="21" t="s">
         <v>276</v>
       </c>
-      <c r="H3" s="23" t="b">
+      <c r="H3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="J3" s="23" t="b">
+      <c r="J3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="L3" s="23" t="b">
+      <c r="L3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="M3" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="N3" s="22" t="n">
+      <c r="N3" s="21" t="n">
         <v>6.5</v>
       </c>
-      <c r="O3" s="22" t="n">
+      <c r="O3" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="P3" s="22" t="n">
+      <c r="P3" s="21" t="n">
         <v>400</v>
       </c>
-      <c r="Q3" s="22" t="n">
+      <c r="Q3" s="21" t="n">
         <v>350</v>
       </c>
-      <c r="R3" s="22" t="n">
+      <c r="R3" s="21" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>280</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="D4" s="22" t="n">
+      <c r="D4" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="22" t="n">
+      <c r="E4" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F4" s="23" t="b">
+      <c r="F4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="H4" s="23" t="b">
+      <c r="H4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="J4" s="23" t="b">
+      <c r="J4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K4" s="22" t="s">
+      <c r="K4" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="L4" s="23" t="b">
+      <c r="L4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M4" s="22" t="s">
+      <c r="M4" s="21" t="s">
         <v>284</v>
       </c>
-      <c r="N4" s="22" t="n">
+      <c r="N4" s="21" t="n">
         <v>6.5</v>
       </c>
-      <c r="O4" s="22" t="n">
+      <c r="O4" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="P4" s="22" t="n">
+      <c r="P4" s="21" t="n">
         <v>400</v>
       </c>
-      <c r="Q4" s="22" t="n">
+      <c r="Q4" s="21" t="n">
         <v>350</v>
       </c>
-      <c r="R4" s="22" t="n">
+      <c r="R4" s="21" t="n">
         <v>25</v>
       </c>
     </row>
@@ -6418,7 +5787,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD21"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="63.93"/>
@@ -6434,52 +5803,52 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>291</v>
       </c>
       <c r="XFB2" s="3"/>
@@ -6487,218 +5856,218 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>292</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="21" t="s">
         <v>296</v>
       </c>
-      <c r="G3" s="23" t="b">
+      <c r="G3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="I3" s="22" t="n">
+      <c r="I3" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J3" s="22" t="n">
+      <c r="J3" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K3" s="22" t="n">
+      <c r="K3" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>298</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="21" t="s">
         <v>296</v>
       </c>
-      <c r="G4" s="23" t="b">
+      <c r="G4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="I4" s="22" t="n">
+      <c r="I4" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" s="22" t="n">
+      <c r="J4" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K4" s="22" t="n">
+      <c r="K4" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="21" t="s">
         <v>302</v>
       </c>
-      <c r="G5" s="23" t="b">
+      <c r="G5" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="I5" s="22" t="n">
+      <c r="I5" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="22" t="n">
+      <c r="J5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="22" t="n">
+      <c r="K5" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>304</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>305</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="21" t="s">
         <v>302</v>
       </c>
-      <c r="G6" s="23" t="b">
+      <c r="G6" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="I6" s="22" t="n">
+      <c r="I6" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J6" s="22" t="n">
+      <c r="J6" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="22" t="n">
+      <c r="K6" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>306</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="21" t="s">
         <v>307</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="21" t="s">
         <v>296</v>
       </c>
-      <c r="G7" s="23" t="b">
+      <c r="G7" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="I7" s="22" t="n">
+      <c r="I7" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="J7" s="22" t="n">
+      <c r="J7" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="22" t="n">
+      <c r="K7" s="21" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="21" t="s">
         <v>307</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="21" t="s">
         <v>302</v>
       </c>
-      <c r="G8" s="23" t="b">
+      <c r="G8" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H8" s="22" t="s">
+      <c r="H8" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="I8" s="22" t="n">
+      <c r="I8" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="J8" s="22" t="n">
+      <c r="J8" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="22" t="n">
+      <c r="K8" s="21" t="n">
         <v>6</v>
       </c>
     </row>

--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -154,7 +154,7 @@
     <t xml:space="preserve">Operational Conditions O1</t>
   </si>
   <si>
-    <t xml:space="preserve">(lat=35.9865559, lon=-5.8930106, alt=8.54)</t>
+    <t xml:space="preserve">(lat=35.9865559, lon=-5.8930106, alt=0.0)</t>
   </si>
   <si>
     <t xml:space="preserve">(Vx=3.0, Vy=1.5, Vz=0.0)</t>

--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="321">
   <si>
     <t xml:space="preserve">GENERAL CONFIGURATION</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t xml:space="preserve">TRACKING01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(X=10.0, Y=-2.5, Z=0.0)</t>
   </si>
   <si>
     <t xml:space="preserve">AGENT02</t>
@@ -995,10 +998,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="h:mm:ss"/>
     <numFmt numFmtId="166" formatCode="0"/>
+    <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -1161,7 +1165,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1247,6 +1251,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1730,7 +1738,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="21" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="21" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.44"/>
@@ -2298,7 +2306,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD16"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="2" width="29.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="40.25"/>
@@ -2313,7 +2321,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -2334,62 +2342,62 @@
         <v>2</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="C3" s="21" t="b">
+        <v>317</v>
+      </c>
+      <c r="C3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>317</v>
-      </c>
-      <c r="E3" s="21" t="b">
+        <v>318</v>
+      </c>
+      <c r="E3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>318</v>
-      </c>
-      <c r="G3" s="21" t="b">
+        <v>319</v>
+      </c>
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I3" s="21" t="n">
         <v>0.4</v>
@@ -2437,7 +2445,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="33.54"/>
@@ -2528,7 +2536,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:BM1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="38.38"/>
@@ -2980,7 +2988,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD20"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="38.28"/>
@@ -3107,7 +3115,7 @@
         <v>77</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="G4" s="18" t="s">
         <v>78</v>
@@ -3124,16 +3132,16 @@
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>27</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E5" s="18" t="s">
         <v>77</v>
@@ -3158,16 +3166,16 @@
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>31</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6" s="18" t="s">
         <v>77</v>
@@ -3190,22 +3198,22 @@
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>31</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>77</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G7" s="18" t="s">
         <v>78</v>
@@ -3222,22 +3230,22 @@
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>31</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>77</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G8" s="18" t="s">
         <v>78</v>
@@ -3254,16 +3262,16 @@
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>34</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>77</v>
@@ -3286,22 +3294,22 @@
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E10" s="18" t="s">
         <v>77</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G10" s="18" t="s">
         <v>78</v>
@@ -3318,22 +3326,22 @@
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E11" s="18" t="s">
         <v>77</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G11" s="18" t="s">
         <v>78</v>
@@ -3350,16 +3358,16 @@
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>37</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E12" s="18" t="s">
         <v>77</v>
@@ -3382,22 +3390,22 @@
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>37</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E13" s="18" t="s">
         <v>77</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G13" s="18" t="s">
         <v>78</v>
@@ -3414,22 +3422,22 @@
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C14" s="18" t="s">
         <v>37</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E14" s="18" t="s">
         <v>77</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G14" s="18" t="s">
         <v>78</v>
@@ -3473,7 +3481,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD24"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="38.28"/>
@@ -3506,16 +3514,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
@@ -3534,10 +3542,10 @@
         <v>76</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D3" s="18" t="n">
         <v>0.2</v>
@@ -3559,10 +3567,10 @@
         <v>81</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>0.2</v>
@@ -3581,13 +3589,13 @@
     </row>
     <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D5" s="18" t="n">
         <v>0.2</v>
@@ -3611,13 +3619,13 @@
     </row>
     <row r="6" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D6" s="18" t="n">
         <v>0.2</v>
@@ -3636,13 +3644,13 @@
     </row>
     <row r="7" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D7" s="18" t="n">
         <v>0.2</v>
@@ -3661,13 +3669,13 @@
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D8" s="18" t="n">
         <v>0.2</v>
@@ -3686,13 +3694,13 @@
     </row>
     <row r="9" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D9" s="18" t="n">
         <v>0.2</v>
@@ -3711,13 +3719,13 @@
     </row>
     <row r="10" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D10" s="18" t="n">
         <v>0.2</v>
@@ -3736,13 +3744,13 @@
     </row>
     <row r="11" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D11" s="18" t="n">
         <v>0.2</v>
@@ -3761,13 +3769,13 @@
     </row>
     <row r="12" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D12" s="18" t="n">
         <v>0.2</v>
@@ -3786,13 +3794,13 @@
     </row>
     <row r="13" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D13" s="18" t="n">
         <v>0.2</v>
@@ -3811,13 +3819,13 @@
     </row>
     <row r="14" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D14" s="18" t="n">
         <v>0.2</v>
@@ -3867,7 +3875,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD32"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="45.28"/>
@@ -3904,31 +3912,31 @@
         <v>2</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>70</v>
       </c>
       <c r="I2" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
@@ -3936,28 +3944,28 @@
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I3" s="18" t="n">
         <v>3</v>
@@ -3972,28 +3980,28 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I4" s="18" t="n">
         <v>8</v>
@@ -4008,28 +4016,28 @@
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>8</v>
@@ -4044,28 +4052,28 @@
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I6" s="18" t="n">
         <v>8</v>
@@ -4080,28 +4088,28 @@
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I7" s="18" t="n">
         <v>8</v>
@@ -4116,28 +4124,28 @@
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I8" s="18" t="n">
         <v>3</v>
@@ -4153,28 +4161,28 @@
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>169</v>
-      </c>
       <c r="E9" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>3</v>
@@ -4189,28 +4197,28 @@
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I10" s="18" t="n">
         <v>8</v>
@@ -4225,28 +4233,28 @@
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I11" s="18" t="n">
         <v>8</v>
@@ -4261,28 +4269,28 @@
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I12" s="18" t="n">
         <v>3</v>
@@ -4297,28 +4305,28 @@
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I13" s="18" t="n">
         <v>8</v>
@@ -4333,28 +4341,28 @@
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I14" s="18" t="n">
         <v>8</v>
@@ -4369,28 +4377,28 @@
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I15" s="18" t="n">
         <v>3</v>
@@ -4405,28 +4413,28 @@
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I16" s="18" t="n">
         <v>8</v>
@@ -4441,28 +4449,28 @@
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I17" s="18" t="n">
         <v>8</v>
@@ -4477,28 +4485,28 @@
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I18" s="18" t="n">
         <v>3</v>
@@ -4513,28 +4521,28 @@
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I19" s="18" t="n">
         <v>8</v>
@@ -4549,28 +4557,28 @@
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I20" s="18" t="n">
         <v>8</v>
@@ -4585,28 +4593,28 @@
     </row>
     <row r="21" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I21" s="18" t="n">
         <v>3</v>
@@ -4622,28 +4630,28 @@
     </row>
     <row r="22" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I22" s="18" t="n">
         <v>3</v>
@@ -4659,28 +4667,28 @@
     </row>
     <row r="23" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I23" s="18" t="n">
         <v>3</v>
@@ -4696,28 +4704,28 @@
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I24" s="18" t="n">
         <v>3</v>
@@ -4732,28 +4740,28 @@
     </row>
     <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I25" s="18" t="n">
         <v>8</v>
@@ -4768,28 +4776,28 @@
     </row>
     <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I26" s="18" t="n">
         <v>8</v>
@@ -4804,28 +4812,28 @@
     </row>
     <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I27" s="18" t="n">
         <v>3</v>
@@ -4840,28 +4848,28 @@
     </row>
     <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I28" s="18" t="n">
         <v>8</v>
@@ -4876,28 +4884,28 @@
     </row>
     <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I29" s="18" t="n">
         <v>8</v>
@@ -4912,28 +4920,28 @@
     </row>
     <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I30" s="18" t="n">
         <v>3</v>
@@ -4948,28 +4956,28 @@
     </row>
     <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I31" s="18" t="n">
         <v>8</v>
@@ -4984,28 +4992,28 @@
     </row>
     <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I32" s="18" t="n">
         <v>8</v>
@@ -5041,7 +5049,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD20"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="45.28"/>
@@ -5072,19 +5080,19 @@
         <v>2</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="XEV2" s="3"/>
       <c r="XEW2" s="3"/>
@@ -5098,16 +5106,16 @@
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E3" s="18" t="n">
         <v>0.167</v>
@@ -5121,16 +5129,16 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="18" t="s">
         <v>225</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>224</v>
       </c>
       <c r="E4" s="18" t="n">
         <v>0.167</v>
@@ -5144,16 +5152,16 @@
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>0.167</v>
@@ -5167,16 +5175,16 @@
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E6" s="18" t="n">
         <v>0.167</v>
@@ -5190,16 +5198,16 @@
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>0.167</v>
@@ -5213,16 +5221,16 @@
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E8" s="18" t="n">
         <v>0.167</v>
@@ -5236,16 +5244,16 @@
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>0.167</v>
@@ -5259,16 +5267,16 @@
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E10" s="18" t="n">
         <v>0.167</v>
@@ -5282,16 +5290,16 @@
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E11" s="18" t="n">
         <v>0.167</v>
@@ -5305,16 +5313,16 @@
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E12" s="18" t="n">
         <v>0.167</v>
@@ -5328,16 +5336,16 @@
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E13" s="18" t="n">
         <v>0.167</v>
@@ -5351,16 +5359,16 @@
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E14" s="18" t="n">
         <v>0.167</v>
@@ -5374,16 +5382,16 @@
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E15" s="18" t="n">
         <v>0.167</v>
@@ -5397,16 +5405,16 @@
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E16" s="18" t="n">
         <v>0.167</v>
@@ -5420,16 +5428,16 @@
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E17" s="18" t="n">
         <v>0.167</v>
@@ -5443,16 +5451,16 @@
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E18" s="18" t="n">
         <v>0.167</v>
@@ -5466,16 +5474,16 @@
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E19" s="18" t="n">
         <v>0.167</v>
@@ -5489,16 +5497,16 @@
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>0.167</v>
@@ -5533,7 +5541,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:R1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="34.63"/>
@@ -5552,7 +5560,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -5583,49 +5591,49 @@
         <v>46</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L2" s="20" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M2" s="20" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N2" s="20" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O2" s="20" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P2" s="20" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q2" s="20" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="R2" s="20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5636,7 +5644,7 @@
         <v>40</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D3" s="21" t="n">
         <v>8</v>
@@ -5644,33 +5652,33 @@
       <c r="E3" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="21" t="b">
+      <c r="F3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="H3" s="21" t="b">
+        <v>277</v>
+      </c>
+      <c r="H3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="J3" s="21" t="b">
+        <v>278</v>
+      </c>
+      <c r="J3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="L3" s="21" t="b">
+        <v>279</v>
+      </c>
+      <c r="L3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N3" s="21" t="n">
         <v>6.5</v>
@@ -5690,13 +5698,13 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D4" s="21" t="n">
         <v>8</v>
@@ -5704,33 +5712,33 @@
       <c r="E4" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F4" s="21" t="b">
+      <c r="F4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="H4" s="21" t="b">
+        <v>282</v>
+      </c>
+      <c r="H4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="J4" s="21" t="b">
+        <v>283</v>
+      </c>
+      <c r="J4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K4" s="21" t="s">
-        <v>283</v>
-      </c>
-      <c r="L4" s="21" t="b">
+        <v>284</v>
+      </c>
+      <c r="L4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="M4" s="21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N4" s="21" t="n">
         <v>6.5</v>
@@ -5787,7 +5795,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD21"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="63.93"/>
@@ -5804,7 +5812,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -5828,28 +5836,28 @@
         <v>46</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="XFB2" s="3"/>
       <c r="XFC2" s="3"/>
@@ -5857,29 +5865,29 @@
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="G3" s="21" t="b">
+        <v>297</v>
+      </c>
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I3" s="21" t="n">
         <v>0.5</v>
@@ -5893,29 +5901,29 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="G4" s="21" t="b">
+        <v>297</v>
+      </c>
+      <c r="G4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I4" s="21" t="n">
         <v>0.5</v>
@@ -5929,29 +5937,29 @@
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="G5" s="21" t="b">
+        <v>303</v>
+      </c>
+      <c r="G5" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I5" s="21" t="n">
         <v>0.5</v>
@@ -5965,29 +5973,29 @@
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="G6" s="21" t="b">
+        <v>303</v>
+      </c>
+      <c r="G6" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I6" s="21" t="n">
         <v>0.5</v>
@@ -6001,29 +6009,29 @@
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="G7" s="21" t="b">
+        <v>297</v>
+      </c>
+      <c r="G7" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I7" s="21" t="n">
         <v>0.8</v>
@@ -6037,29 +6045,29 @@
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>310</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="B8" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>307</v>
-      </c>
       <c r="E8" s="21" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="G8" s="21" t="b">
+        <v>303</v>
+      </c>
+      <c r="G8" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I8" s="21" t="n">
         <v>0.8</v>

--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -463,7 +463,7 @@
     <t xml:space="preserve">RefFocal [mm]</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA0</t>
+    <t xml:space="preserve">MULTICAMERA00</t>
   </si>
   <si>
     <t xml:space="preserve">Central Head Multi-Camera (Single)</t>
@@ -484,7 +484,7 @@
     <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=90.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA1</t>
+    <t xml:space="preserve">MULTICAMERA01</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 1 Multi-Camera (Single)</t>
@@ -502,7 +502,7 @@
     <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=0.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA2</t>
+    <t xml:space="preserve">MULTICAMERA02</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 2 Multi-Camera (Single)</t>
@@ -511,7 +511,7 @@
     <t xml:space="preserve">(X=0.0, Y=0.3, Z=-0.15)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA3</t>
+    <t xml:space="preserve">MULTICAMERA03</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 3 Multi-Camera (Single)</t>
@@ -523,7 +523,7 @@
     <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=180.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA4</t>
+    <t xml:space="preserve">MULTICAMERA04</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 4 Multi-Camera (Single)</t>
@@ -535,7 +535,7 @@
     <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=270.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA5</t>
+    <t xml:space="preserve">MULTICAMERA05</t>
   </si>
   <si>
     <t xml:space="preserve">Central Head Multi-Window (Single)</t>
@@ -544,25 +544,25 @@
     <t xml:space="preserve">CAM04</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA6</t>
+    <t xml:space="preserve">MULTICAMERA06</t>
   </si>
   <si>
     <t xml:space="preserve">Central Head Multi-Hybrid (Single)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA7</t>
+    <t xml:space="preserve">MULTICAMERA07</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 1 Multi-Hybrid (Single)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA8</t>
+    <t xml:space="preserve">MULTICAMERA08</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 2 Multi-Hybrid (Single)</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTICAMERA9</t>
+    <t xml:space="preserve">MULTICAMERA09</t>
   </si>
   <si>
     <t xml:space="preserve">Central Head Multi-Camera 1 (Multi)</t>
@@ -998,11 +998,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="h:mm:ss"/>
     <numFmt numFmtId="166" formatCode="0"/>
-    <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -1165,7 +1164,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1251,10 +1250,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1738,7 +1733,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="21" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="21" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.44"/>
@@ -2306,7 +2301,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD16"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="2" width="29.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="40.25"/>
@@ -2378,21 +2373,21 @@
       <c r="B3" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="C3" s="22" t="b">
+      <c r="C3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>318</v>
       </c>
-      <c r="E3" s="22" t="b">
+      <c r="E3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F3" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="G3" s="22" t="b">
+      <c r="G3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -2445,7 +2440,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="33.54"/>
@@ -2536,7 +2531,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:BM1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="38.38"/>
@@ -2988,7 +2983,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD20"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="38.28"/>
@@ -3481,7 +3476,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD24"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="38.28"/>
@@ -3875,7 +3870,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD32"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="45.28"/>
@@ -5049,7 +5044,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD20"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="45.28"/>
@@ -5541,7 +5536,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:R1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="34.63"/>
@@ -5652,28 +5647,28 @@
       <c r="E3" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="22" t="b">
+      <c r="F3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="G3" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="H3" s="22" t="b">
+      <c r="H3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I3" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="J3" s="22" t="b">
+      <c r="J3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K3" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="L3" s="22" t="b">
+      <c r="L3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5712,28 +5707,28 @@
       <c r="E4" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F4" s="22" t="b">
+      <c r="F4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="G4" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="H4" s="22" t="b">
+      <c r="H4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="J4" s="22" t="b">
+      <c r="J4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K4" s="21" t="s">
         <v>284</v>
       </c>
-      <c r="L4" s="22" t="b">
+      <c r="L4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5795,7 +5790,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD21"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="63.93"/>
@@ -5882,7 +5877,7 @@
       <c r="F3" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="G3" s="22" t="b">
+      <c r="G3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5918,7 +5913,7 @@
       <c r="F4" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="G4" s="22" t="b">
+      <c r="G4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5954,7 +5949,7 @@
       <c r="F5" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="G5" s="22" t="b">
+      <c r="G5" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5990,7 +5985,7 @@
       <c r="F6" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="G6" s="22" t="b">
+      <c r="G6" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -6026,7 +6021,7 @@
       <c r="F7" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="G7" s="22" t="b">
+      <c r="G7" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -6062,7 +6057,7 @@
       <c r="F8" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="G8" s="22" t="b">
+      <c r="G8" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>

--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -64,37 +64,37 @@
     <t xml:space="preserve">StartHour</t>
   </si>
   <si>
+    <t xml:space="preserve">MISSION00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-Agent Test (Multi-Camera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENVIRONMENT00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GROUP02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-150.0, 150.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(30.0, 150.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PX4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(13/12/2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(16:30:00)</t>
+  </si>
+  <si>
     <t xml:space="preserve">X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISSION00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single-Agent Test (Multi-Camera)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENVIRONMENT00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GROUP02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(-150.0, 150.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(30.0, 150.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PX4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(13/12/2024)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(16:30:00)</t>
   </si>
   <si>
     <t xml:space="preserve">MISSION01</t>
@@ -1102,18 +1102,18 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="2" tint="-0.75"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="2" tint="-0.75"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1240,7 +1240,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1252,7 +1252,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1260,7 +1260,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1845,38 +1845,36 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="J3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
@@ -1925,7 +1923,9 @@
       <c r="BD3" s="12"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13"/>
+      <c r="A4" s="13" t="s">
+        <v>21</v>
+      </c>
       <c r="B4" s="9" t="s">
         <v>22</v>
       </c>
@@ -1933,28 +1933,28 @@
         <v>23</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>15</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="J4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="K4" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
@@ -2003,7 +2003,7 @@
       <c r="BD4" s="12"/>
     </row>
     <row r="5" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13"/>
+      <c r="A5" s="8"/>
       <c r="B5" s="9" t="s">
         <v>25</v>
       </c>
@@ -2011,28 +2011,28 @@
         <v>26</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>14</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>15</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>27</v>
       </c>
       <c r="G5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="I5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="J5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="K5" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L5" s="12"/>
       <c r="M5" s="12"/>
@@ -2081,7 +2081,7 @@
       <c r="BD5" s="12"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13"/>
+      <c r="A6" s="8"/>
       <c r="B6" s="9" t="s">
         <v>28</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>29</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>30</v>
@@ -2098,19 +2098,19 @@
         <v>31</v>
       </c>
       <c r="G6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="I6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="J6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="K6" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
@@ -2159,7 +2159,7 @@
       <c r="BD6" s="12"/>
     </row>
     <row r="7" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13"/>
+      <c r="A7" s="8"/>
       <c r="B7" s="9" t="s">
         <v>32</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>33</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>30</v>
@@ -2176,19 +2176,19 @@
         <v>34</v>
       </c>
       <c r="G7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="I7" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="J7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="K7" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="12"/>
@@ -2237,7 +2237,7 @@
       <c r="BD7" s="12"/>
     </row>
     <row r="8" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13"/>
+      <c r="A8" s="8"/>
       <c r="B8" s="9" t="s">
         <v>35</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>36</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>30</v>
@@ -2254,19 +2254,19 @@
         <v>37</v>
       </c>
       <c r="G8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="I8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="J8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="K8" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="12"/>
@@ -2527,7 +2527,7 @@
     </row>
     <row r="3" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>40</v>
@@ -2850,7 +2850,7 @@
         <v>61</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>53</v>
@@ -3114,7 +3114,7 @@
         <v>75</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>76</v>

--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -1102,18 +1102,18 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="2" tint="-0.75"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1240,7 +1240,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1252,7 +1252,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1260,7 +1260,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1923,7 +1923,7 @@
       <c r="BD3" s="12"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="8" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -2003,7 +2003,7 @@
       <c r="BD4" s="12"/>
     </row>
     <row r="5" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="9" t="s">
         <v>25</v>
       </c>
@@ -2081,7 +2081,7 @@
       <c r="BD5" s="12"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8"/>
+      <c r="A6" s="13"/>
       <c r="B6" s="9" t="s">
         <v>28</v>
       </c>
@@ -2159,7 +2159,7 @@
       <c r="BD6" s="12"/>
     </row>
     <row r="7" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="9" t="s">
         <v>32</v>
       </c>
@@ -2237,7 +2237,7 @@
       <c r="BD7" s="12"/>
     </row>
     <row r="8" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="9" t="s">
         <v>35</v>
       </c>

--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="341">
   <si>
     <t xml:space="preserve">GENERAL CONFIGURATION</t>
   </si>
@@ -463,7 +463,10 @@
     <t xml:space="preserve">RefFocal [mm]</t>
   </si>
   <si>
-    <t xml:space="preserve">StreamURL</t>
+    <t xml:space="preserve">SrcStreamURL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DstStreamURL</t>
   </si>
   <si>
     <t xml:space="preserve">MULTICAMERA00</t>
@@ -490,6 +493,9 @@
     <t xml:space="preserve">udp://127.0.0.1:5000</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:6000</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA01</t>
   </si>
   <si>
@@ -511,6 +517,9 @@
     <t xml:space="preserve">udp://127.0.0.1:5001</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:6001</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA02</t>
   </si>
   <si>
@@ -523,6 +532,9 @@
     <t xml:space="preserve">udp://127.0.0.1:5002</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:6002</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA03</t>
   </si>
   <si>
@@ -538,6 +550,9 @@
     <t xml:space="preserve">udp://127.0.0.1:5003</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:6003</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA04</t>
   </si>
   <si>
@@ -553,6 +568,9 @@
     <t xml:space="preserve">udp://127.0.0.1:5004</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:6004</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA05</t>
   </si>
   <si>
@@ -619,6 +637,9 @@
     <t xml:space="preserve">udp://127.0.0.1:5005</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:6005</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA15</t>
   </si>
   <si>
@@ -628,6 +649,9 @@
     <t xml:space="preserve">udp://127.0.0.1:5006</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:6006</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA16</t>
   </si>
   <si>
@@ -637,6 +661,9 @@
     <t xml:space="preserve">udp://127.0.0.1:5007</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:6007</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA17</t>
   </si>
   <si>
@@ -646,6 +673,9 @@
     <t xml:space="preserve">udp://127.0.0.1:5008</t>
   </si>
   <si>
+    <t xml:space="preserve">udp://127.0.0.1:6008</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA18</t>
   </si>
   <si>
@@ -706,27 +736,18 @@
     <t xml:space="preserve">Central Head Multi-Hybrid 3 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">udp://127.0.0.1:5009</t>
-  </si>
-  <si>
     <t xml:space="preserve">MULTICAMERA28</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 1 Multi-Hybrid 3 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">udp://127.0.0.1:5010</t>
-  </si>
-  <si>
     <t xml:space="preserve">MULTICAMERA29</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 2 Multi-Hybrid 3 (Multi)</t>
   </si>
   <si>
-    <t xml:space="preserve">udp://127.0.0.1:5011</t>
-  </si>
-  <si>
     <t xml:space="preserve">Resolution [pix]</t>
   </si>
   <si>
@@ -992,6 +1013,9 @@
   </si>
   <si>
     <t xml:space="preserve">Operational Conditions O1 (ultra-high-resolution camera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3840x2160)</t>
   </si>
   <si>
     <t xml:space="preserve">CAM05</t>
@@ -1039,7 +1063,7 @@
     <numFmt numFmtId="165" formatCode="h:mm:ss"/>
     <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1100,13 +1124,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1207,7 +1224,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1240,7 +1257,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1252,16 +1269,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2003,7 +2016,7 @@
       <c r="BD4" s="12"/>
     </row>
     <row r="5" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13"/>
+      <c r="A5" s="8"/>
       <c r="B5" s="9" t="s">
         <v>25</v>
       </c>
@@ -2081,7 +2094,7 @@
       <c r="BD5" s="12"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13"/>
+      <c r="A6" s="8"/>
       <c r="B6" s="9" t="s">
         <v>28</v>
       </c>
@@ -2159,7 +2172,7 @@
       <c r="BD6" s="12"/>
     </row>
     <row r="7" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13"/>
+      <c r="A7" s="8"/>
       <c r="B7" s="9" t="s">
         <v>32</v>
       </c>
@@ -2237,7 +2250,7 @@
       <c r="BD7" s="12"/>
     </row>
     <row r="8" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13"/>
+      <c r="A8" s="8"/>
       <c r="B8" s="9" t="s">
         <v>35</v>
       </c>
@@ -2362,92 +2375,92 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="A1" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="G2" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>328</v>
-      </c>
-      <c r="I2" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="J2" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="K2" s="21" t="s">
-        <v>305</v>
+      <c r="C2" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>312</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>329</v>
-      </c>
-      <c r="C3" s="22" t="b">
+      <c r="A3" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="C3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D3" s="22" t="s">
-        <v>330</v>
-      </c>
-      <c r="E3" s="22" t="b">
+      <c r="D3" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="E3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F3" s="22" t="s">
-        <v>331</v>
-      </c>
-      <c r="G3" s="22" t="b">
+      <c r="F3" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="G3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="I3" s="22" t="n">
+      <c r="H3" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="I3" s="21" t="n">
         <v>0.4</v>
       </c>
-      <c r="J3" s="22" t="n">
+      <c r="J3" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="22" t="n">
+      <c r="K3" s="21" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2500,12 +2513,12 @@
   </cols>
   <sheetData>
     <row r="1" s="7" customFormat="true" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
       <c r="E1" s="12"/>
       <c r="XFB1" s="3"/>
       <c r="XFC1" s="3"/>
@@ -2535,7 +2548,7 @@
       <c r="C3" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="14" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2549,7 +2562,7 @@
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="14" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2589,15 +2602,15 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
@@ -2693,7 +2706,7 @@
       <c r="D3" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="15" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="9" t="s">
@@ -2774,7 +2787,7 @@
       <c r="D4" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="15" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="9" t="s">
@@ -2855,7 +2868,7 @@
       <c r="D5" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="15" t="n">
         <v>8</v>
       </c>
       <c r="F5" s="9" t="s">
@@ -2936,7 +2949,7 @@
       <c r="D6" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="15" t="n">
         <v>16</v>
       </c>
       <c r="F6" s="9" t="s">
@@ -3049,50 +3062,50 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
       <c r="XFC1" s="3"/>
       <c r="XFD1" s="3"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>73</v>
       </c>
       <c r="L2" s="12"/>
@@ -3107,390 +3120,390 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H3" s="19" t="n">
+      <c r="H3" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I3" s="19" t="n">
+      <c r="I3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="J3" s="18" t="n">
         <v>12000</v>
       </c>
       <c r="XFC3" s="3"/>
       <c r="XFD3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H4" s="19" t="n">
+      <c r="H4" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="I4" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="18" t="n">
         <v>12000</v>
       </c>
       <c r="XFC5" s="3"/>
       <c r="XFD5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="19" t="n">
+      <c r="H6" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="I6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J6" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H7" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I7" s="19" t="n">
+      <c r="I7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J7" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H8" s="19" t="n">
+      <c r="H8" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I8" s="19" t="n">
+      <c r="I8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J8" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H12" s="19" t="n">
+      <c r="H12" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I12" s="19" t="n">
+      <c r="I12" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="19" t="n">
+      <c r="J12" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H13" s="19" t="n">
+      <c r="H13" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I13" s="19" t="n">
+      <c r="I13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="19" t="n">
+      <c r="J13" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H14" s="19" t="n">
+      <c r="H14" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I14" s="19" t="n">
+      <c r="I14" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J14" s="19" t="n">
+      <c r="J14" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -3539,32 +3552,32 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>112</v>
       </c>
       <c r="H2" s="12"/>
@@ -3580,22 +3593,22 @@
       <c r="XFD2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="19" t="n">
+      <c r="D3" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="19" t="n">
+      <c r="E3" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G3" s="2"/>
@@ -3605,22 +3618,22 @@
       <c r="XEY3" s="3"/>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D4" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G4" s="2"/>
@@ -3630,22 +3643,22 @@
       <c r="XEY4" s="3"/>
     </row>
     <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G5" s="2"/>
@@ -3660,22 +3673,22 @@
       <c r="XFD5" s="3"/>
     </row>
     <row r="6" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G6" s="2"/>
@@ -3685,22 +3698,22 @@
       <c r="XEY6" s="3"/>
     </row>
     <row r="7" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G7" s="2"/>
@@ -3710,22 +3723,22 @@
       <c r="XEY7" s="3"/>
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G8" s="2"/>
@@ -3735,22 +3748,22 @@
       <c r="XEY8" s="3"/>
     </row>
     <row r="9" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G9" s="2"/>
@@ -3760,22 +3773,22 @@
       <c r="XEY9" s="3"/>
     </row>
     <row r="10" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G10" s="2"/>
@@ -3785,22 +3798,22 @@
       <c r="XEY10" s="3"/>
     </row>
     <row r="11" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G11" s="2"/>
@@ -3810,22 +3823,22 @@
       <c r="XEY11" s="3"/>
     </row>
     <row r="12" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G12" s="2"/>
@@ -3835,22 +3848,22 @@
       <c r="XEY12" s="3"/>
     </row>
     <row r="13" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G13" s="2"/>
@@ -3860,22 +3873,22 @@
       <c r="XEY13" s="3"/>
     </row>
     <row r="14" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G14" s="2"/>
@@ -3916,7 +3929,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:XFD32"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
@@ -3924,1211 +3937,1299 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="12" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="36.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="2" width="27.34"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="13" style="12" width="11"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="15" style="2" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="3" width="10.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="9" style="2" width="27.34"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="14" style="12" width="11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16" style="2" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="M2" s="12"/>
+      <c r="M2" s="17" t="s">
+        <v>145</v>
+      </c>
       <c r="N2" s="12"/>
-      <c r="XFD2" s="3"/>
+      <c r="O2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="B3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="B3" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="E3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="I3" s="19" t="n">
+      <c r="H3" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="J3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K3" s="19" t="n">
+      <c r="K3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L3" s="19" t="s">
+      <c r="L3" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K4" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="M4" s="18" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="H5" s="18" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="I5" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="M5" s="18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="M6" s="18" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="M7" s="18" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="M8" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E4" s="19" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="M9" s="18" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="M10" s="18" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="M11" s="18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="D12" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G4" s="19" t="s">
+      <c r="E12" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="M12" s="18" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="E13" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F13" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="G13" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="I13" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J13" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K4" s="19" t="n">
+      <c r="K13" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L4" s="19" t="s">
+      <c r="L13" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="M13" s="18" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="M14" s="18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="M15" s="18" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G16" s="18" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="H16" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="I16" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K16" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L16" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="M16" s="18" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="M17" s="18" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="M18" s="18" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J19" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K19" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="M19" s="18" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I20" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K20" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="M20" s="18" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="21" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I21" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="M21" s="18" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G5" s="19" t="s">
+      <c r="M22" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="H5" s="19" t="s">
+    </row>
+    <row r="23" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G23" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="H23" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="M23" s="18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="H24" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="M24" s="18" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="I25" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J25" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K5" s="19" t="n">
+      <c r="K25" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L5" s="19" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="B6" s="19" t="s">
+      <c r="L25" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="M25" s="18" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G26" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G6" s="19" t="s">
+      <c r="H26" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I26" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J26" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K26" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="M26" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="I6" s="19" t="n">
+    </row>
+    <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="H27" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I27" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="M27" s="18" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="I28" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J28" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K6" s="19" t="n">
+      <c r="K28" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L6" s="19" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="I7" s="19" t="n">
+      <c r="L28" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="M28" s="18" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="H29" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I29" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J29" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K7" s="19" t="n">
+      <c r="K29" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L7" s="19" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F8" s="19" t="s">
+      <c r="L29" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="M29" s="18" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="E30" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="F30" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="G30" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="I8" s="19" t="n">
+      <c r="H30" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I30" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J30" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="19" t="n">
+      <c r="K30" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="L30" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="M30" s="18" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="H31" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="I31" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J31" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K31" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L31" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="M31" s="18" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="H32" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="XFD8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="I9" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" s="19" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="I10" s="19" t="n">
+      <c r="I32" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J32" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K10" s="19" t="n">
+      <c r="K32" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L10" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="I11" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J11" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K11" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" s="19" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="I12" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" s="19" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G13" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J13" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K13" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L13" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="I14" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J14" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K14" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L14" s="19" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="H15" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" s="19" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J16" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K16" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L16" s="19" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="H17" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J17" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K17" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L17" s="19" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="H18" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="I18" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" s="19" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G19" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="H19" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="I19" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J19" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K19" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L19" s="19" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="H20" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="I20" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J20" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K20" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L20" s="19" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="21" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="G21" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="I21" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L21" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="XFD21" s="3"/>
-    </row>
-    <row r="22" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="I22" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="XFD22" s="3"/>
-    </row>
-    <row r="23" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="H23" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="I23" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="XFD23" s="3"/>
-    </row>
-    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F24" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="G24" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="H24" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="I24" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L24" s="19" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
+      <c r="L32" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="M32" s="18" t="s">
         <v>214</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F25" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="H25" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="I25" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J25" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K25" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L25" s="19" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D26" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F26" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G26" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="H26" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="I26" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K26" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L26" s="19" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="H27" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="I27" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K27" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" s="19" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="D28" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="H28" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="I28" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J28" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K28" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L28" s="19" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="H29" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="I29" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J29" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K29" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L29" s="19" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="H30" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="I30" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K30" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L30" s="19" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="H31" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="I31" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J31" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K31" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L31" s="19" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="H32" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="I32" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J32" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K32" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L32" s="19" t="s">
-        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -5153,7 +5254,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:XFD20"/>
+  <dimension ref="A1:XFD32"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
@@ -5162,42 +5263,47 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="12" width="27.34"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16375" min="8" style="2" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="27.34"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16375" min="9" style="2" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16376" style="3" width="10.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>235</v>
+      <c r="D2" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>145</v>
       </c>
       <c r="XEV2" s="3"/>
       <c r="XEW2" s="3"/>
@@ -5210,418 +5316,508 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="A3" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E3" s="19" t="n">
+      <c r="D3" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E3" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="19" t="n">
+      <c r="G3" s="18" t="n">
         <v>0.583</v>
       </c>
+      <c r="H3" s="18" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="C4" s="19" t="s">
+      <c r="A4" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C4" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E4" s="19" t="n">
+      <c r="D4" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E4" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="19" t="n">
+      <c r="G4" s="18" t="n">
         <v>0.583</v>
       </c>
+      <c r="H4" s="18" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="C5" s="19" t="s">
+      <c r="A5" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="C5" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E5" s="19" t="n">
+      <c r="D5" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E5" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="18" t="n">
         <v>0.583</v>
       </c>
+      <c r="H5" s="18" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="C6" s="19" t="s">
+      <c r="A6" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="C6" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E6" s="19" t="n">
+      <c r="D6" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E6" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="18" t="n">
         <v>0.583</v>
       </c>
+      <c r="H6" s="18" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="C7" s="19" t="s">
+      <c r="E7" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="C8" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D7" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E7" s="19" t="n">
+      <c r="D8" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E8" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F8" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G8" s="18" t="n">
         <v>0.583</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E8" s="19" t="n">
+      <c r="H8" s="18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E9" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G9" s="18" t="n">
         <v>0.583</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="C9" s="19" t="s">
+      <c r="H9" s="18" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="C10" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D9" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E9" s="19" t="n">
+      <c r="D10" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E10" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G10" s="18" t="n">
         <v>0.583</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E10" s="19" t="n">
+      <c r="H10" s="18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E11" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F11" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G11" s="18" t="n">
         <v>0.583</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="C11" s="19" t="s">
+      <c r="H11" s="18" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="C12" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="D11" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E11" s="19" t="n">
+      <c r="D12" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E12" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F12" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G12" s="18" t="n">
         <v>0.583</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E12" s="19" t="n">
+      <c r="H12" s="18" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E13" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F13" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G13" s="18" t="n">
         <v>0.583</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="C13" s="19" t="s">
+      <c r="H13" s="18" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E13" s="19" t="n">
+      <c r="D14" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E14" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F14" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="19" t="n">
+      <c r="G14" s="18" t="n">
         <v>0.583</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E14" s="19" t="n">
+      <c r="H14" s="18" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E15" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F15" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G15" s="18" t="n">
         <v>0.583</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="C15" s="19" t="s">
+      <c r="H15" s="18" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="C16" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E15" s="19" t="n">
+      <c r="D16" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E16" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F16" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="19" t="n">
+      <c r="G16" s="18" t="n">
         <v>0.583</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E16" s="19" t="n">
+      <c r="H16" s="18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E17" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F17" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="19" t="n">
+      <c r="G17" s="18" t="n">
         <v>0.583</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="C17" s="19" t="s">
+      <c r="H17" s="18" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C18" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="D17" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E17" s="19" t="n">
+      <c r="D18" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E18" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F18" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="19" t="n">
+      <c r="G18" s="18" t="n">
         <v>0.583</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E18" s="19" t="n">
+      <c r="H18" s="18" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E19" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F19" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="19" t="n">
+      <c r="G19" s="18" t="n">
         <v>0.583</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="C19" s="19" t="s">
+      <c r="H19" s="18" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="C20" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E19" s="19" t="n">
+      <c r="D20" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E20" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F20" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="19" t="n">
+      <c r="G20" s="18" t="n">
         <v>0.583</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E20" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F20" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="19" t="n">
-        <v>0.583</v>
-      </c>
+      <c r="H20" s="18" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H21" s="12"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H22" s="12"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H23" s="12"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H25" s="12"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H26" s="12"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H27" s="12"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H28" s="12"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H29" s="12"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H30" s="12"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H31" s="12"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H32" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5664,200 +5860,200 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
+      <c r="A1" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>274</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="G2" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="I2" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="J2" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="K2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="N2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="P2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="Q2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="R2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>288</v>
       </c>
+      <c r="L2" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="M2" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="N2" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="O2" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="P2" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q2" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="R2" s="20" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="D3" s="22" t="n">
+      <c r="C3" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="D3" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="22" t="n">
+      <c r="E3" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="22" t="b">
+      <c r="F3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G3" s="22" t="s">
-        <v>290</v>
-      </c>
-      <c r="H3" s="22" t="b">
+      <c r="G3" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="H3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I3" s="22" t="s">
-        <v>291</v>
-      </c>
-      <c r="J3" s="22" t="b">
+      <c r="I3" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="J3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K3" s="22" t="s">
-        <v>292</v>
-      </c>
-      <c r="L3" s="22" t="b">
+      <c r="K3" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="L3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M3" s="22" t="s">
-        <v>293</v>
-      </c>
-      <c r="N3" s="22" t="n">
+      <c r="M3" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="N3" s="21" t="n">
         <v>6.5</v>
       </c>
-      <c r="O3" s="22" t="n">
+      <c r="O3" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="P3" s="22" t="n">
+      <c r="P3" s="21" t="n">
         <v>400</v>
       </c>
-      <c r="Q3" s="22" t="n">
+      <c r="Q3" s="21" t="n">
         <v>350</v>
       </c>
-      <c r="R3" s="22" t="n">
+      <c r="R3" s="21" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
-        <v>294</v>
-      </c>
-      <c r="B4" s="22" t="s">
+      <c r="A4" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="B4" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="D4" s="22" t="n">
+      <c r="C4" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="D4" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="22" t="n">
+      <c r="E4" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F4" s="22" t="b">
+      <c r="F4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G4" s="22" t="s">
-        <v>295</v>
-      </c>
-      <c r="H4" s="22" t="b">
+      <c r="G4" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="H4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I4" s="22" t="s">
-        <v>296</v>
-      </c>
-      <c r="J4" s="22" t="b">
+      <c r="I4" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="J4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K4" s="22" t="s">
-        <v>297</v>
-      </c>
-      <c r="L4" s="22" t="b">
+      <c r="K4" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="L4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M4" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="N4" s="22" t="n">
+      <c r="M4" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="N4" s="21" t="n">
         <v>6.5</v>
       </c>
-      <c r="O4" s="22" t="n">
+      <c r="O4" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="P4" s="22" t="n">
+      <c r="P4" s="21" t="n">
         <v>400</v>
       </c>
-      <c r="Q4" s="22" t="n">
+      <c r="Q4" s="21" t="n">
         <v>350</v>
       </c>
-      <c r="R4" s="22" t="n">
+      <c r="R4" s="21" t="n">
         <v>25</v>
       </c>
     </row>
@@ -5916,271 +6112,271 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="A1" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>299</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>300</v>
-      </c>
-      <c r="G2" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="I2" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="J2" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="K2" s="21" t="s">
-        <v>305</v>
+      <c r="D2" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>312</v>
       </c>
       <c r="XFB2" s="3"/>
       <c r="XFC2" s="3"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>306</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>307</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>308</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>309</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>310</v>
-      </c>
-      <c r="G3" s="22" t="b">
+      <c r="A3" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="G3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="I3" s="22" t="n">
+      <c r="H3" s="21" t="s">
+        <v>318</v>
+      </c>
+      <c r="I3" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J3" s="22" t="n">
+      <c r="J3" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K3" s="22" t="n">
+      <c r="K3" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>312</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>307</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>309</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>310</v>
-      </c>
-      <c r="G4" s="22" t="b">
+      <c r="A4" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="G4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="I4" s="22" t="n">
+      <c r="H4" s="21" t="s">
+        <v>318</v>
+      </c>
+      <c r="I4" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" s="22" t="n">
+      <c r="J4" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K4" s="22" t="n">
+      <c r="K4" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="C5" s="21" t="s">
         <v>314</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="D5" s="21" t="s">
         <v>315</v>
       </c>
-      <c r="C5" s="22" t="s">
-        <v>307</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>308</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>309</v>
-      </c>
-      <c r="F5" s="22" t="s">
+      <c r="E5" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="G5" s="22" t="b">
+      <c r="F5" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="G5" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H5" s="22" t="s">
-        <v>317</v>
-      </c>
-      <c r="I5" s="22" t="n">
+      <c r="H5" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="I5" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="22" t="n">
+      <c r="J5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="22" t="n">
+      <c r="K5" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
-        <v>318</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>319</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>307</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>309</v>
-      </c>
-      <c r="F6" s="22" t="s">
+      <c r="A6" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="E6" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="G6" s="22" t="b">
+      <c r="F6" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="G6" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="I6" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J6" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="F7" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="I6" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J6" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="22" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>307</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>308</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>309</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>310</v>
-      </c>
-      <c r="G7" s="22" t="b">
+      <c r="G7" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H7" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="I7" s="22" t="n">
+      <c r="H7" s="21" t="s">
+        <v>318</v>
+      </c>
+      <c r="I7" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="J7" s="22" t="n">
+      <c r="J7" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="22" t="n">
+      <c r="K7" s="21" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
-        <v>321</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>322</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>307</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>308</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>309</v>
-      </c>
-      <c r="F8" s="22" t="s">
+      <c r="A8" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="E8" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="G8" s="22" t="b">
+      <c r="F8" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="G8" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H8" s="22" t="s">
-        <v>317</v>
-      </c>
-      <c r="I8" s="22" t="n">
+      <c r="H8" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="I8" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="J8" s="22" t="n">
+      <c r="J8" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="22" t="n">
+      <c r="K8" s="21" t="n">
         <v>6</v>
       </c>
     </row>

--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="370">
   <si>
     <t xml:space="preserve">GENERAL CONFIGURATION</t>
   </si>
@@ -94,55 +94,64 @@
     <t xml:space="preserve">(16:30:00)</t>
   </si>
   <si>
+    <t xml:space="preserve">MISSION01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-Agent Test (Multi-Window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISSION02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-Agent Test (Multi-Hybrid)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISSION03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Agent Test (Multi-Camera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GROUP03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISSION04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Agent Test (Multi-Window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISSION05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Agent Test (Multi-Hybrid)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM05</t>
+  </si>
+  <si>
     <t xml:space="preserve">X</t>
   </si>
   <si>
-    <t xml:space="preserve">MISSION01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single-Agent Test (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISSION02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single-Agent Test (Multi-Hybrid)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISSION03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Agent Test (Multi-Camera)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GROUP03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISSION04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Agent Test (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISSION05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Agent Test (Multi-Hybrid)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM05</t>
+    <t xml:space="preserve">MISSION06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-Agent Hardware (Multi-Window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM06</t>
   </si>
   <si>
     <t xml:space="preserve">Geopoint</t>
@@ -238,33 +247,36 @@
     <t xml:space="preserve">DroneID</t>
   </si>
   <si>
+    <t xml:space="preserve">Position [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orientation [°]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxAltitude [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SafetyRadius [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BatteryCapacity [mAh]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENT00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Camera Agent (Single)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRACKING00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRONE00</t>
+  </si>
+  <si>
     <t xml:space="preserve">(X=10.0, Y=0.0, Z=0.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">Orientation [°]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxAltitude [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SafetyRadius [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BatteryCapacity [mAh]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGENT00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Camera Agent (Single)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRACKING00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRONE00</t>
-  </si>
-  <si>
     <t xml:space="preserve">(Roll=0.0, Pitch=0.0, Yaw=0.0)</t>
   </si>
   <si>
@@ -358,6 +370,18 @@
     <t xml:space="preserve">TRACKING11</t>
   </si>
   <si>
+    <t xml:space="preserve">AGENT12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Window Agent Hardware (Single)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRACKING12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRONE02</t>
+  </si>
+  <si>
     <t xml:space="preserve">ObservationSetID</t>
   </si>
   <si>
@@ -442,6 +466,12 @@
     <t xml:space="preserve">SET11</t>
   </si>
   <si>
+    <t xml:space="preserve">Multi-Window Tracking Hardware (Single)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET12</t>
+  </si>
+  <si>
     <t xml:space="preserve">CameraID</t>
   </si>
   <si>
@@ -451,9 +481,6 @@
     <t xml:space="preserve">Role</t>
   </si>
   <si>
-    <t xml:space="preserve">Position [m]</t>
-  </si>
-  <si>
     <t xml:space="preserve">MinFocal [mm]</t>
   </si>
   <si>
@@ -469,6 +496,9 @@
     <t xml:space="preserve">DstStreamURL</t>
   </si>
   <si>
+    <t xml:space="preserve">Hardware</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA00</t>
   </si>
   <si>
@@ -748,6 +778,18 @@
     <t xml:space="preserve">Tracking Head 2 Multi-Hybrid 3 (Multi)</t>
   </si>
   <si>
+    <t xml:space="preserve">MULTICAMERA30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central Head Multi-Window Hardware (Single)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAM06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIYI A8 Mini</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resolution [pix]</t>
   </si>
   <si>
@@ -871,6 +913,30 @@
     <t xml:space="preserve">Tracking Window 2 Multi-Hybrid 3 (Multi)</t>
   </si>
   <si>
+    <t xml:space="preserve">MULTIWINDOW18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 1 Multi-Window Hardware (Single)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 2 Multi-Window Hardware (Single)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 3 Multi-Window Hardware (Single)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 4 Multi-Window Hardware (Single)</t>
+  </si>
+  <si>
     <t xml:space="preserve">HARDWARE CATALOGS</t>
   </si>
   <si>
@@ -949,6 +1015,12 @@
     <t xml:space="preserve">(WhiteNoiseSigma=0.02, WhiteNoiseBias=0)</t>
   </si>
   <si>
+    <t xml:space="preserve">x500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quadcopter</t>
+  </si>
+  <si>
     <t xml:space="preserve">SensorSize [mm]</t>
   </si>
   <si>
@@ -1024,6 +1096,9 @@
     <t xml:space="preserve">Operational Conditions O2 (ultra-high-resolution camera)</t>
   </si>
   <si>
+    <t xml:space="preserve">(7.6x4.275)</t>
+  </si>
+  <si>
     <t xml:space="preserve">EnableRoll</t>
   </si>
   <si>
@@ -1052,6 +1127,18 @@
   </si>
   <si>
     <t xml:space="preserve">(Min=-320.0, Max=320.0, Speed=270)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIM01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Min=-30.0, Max=30.0, Speed=100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Min=-45.0, Max=90.0, Speed=100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Min=-135.0, Max=135.0, Speed=100)</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1150,7 @@
     <numFmt numFmtId="165" formatCode="h:mm:ss"/>
     <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1131,6 +1218,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1224,7 +1318,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1277,6 +1371,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1299,6 +1397,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1452,7 +1554,7 @@
     <tableColumn id="3" name="AgentTeamID"/>
     <tableColumn id="4" name="TrackingID"/>
     <tableColumn id="5" name="DroneID"/>
-    <tableColumn id="6" name="(X=10.0, Y=0.0, Z=0.0)"/>
+    <tableColumn id="6" name="Position [m]"/>
     <tableColumn id="7" name="Orientation [°]"/>
     <tableColumn id="8" name="MaxAltitude [m]"/>
     <tableColumn id="9" name="SafetyRadius [m]"/>
@@ -1936,14 +2038,12 @@
       <c r="BD3" s="12"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>13</v>
@@ -1952,7 +2052,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>16</v>
@@ -2018,10 +2118,10 @@
     <row r="5" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8"/>
       <c r="B5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>25</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>26</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>13</v>
@@ -2030,7 +2130,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>16</v>
@@ -2096,19 +2196,19 @@
     <row r="6" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8"/>
       <c r="B6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>29</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>31</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>16</v>
@@ -2174,19 +2274,19 @@
     <row r="7" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8"/>
       <c r="B7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>32</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>33</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>16</v>
@@ -2252,19 +2352,19 @@
     <row r="8" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8"/>
       <c r="B8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>35</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>36</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>16</v>
@@ -2327,12 +2427,96 @@
       <c r="BC8" s="12"/>
       <c r="BD8" s="12"/>
     </row>
-    <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="12"/>
+      <c r="V9" s="12"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="12"/>
+      <c r="Y9" s="12"/>
+      <c r="Z9" s="12"/>
+      <c r="AA9" s="12"/>
+      <c r="AB9" s="12"/>
+      <c r="AC9" s="12"/>
+      <c r="AD9" s="12"/>
+      <c r="AE9" s="12"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="XFC9" s="0"/>
+      <c r="XFD9" s="0"/>
+    </row>
+    <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="XFC10" s="0"/>
+      <c r="XFD10" s="0"/>
+    </row>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2340,7 +2524,7 @@
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2360,7 +2544,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:XFD16"/>
+  <dimension ref="A1:XFD17"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="2" width="29.34"/>
@@ -2375,96 +2559,133 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>280</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="A1" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>331</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>333</v>
-      </c>
-      <c r="F2" s="20" t="s">
+      <c r="C2" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>359</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="I2" s="22" t="s">
         <v>334</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="J2" s="22" t="s">
         <v>335</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="K2" s="22" t="s">
         <v>336</v>
       </c>
-      <c r="I2" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>312</v>
-      </c>
       <c r="L2" s="12"/>
-      <c r="XFD2" s="3"/>
+      <c r="XFD2" s="0"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="C3" s="21" t="b">
+      <c r="A3" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="C3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>338</v>
-      </c>
-      <c r="E3" s="21" t="b">
+      <c r="D3" s="23" t="s">
+        <v>363</v>
+      </c>
+      <c r="E3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F3" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="G3" s="21" t="b">
+      <c r="F3" s="23" t="s">
+        <v>364</v>
+      </c>
+      <c r="G3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="21" t="s">
-        <v>340</v>
-      </c>
-      <c r="I3" s="21" t="n">
+      <c r="H3" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="I3" s="23" t="n">
         <v>0.4</v>
       </c>
-      <c r="J3" s="21" t="n">
+      <c r="J3" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="21" t="n">
+      <c r="K3" s="23" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="C4" s="23" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="E4" s="23" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>368</v>
+      </c>
+      <c r="G4" s="23" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>369</v>
+      </c>
+      <c r="I4" s="23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J4" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" s="23" t="n">
+        <v>15</v>
+      </c>
+    </row>
     <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2477,6 +2698,7 @@
     <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
@@ -2513,12 +2735,12 @@
   </cols>
   <sheetData>
     <row r="1" s="7" customFormat="true" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
       <c r="E1" s="12"/>
       <c r="XFB1" s="3"/>
       <c r="XFC1" s="3"/>
@@ -2532,10 +2754,10 @@
         <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2543,27 +2765,27 @@
         <v>13</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>45</v>
+      <c r="D4" s="15" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2602,15 +2824,15 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
@@ -2623,16 +2845,16 @@
         <v>4</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
@@ -2695,25 +2917,25 @@
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="15" t="n">
+        <v>56</v>
+      </c>
+      <c r="E3" s="16" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
@@ -2776,25 +2998,25 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="E4" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>54</v>
-      </c>
       <c r="G4" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
@@ -2857,25 +3079,25 @@
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" s="15" t="n">
+        <v>56</v>
+      </c>
+      <c r="E5" s="16" t="n">
         <v>8</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
@@ -2938,25 +3160,25 @@
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="15" t="n">
+        <v>56</v>
+      </c>
+      <c r="E6" s="16" t="n">
         <v>16</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
@@ -3042,7 +3264,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:XFD20"/>
+  <dimension ref="A1:XFD21"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
@@ -3062,51 +3284,51 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="A1" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
       <c r="XFC1" s="3"/>
       <c r="XFD1" s="3"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>68</v>
+      <c r="D2" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>71</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="I2" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>73</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>76</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="12"/>
@@ -3120,399 +3342,433 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="18" t="s">
+      <c r="A3" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H3" s="18" t="n">
+      <c r="D3" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I3" s="18" t="n">
+      <c r="I3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J3" s="19" t="n">
         <v>12000</v>
       </c>
       <c r="XFC3" s="3"/>
       <c r="XFD3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" s="18" t="s">
+      <c r="A4" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="18" t="s">
+      <c r="F4" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H4" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I4" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="19" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="E4" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="18" t="s">
+      <c r="G5" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="G4" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H4" s="18" t="n">
+      <c r="H5" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="I5" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="18" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H5" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I5" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J5" s="18" t="n">
+      <c r="J5" s="19" t="n">
         <v>12000</v>
       </c>
       <c r="XFC5" s="3"/>
       <c r="XFD5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I6" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="F15" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H6" s="18" t="n">
+      <c r="G15" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I15" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="J15" s="19" t="n">
         <v>12000</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I7" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" s="18" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H8" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I8" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="18" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="XFC15" s="0"/>
+      <c r="XFD15" s="0"/>
+    </row>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
@@ -3535,7 +3791,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:XFD24"/>
+  <dimension ref="A1:XFD25"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
@@ -3552,33 +3808,33 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="A1" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>112</v>
+      <c r="C2" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>120</v>
       </c>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
@@ -3593,22 +3849,22 @@
       <c r="XFD2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" s="18" t="n">
+      <c r="A3" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G3" s="2"/>
@@ -3618,22 +3874,22 @@
       <c r="XEY3" s="3"/>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D4" s="18" t="n">
+      <c r="A4" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G4" s="2"/>
@@ -3643,22 +3899,22 @@
       <c r="XEY4" s="3"/>
     </row>
     <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" s="18" t="n">
+      <c r="A5" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G5" s="2"/>
@@ -3673,22 +3929,22 @@
       <c r="XFD5" s="3"/>
     </row>
     <row r="6" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D6" s="18" t="n">
+      <c r="A6" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G6" s="2"/>
@@ -3698,22 +3954,22 @@
       <c r="XEY6" s="3"/>
     </row>
     <row r="7" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="18" t="n">
+      <c r="A7" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G7" s="2"/>
@@ -3723,22 +3979,22 @@
       <c r="XEY7" s="3"/>
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D8" s="18" t="n">
+      <c r="A8" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G8" s="2"/>
@@ -3748,22 +4004,22 @@
       <c r="XEY8" s="3"/>
     </row>
     <row r="9" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="18" t="n">
+      <c r="A9" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G9" s="2"/>
@@ -3773,22 +4029,22 @@
       <c r="XEY9" s="3"/>
     </row>
     <row r="10" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D10" s="18" t="n">
+      <c r="A10" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G10" s="2"/>
@@ -3798,22 +4054,22 @@
       <c r="XEY10" s="3"/>
     </row>
     <row r="11" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="D11" s="18" t="n">
+      <c r="A11" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G11" s="2"/>
@@ -3823,22 +4079,22 @@
       <c r="XEY11" s="3"/>
     </row>
     <row r="12" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D12" s="18" t="n">
+      <c r="A12" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D12" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G12" s="2"/>
@@ -3848,22 +4104,22 @@
       <c r="XEY12" s="3"/>
     </row>
     <row r="13" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D13" s="18" t="n">
+      <c r="A13" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D13" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G13" s="2"/>
@@ -3873,22 +4129,22 @@
       <c r="XEY13" s="3"/>
     </row>
     <row r="14" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="D14" s="18" t="n">
+      <c r="A14" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G14" s="2"/>
@@ -3897,7 +4153,36 @@
       <c r="XEX14" s="2"/>
       <c r="XEY14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="XEV15" s="2"/>
+      <c r="XEW15" s="2"/>
+      <c r="XEX15" s="2"/>
+      <c r="XEY15" s="3"/>
+      <c r="XEZ15" s="0"/>
+      <c r="XFA15" s="0"/>
+      <c r="XFB15" s="0"/>
+      <c r="XFC15" s="0"/>
+      <c r="XFD15" s="0"/>
+    </row>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3907,6 +4192,7 @@
     <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="24" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
@@ -3929,7 +4215,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
@@ -3937,1304 +4223,1386 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="12" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="36.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="9" style="2" width="27.34"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="14" style="12" width="11"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16" style="2" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="9" style="2" width="27.34"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="17" min="15" style="12" width="11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="18" style="2" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
+      <c r="A1" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="E2" s="17" t="s">
+      <c r="C2" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="M2" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="N2" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+    </row>
+    <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I3" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="N3" s="19"/>
+    </row>
+    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="I4" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K4" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="M4" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="N4" s="19"/>
+    </row>
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I5" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="M5" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="N5" s="19"/>
+    </row>
+    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="I6" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="N6" s="19"/>
+    </row>
+    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="N7" s="19"/>
+    </row>
+    <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="M8" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="N8" s="19"/>
+    </row>
+    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="N9" s="19"/>
+    </row>
+    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="N10" s="19"/>
+    </row>
+    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="N11" s="19"/>
+    </row>
+    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="N12" s="19"/>
+    </row>
+    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="M13" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="N13" s="19"/>
+    </row>
+    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K14" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="N14" s="19"/>
+    </row>
+    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="N15" s="19"/>
+    </row>
+    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K16" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="M16" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="N16" s="19"/>
+    </row>
+    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J17" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K17" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="M17" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="N17" s="19"/>
+    </row>
+    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="N18" s="19"/>
+    </row>
+    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J19" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K19" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="M19" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="N19" s="19"/>
+    </row>
+    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K20" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="M20" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="N20" s="19"/>
+    </row>
+    <row r="21" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I21" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="M21" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="N21" s="19"/>
+    </row>
+    <row r="22" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="M22" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="N22" s="19"/>
+    </row>
+    <row r="23" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C23" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="F2" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="G2" s="17" t="s">
+      <c r="D23" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="M23" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="N23" s="19"/>
+    </row>
+    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="C24" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="H2" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="J2" s="17" t="s">
+      <c r="D24" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="M24" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="N24" s="19"/>
+    </row>
+    <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="I25" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J25" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K25" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L25" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="M25" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="N25" s="19"/>
+    </row>
+    <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J26" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K26" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="M26" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="N26" s="19"/>
+    </row>
+    <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="C27" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="K2" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="L2" s="17" t="s">
+      <c r="D27" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="M27" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="N27" s="19"/>
+    </row>
+    <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="I28" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J28" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K28" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="M28" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="N28" s="19"/>
+    </row>
+    <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K29" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L29" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="M29" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="N29" s="19"/>
+    </row>
+    <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="M2" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-    </row>
-    <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="D30" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I30" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="M30" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="N30" s="19"/>
+    </row>
+    <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J31" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K31" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L31" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="M31" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="N31" s="19"/>
+    </row>
+    <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I32" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J32" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K32" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L32" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="M32" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="N32" s="19"/>
+    </row>
+    <row r="33" s="20" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="C33" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I3" s="18" t="n">
+      <c r="D33" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I33" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J33" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K3" s="18" t="n">
+      <c r="K33" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="L3" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="I4" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J4" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K4" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="M4" s="18" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="L33" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="M33" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I5" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J5" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L5" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="M5" s="18" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="I6" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J6" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K6" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L6" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="M6" s="18" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="I7" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J7" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="M7" s="18" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I8" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="M8" s="18" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="M9" s="18" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L10" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="M10" s="18" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="M11" s="18" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="M12" s="18" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K13" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L13" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="M13" s="18" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L14" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="M14" s="18" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="M15" s="18" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L16" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="M16" s="18" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J17" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K17" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L17" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="M17" s="18" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="M18" s="18" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="I19" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J19" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K19" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L19" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="M19" s="18" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I20" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J20" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K20" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L20" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="M20" s="18" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="21" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="H21" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I21" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L21" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="M21" s="18" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="22" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I22" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="M22" s="18" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="23" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="H23" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I23" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="M23" s="18" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I24" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L24" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="M24" s="18" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G25" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H25" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="I25" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J25" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K25" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L25" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="M25" s="18" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="H26" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I26" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K26" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L26" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="M26" s="18" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>228</v>
-      </c>
-      <c r="C27" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G27" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="H27" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I27" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K27" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="M27" s="18" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="I28" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J28" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K28" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L28" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="M28" s="18" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G29" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="H29" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I29" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J29" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K29" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L29" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="M29" s="18" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G30" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="H30" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I30" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K30" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L30" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="M30" s="18" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="C31" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G31" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H31" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="I31" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J31" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K31" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L31" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="M31" s="18" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="B32" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="C32" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F32" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="H32" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I32" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J32" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K32" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L32" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="M32" s="18" t="s">
-        <v>214</v>
-      </c>
+      <c r="N33" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="O33" s="12"/>
+      <c r="P33" s="12"/>
+      <c r="Q33" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5254,11 +5622,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:XFD32"/>
+  <dimension ref="A1:XFD33"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="45.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="57.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="2" width="27.34"/>
@@ -5269,41 +5637,41 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="A1" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>145</v>
+      <c r="C2" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>154</v>
       </c>
       <c r="XEV2" s="3"/>
       <c r="XEW2" s="3"/>
@@ -5316,484 +5684,612 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E3" s="18" t="n">
+      <c r="A3" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E3" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="18" t="n">
+      <c r="G3" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="H3" s="18" t="s">
-        <v>162</v>
+      <c r="H3" s="19" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E4" s="18" t="n">
+      <c r="A4" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E4" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="G4" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="H4" s="18" t="s">
-        <v>167</v>
+      <c r="H4" s="19" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E5" s="18" t="n">
+      <c r="A5" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E5" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="H5" s="18" t="s">
-        <v>173</v>
+      <c r="H5" s="19" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E6" s="18" t="n">
+      <c r="A6" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E6" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="H6" s="18" t="s">
-        <v>179</v>
+      <c r="H6" s="19" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E7" s="18" t="n">
+      <c r="A7" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E7" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="H7" s="18" t="s">
-        <v>162</v>
+      <c r="H7" s="19" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E8" s="18" t="n">
+      <c r="A8" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E8" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="G8" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="H8" s="18" t="s">
-        <v>167</v>
+      <c r="H8" s="19" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E9" s="18" t="n">
+      <c r="A9" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E9" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="18" t="n">
+      <c r="G9" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="H9" s="18" t="s">
-        <v>162</v>
+      <c r="H9" s="19" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>258</v>
-      </c>
-      <c r="B10" s="18" t="s">
+      <c r="A10" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="18" t="n">
+      <c r="G10" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="H10" s="18" t="s">
-        <v>167</v>
+      <c r="H10" s="19" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>260</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>261</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E11" s="18" t="n">
+      <c r="A11" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E11" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="G11" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="H11" s="18" t="s">
-        <v>173</v>
+      <c r="H11" s="19" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>262</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E12" s="18" t="n">
+      <c r="A12" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E12" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="H12" s="18" t="s">
-        <v>179</v>
+      <c r="H12" s="19" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>265</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E13" s="18" t="n">
+      <c r="A13" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E13" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="H13" s="18" t="s">
-        <v>202</v>
+      <c r="H13" s="19" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>266</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E14" s="18" t="n">
+      <c r="A14" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E14" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="H14" s="18" t="s">
-        <v>206</v>
+      <c r="H14" s="19" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>269</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E15" s="18" t="n">
+      <c r="A15" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E15" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="F15" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="H15" s="18" t="s">
-        <v>162</v>
+      <c r="H15" s="19" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
-        <v>270</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E16" s="18" t="n">
+      <c r="A16" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E16" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="H16" s="18" t="s">
-        <v>167</v>
+      <c r="H16" s="19" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E17" s="18" t="n">
+      <c r="A17" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E17" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F17" s="18" t="n">
+      <c r="F17" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="H17" s="18" t="s">
-        <v>173</v>
+      <c r="H17" s="19" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>275</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E18" s="18" t="n">
+      <c r="A18" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E18" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="18" t="n">
+      <c r="G18" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="H18" s="18" t="s">
-        <v>179</v>
+      <c r="H18" s="19" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E19" s="18" t="n">
+      <c r="A19" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E19" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F19" s="18" t="n">
+      <c r="F19" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="18" t="n">
+      <c r="G19" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="H19" s="18" t="s">
-        <v>202</v>
+      <c r="H19" s="19" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="s">
-        <v>278</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>279</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E20" s="18" t="n">
+      <c r="A20" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E20" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F20" s="18" t="n">
+      <c r="F20" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="18" t="n">
+      <c r="G20" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="H20" s="18" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H21" s="12"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H22" s="12"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H23" s="12"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H24" s="12"/>
+      <c r="H20" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="19" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="XEV21" s="0"/>
+      <c r="XEW21" s="0"/>
+      <c r="XEX21" s="0"/>
+      <c r="XEY21" s="0"/>
+      <c r="XEZ21" s="0"/>
+      <c r="XFA21" s="0"/>
+      <c r="XFB21" s="0"/>
+      <c r="XFC21" s="0"/>
+      <c r="XFD21" s="0"/>
+    </row>
+    <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="XEV22" s="0"/>
+      <c r="XEW22" s="0"/>
+      <c r="XEX22" s="0"/>
+      <c r="XEY22" s="0"/>
+      <c r="XEZ22" s="0"/>
+      <c r="XFA22" s="0"/>
+      <c r="XFB22" s="0"/>
+      <c r="XFC22" s="0"/>
+      <c r="XFD22" s="0"/>
+    </row>
+    <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E23" s="19" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="XEV23" s="0"/>
+      <c r="XEW23" s="0"/>
+      <c r="XEX23" s="0"/>
+      <c r="XEY23" s="0"/>
+      <c r="XEZ23" s="0"/>
+      <c r="XFA23" s="0"/>
+      <c r="XFB23" s="0"/>
+      <c r="XFC23" s="0"/>
+      <c r="XFD23" s="0"/>
+    </row>
+    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="XEV24" s="0"/>
+      <c r="XEW24" s="0"/>
+      <c r="XEX24" s="0"/>
+      <c r="XEY24" s="0"/>
+      <c r="XEZ24" s="0"/>
+      <c r="XFA24" s="0"/>
+      <c r="XFB24" s="0"/>
+      <c r="XFC24" s="0"/>
+      <c r="XFD24" s="0"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H25" s="12"/>
@@ -5819,9 +6315,12 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H32" s="12"/>
     </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H33" s="12"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5841,7 +6340,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:R1048576"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="2" width="26.66"/>
@@ -5860,205 +6359,283 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>280</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
+      <c r="A1" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="L2" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="M2" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="N2" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="O2" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="P2" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q2" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="R2" s="20" t="s">
-        <v>295</v>
+      <c r="C2" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="L2" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="M2" s="22" t="s">
+        <v>312</v>
+      </c>
+      <c r="N2" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="O2" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="P2" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q2" s="22" t="s">
+        <v>316</v>
+      </c>
+      <c r="R2" s="22" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="D3" s="21" t="n">
+      <c r="A3" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="D3" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="21" t="n">
+      <c r="E3" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="21" t="b">
+      <c r="F3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G3" s="21" t="s">
-        <v>297</v>
-      </c>
-      <c r="H3" s="21" t="b">
+      <c r="G3" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="H3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I3" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="J3" s="21" t="b">
+      <c r="I3" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="J3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K3" s="21" t="s">
-        <v>299</v>
-      </c>
-      <c r="L3" s="21" t="b">
+      <c r="K3" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="L3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M3" s="21" t="s">
-        <v>300</v>
-      </c>
-      <c r="N3" s="21" t="n">
+      <c r="M3" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="N3" s="23" t="n">
         <v>6.5</v>
       </c>
-      <c r="O3" s="21" t="n">
+      <c r="O3" s="23" t="n">
         <v>2.5</v>
       </c>
-      <c r="P3" s="21" t="n">
+      <c r="P3" s="23" t="n">
         <v>400</v>
       </c>
-      <c r="Q3" s="21" t="n">
+      <c r="Q3" s="23" t="n">
         <v>350</v>
       </c>
-      <c r="R3" s="21" t="n">
+      <c r="R3" s="23" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="D4" s="21" t="n">
+      <c r="A4" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="D4" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="21" t="n">
+      <c r="E4" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="F4" s="21" t="b">
+      <c r="F4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G4" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="H4" s="21" t="b">
+      <c r="G4" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="H4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I4" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="J4" s="21" t="b">
+      <c r="I4" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="J4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K4" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="L4" s="21" t="b">
+      <c r="K4" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="L4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M4" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="N4" s="21" t="n">
+      <c r="M4" s="23" t="s">
+        <v>327</v>
+      </c>
+      <c r="N4" s="23" t="n">
         <v>6.5</v>
       </c>
-      <c r="O4" s="21" t="n">
+      <c r="O4" s="23" t="n">
         <v>2.5</v>
       </c>
-      <c r="P4" s="21" t="n">
+      <c r="P4" s="23" t="n">
         <v>400</v>
       </c>
-      <c r="Q4" s="21" t="n">
+      <c r="Q4" s="23" t="n">
         <v>350</v>
       </c>
-      <c r="R4" s="21" t="n">
+      <c r="R4" s="23" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="5" s="20" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="D5" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" s="23" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="H5" s="23" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="J5" s="23" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="K5" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="L5" s="23" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="M5" s="23" t="s">
+        <v>327</v>
+      </c>
+      <c r="N5" s="23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O5" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P5" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q5" s="23" t="n">
+        <v>350</v>
+      </c>
+      <c r="R5" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" s="20" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+    </row>
     <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -6072,7 +6649,7 @@
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:R1"/>
@@ -6095,7 +6672,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:XFD21"/>
+  <dimension ref="A1:XFD22"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
@@ -6112,275 +6689,313 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>280</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="A1" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>307</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>312</v>
+      <c r="C2" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>330</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>331</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>333</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>336</v>
       </c>
       <c r="XFB2" s="3"/>
       <c r="XFC2" s="3"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>313</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>314</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>315</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>317</v>
-      </c>
-      <c r="G3" s="21" t="b">
+      <c r="A3" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>341</v>
+      </c>
+      <c r="G3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="21" t="s">
-        <v>318</v>
-      </c>
-      <c r="I3" s="21" t="n">
+      <c r="H3" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="I3" s="23" t="n">
         <v>0.5</v>
       </c>
-      <c r="J3" s="21" t="n">
+      <c r="J3" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="K3" s="21" t="n">
+      <c r="K3" s="23" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>319</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>314</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>320</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>317</v>
-      </c>
-      <c r="G4" s="21" t="b">
+      <c r="A4" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>341</v>
+      </c>
+      <c r="G4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="21" t="s">
-        <v>318</v>
-      </c>
-      <c r="I4" s="21" t="n">
+      <c r="H4" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="I4" s="23" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" s="21" t="n">
+      <c r="J4" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="K4" s="21" t="n">
+      <c r="K4" s="23" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
-        <v>321</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>322</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>314</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>315</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="G5" s="21" t="b">
+      <c r="A5" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="G5" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H5" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="I5" s="21" t="n">
+      <c r="H5" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="I5" s="23" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="21" t="n">
+      <c r="J5" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="21" t="n">
+      <c r="K5" s="23" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>314</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>320</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="G6" s="21" t="b">
+      <c r="A6" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>350</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="G6" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H6" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="I6" s="21" t="n">
+      <c r="H6" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="I6" s="23" t="n">
         <v>0.5</v>
       </c>
-      <c r="J6" s="21" t="n">
+      <c r="J6" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="21" t="n">
+      <c r="K6" s="23" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>314</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>328</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>317</v>
-      </c>
-      <c r="G7" s="21" t="b">
+      <c r="A7" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>352</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>341</v>
+      </c>
+      <c r="G7" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H7" s="21" t="s">
-        <v>318</v>
-      </c>
-      <c r="I7" s="21" t="n">
+      <c r="H7" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="I7" s="23" t="n">
         <v>0.8</v>
       </c>
-      <c r="J7" s="21" t="n">
+      <c r="J7" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="21" t="n">
+      <c r="K7" s="23" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
-        <v>329</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>330</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>314</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>328</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="G8" s="21" t="b">
+      <c r="A8" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>354</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>352</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="G8" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H8" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="I8" s="21" t="n">
+      <c r="H8" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="I8" s="23" t="n">
         <v>0.8</v>
       </c>
-      <c r="J8" s="21" t="n">
+      <c r="J8" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="21" t="n">
+      <c r="K8" s="23" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>355</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>341</v>
+      </c>
+      <c r="G9" s="23" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="I9" s="23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J9" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="XFB9" s="0"/>
+      <c r="XFC9" s="0"/>
+      <c r="XFD9" s="0"/>
+    </row>
     <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -6393,6 +7008,7 @@
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>

--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="373">
   <si>
     <t xml:space="preserve">GENERAL CONFIGURATION</t>
   </si>
@@ -499,6 +499,12 @@
     <t xml:space="preserve">Hardware</t>
   </si>
   <si>
+    <t xml:space="preserve">IP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port</t>
+  </si>
+  <si>
     <t xml:space="preserve">MULTICAMERA00</t>
   </si>
   <si>
@@ -788,6 +794,9 @@
   </si>
   <si>
     <t xml:space="preserve">SIYI A8 Mini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.168.144.25</t>
   </si>
   <si>
     <t xml:space="preserve">Resolution [pix]</t>
@@ -1150,7 +1159,7 @@
     <numFmt numFmtId="165" formatCode="h:mm:ss"/>
     <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1218,13 +1227,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1318,7 +1320,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1371,10 +1373,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1397,10 +1395,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2428,7 +2422,7 @@
       <c r="BD8" s="12"/>
     </row>
     <row r="9" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B9" s="9" t="s">
@@ -2506,13 +2500,8 @@
       <c r="BB9" s="12"/>
       <c r="BC9" s="12"/>
       <c r="BD9" s="12"/>
-      <c r="XFC9" s="0"/>
-      <c r="XFD9" s="0"/>
-    </row>
-    <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="XFC10" s="0"/>
-      <c r="XFD10" s="0"/>
-    </row>
+    </row>
+    <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2559,130 +2548,130 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
+      <c r="A1" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>357</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>358</v>
-      </c>
-      <c r="F2" s="22" t="s">
+      <c r="C2" s="20" t="s">
         <v>359</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="D2" s="20" t="s">
         <v>360</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="E2" s="20" t="s">
         <v>361</v>
       </c>
-      <c r="I2" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="J2" s="22" t="s">
-        <v>335</v>
-      </c>
-      <c r="K2" s="22" t="s">
-        <v>336</v>
+      <c r="F2" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>339</v>
       </c>
       <c r="L2" s="12"/>
-      <c r="XFD2" s="0"/>
+      <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>362</v>
-      </c>
-      <c r="C3" s="23" t="b">
+      <c r="A3" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="C3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D3" s="23" t="s">
-        <v>363</v>
-      </c>
-      <c r="E3" s="23" t="b">
+      <c r="D3" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="E3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F3" s="23" t="s">
-        <v>364</v>
-      </c>
-      <c r="G3" s="23" t="b">
+      <c r="F3" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="G3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="23" t="s">
-        <v>365</v>
-      </c>
-      <c r="I3" s="23" t="n">
+      <c r="H3" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="I3" s="21" t="n">
         <v>0.4</v>
       </c>
-      <c r="J3" s="23" t="n">
+      <c r="J3" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="23" t="n">
+      <c r="K3" s="21" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="s">
-        <v>366</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="C4" s="23" t="b">
+      <c r="A4" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D4" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="E4" s="23" t="b">
+      <c r="D4" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="E4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F4" s="23" t="s">
-        <v>368</v>
-      </c>
-      <c r="G4" s="23" t="b">
+      <c r="F4" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="G4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="23" t="s">
-        <v>369</v>
-      </c>
-      <c r="I4" s="23" t="n">
+      <c r="H4" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="I4" s="21" t="n">
         <v>0.4</v>
       </c>
-      <c r="J4" s="23" t="n">
+      <c r="J4" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="K4" s="23" t="n">
+      <c r="K4" s="21" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2735,12 +2724,12 @@
   </cols>
   <sheetData>
     <row r="1" s="7" customFormat="true" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
       <c r="E1" s="12"/>
       <c r="XFB1" s="3"/>
       <c r="XFC1" s="3"/>
@@ -2770,7 +2759,7 @@
       <c r="C3" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="14" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2784,7 +2773,7 @@
       <c r="C4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="14" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2824,15 +2813,15 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
@@ -2928,7 +2917,7 @@
       <c r="D3" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="15" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="9" t="s">
@@ -3009,7 +2998,7 @@
       <c r="D4" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="15" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="9" t="s">
@@ -3090,7 +3079,7 @@
       <c r="D5" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="15" t="n">
         <v>8</v>
       </c>
       <c r="F5" s="9" t="s">
@@ -3171,7 +3160,7 @@
       <c r="D6" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="15" t="n">
         <v>16</v>
       </c>
       <c r="F6" s="9" t="s">
@@ -3284,50 +3273,50 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
       <c r="XFC1" s="3"/>
       <c r="XFD1" s="3"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>76</v>
       </c>
       <c r="L2" s="12"/>
@@ -3342,426 +3331,426 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="H3" s="19" t="n">
+      <c r="H3" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I3" s="19" t="n">
+      <c r="I3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="J3" s="18" t="n">
         <v>12000</v>
       </c>
       <c r="XFC3" s="3"/>
       <c r="XFD3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="H4" s="19" t="n">
+      <c r="H4" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="I4" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="18" t="n">
         <v>12000</v>
       </c>
       <c r="XFC5" s="3"/>
       <c r="XFD5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="H6" s="19" t="n">
+      <c r="H6" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="I6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J6" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H7" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I7" s="19" t="n">
+      <c r="I7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J7" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="19" t="n">
+      <c r="H8" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I8" s="19" t="n">
+      <c r="I8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J8" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="H12" s="19" t="n">
+      <c r="H12" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I12" s="19" t="n">
+      <c r="I12" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="19" t="n">
+      <c r="J12" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="H13" s="19" t="n">
+      <c r="H13" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I13" s="19" t="n">
+      <c r="I13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="19" t="n">
+      <c r="J13" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="H14" s="19" t="n">
+      <c r="H14" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I14" s="19" t="n">
+      <c r="I14" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J14" s="19" t="n">
+      <c r="J14" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="H15" s="19" t="n">
+      <c r="H15" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I15" s="19" t="n">
+      <c r="I15" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J15" s="19" t="n">
+      <c r="J15" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="XFC15" s="0"/>
-      <c r="XFD15" s="0"/>
+      <c r="XFC15" s="3"/>
+      <c r="XFD15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3808,32 +3797,32 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>120</v>
       </c>
       <c r="H2" s="12"/>
@@ -3849,22 +3838,22 @@
       <c r="XFD2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D3" s="19" t="n">
+      <c r="D3" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="19" t="n">
+      <c r="E3" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G3" s="2"/>
@@ -3874,22 +3863,22 @@
       <c r="XEY3" s="3"/>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D4" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G4" s="2"/>
@@ -3899,22 +3888,22 @@
       <c r="XEY4" s="3"/>
     </row>
     <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G5" s="2"/>
@@ -3929,22 +3918,22 @@
       <c r="XFD5" s="3"/>
     </row>
     <row r="6" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G6" s="2"/>
@@ -3954,22 +3943,22 @@
       <c r="XEY6" s="3"/>
     </row>
     <row r="7" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G7" s="2"/>
@@ -3979,22 +3968,22 @@
       <c r="XEY7" s="3"/>
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G8" s="2"/>
@@ -4004,22 +3993,22 @@
       <c r="XEY8" s="3"/>
     </row>
     <row r="9" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G9" s="2"/>
@@ -4029,22 +4018,22 @@
       <c r="XEY9" s="3"/>
     </row>
     <row r="10" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G10" s="2"/>
@@ -4054,22 +4043,22 @@
       <c r="XEY10" s="3"/>
     </row>
     <row r="11" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G11" s="2"/>
@@ -4079,22 +4068,22 @@
       <c r="XEY11" s="3"/>
     </row>
     <row r="12" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G12" s="2"/>
@@ -4104,22 +4093,22 @@
       <c r="XEY12" s="3"/>
     </row>
     <row r="13" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G13" s="2"/>
@@ -4129,22 +4118,22 @@
       <c r="XEY13" s="3"/>
     </row>
     <row r="14" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G14" s="2"/>
@@ -4154,22 +4143,22 @@
       <c r="XEY14" s="3"/>
     </row>
     <row r="15" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G15" s="2"/>
@@ -4177,11 +4166,11 @@
       <c r="XEW15" s="2"/>
       <c r="XEX15" s="2"/>
       <c r="XEY15" s="3"/>
-      <c r="XEZ15" s="0"/>
-      <c r="XFA15" s="0"/>
-      <c r="XFB15" s="0"/>
-      <c r="XFC15" s="0"/>
-      <c r="XFD15" s="0"/>
+      <c r="XEZ15" s="3"/>
+      <c r="XFA15" s="3"/>
+      <c r="XFB15" s="3"/>
+      <c r="XFC15" s="3"/>
+      <c r="XFD15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4215,7 +4204,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
@@ -4224,1385 +4213,1458 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="12" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="36.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="9" style="2" width="27.34"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="17" min="15" style="12" width="11"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="18" style="2" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="21.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="16.23"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="19" min="17" style="12" width="11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="20" style="2" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="N2" s="18" t="s">
+      <c r="N2" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
+      <c r="O2" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="P2" s="17" t="s">
+        <v>157</v>
+      </c>
       <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="A3" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="I3" s="19" t="n">
+      <c r="G3" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="J3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K3" s="19" t="n">
+      <c r="K3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L3" s="19" t="s">
+      <c r="L3" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+    </row>
+    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K4" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="M4" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+    </row>
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="M5" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="N5" s="18"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="18"/>
+    </row>
+    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="M6" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+    </row>
+    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="M7" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18"/>
+    </row>
+    <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="G8" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="M3" s="19" t="s">
+      <c r="H8" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="N3" s="19"/>
-    </row>
-    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="I8" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="M8" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G4" s="19" t="s">
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="M9" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="E10" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F10" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="G10" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="I10" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K4" s="19" t="n">
+      <c r="K10" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L4" s="19" t="s">
+      <c r="L10" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="M10" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
+    </row>
+    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="M11" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+    </row>
+    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="M12" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="18"/>
+    </row>
+    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G13" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="M4" s="19" t="s">
+      <c r="H13" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="N4" s="19"/>
-    </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="I13" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="M13" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="H5" s="19" t="s">
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="18"/>
+    </row>
+    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="M14" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="18"/>
+    </row>
+    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F15" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="G15" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="M15" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="18"/>
+    </row>
+    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="I16" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J16" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K5" s="19" t="n">
+      <c r="K16" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L5" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="M5" s="19" t="s">
+      <c r="L16" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="M16" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="18"/>
+    </row>
+    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G17" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="N5" s="19"/>
-    </row>
-    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="H17" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="M17" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="18"/>
+    </row>
+    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="M18" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="18"/>
+    </row>
+    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J19" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K19" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="M19" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
+    </row>
+    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I20" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K20" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="M20" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="N20" s="18"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="18"/>
+    </row>
+    <row r="21" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I21" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="M21" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="18"/>
+    </row>
+    <row r="22" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="M22" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+    </row>
+    <row r="23" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="M23" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="I6" s="19" t="n">
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="H24" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="M24" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="18"/>
+    </row>
+    <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="I25" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J25" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K6" s="19" t="n">
+      <c r="K25" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L6" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="M6" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="N6" s="19"/>
-    </row>
-    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="L25" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="M25" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
+    </row>
+    <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I26" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J26" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K26" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="M26" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="18"/>
+    </row>
+    <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="H27" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I27" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="M27" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="I7" s="19" t="n">
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
+    </row>
+    <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="I28" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J28" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K7" s="19" t="n">
+      <c r="K28" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L7" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="M7" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="N7" s="19"/>
-    </row>
-    <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="L28" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="M28" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="G8" s="19" t="s">
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
+    </row>
+    <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E29" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="F29" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="H29" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I29" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K29" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L29" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="M29" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="18"/>
+    </row>
+    <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F30" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="I8" s="19" t="n">
+      <c r="G30" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="H30" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I30" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J30" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="19" t="n">
+      <c r="K30" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="L30" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="M30" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
+      <c r="P30" s="18"/>
+    </row>
+    <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="H31" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="I31" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J31" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K31" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L31" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="M31" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="18"/>
+    </row>
+    <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="H32" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I32" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J32" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K32" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L32" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="M32" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
+    </row>
+    <row r="33" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="G33" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="M8" s="19" t="s">
+      <c r="H33" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="N8" s="19"/>
-    </row>
-    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="I9" s="19" t="n">
+      <c r="I33" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J33" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="19" t="n">
+      <c r="K33" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L9" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="M9" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="N9" s="19"/>
-    </row>
-    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="I10" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K10" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L10" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="M10" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="N10" s="19"/>
-    </row>
-    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="I11" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J11" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K11" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="M11" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="N11" s="19"/>
-    </row>
-    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="I12" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="M12" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="N12" s="19"/>
-    </row>
-    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G13" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J13" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K13" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L13" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="M13" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="N13" s="19"/>
-    </row>
-    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="I14" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J14" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K14" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L14" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="M14" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="N14" s="19"/>
-    </row>
-    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="H15" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="M15" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="N15" s="19"/>
-    </row>
-    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J16" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K16" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L16" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="M16" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="N16" s="19"/>
-    </row>
-    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="H17" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J17" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K17" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L17" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="M17" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="N17" s="19"/>
-    </row>
-    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="H18" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="I18" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="M18" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="N18" s="19"/>
-    </row>
-    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G19" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H19" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="I19" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J19" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K19" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L19" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="M19" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="N19" s="19"/>
-    </row>
-    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="H20" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="I20" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J20" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K20" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L20" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="M20" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="N20" s="19"/>
-    </row>
-    <row r="21" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="G21" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="I21" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L21" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="M21" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="N21" s="19"/>
-    </row>
-    <row r="22" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="I22" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="M22" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="N22" s="19"/>
-    </row>
-    <row r="23" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="H23" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="I23" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="M23" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="N23" s="19"/>
-    </row>
-    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F24" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="G24" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="H24" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="I24" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L24" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="M24" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="N24" s="19"/>
-    </row>
-    <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F25" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H25" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="I25" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J25" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K25" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L25" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="M25" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="N25" s="19"/>
-    </row>
-    <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="D26" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F26" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G26" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="H26" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="I26" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K26" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L26" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="M26" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="N26" s="19"/>
-    </row>
-    <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="H27" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="I27" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K27" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="M27" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="N27" s="19"/>
-    </row>
-    <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="D28" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H28" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="I28" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J28" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K28" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L28" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="M28" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="N28" s="19"/>
-    </row>
-    <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="H29" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="I29" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J29" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K29" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L29" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="M29" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="N29" s="19"/>
-    </row>
-    <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="H30" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="I30" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K30" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L30" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="M30" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="N30" s="19"/>
-    </row>
-    <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
-        <v>245</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H31" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="I31" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J31" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K31" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L31" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="M31" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="N31" s="19"/>
-    </row>
-    <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="H32" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="I32" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J32" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K32" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L32" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="M32" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="N32" s="19"/>
-    </row>
-    <row r="33" s="20" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="C33" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D33" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="E33" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="H33" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="I33" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J33" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K33" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L33" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="M33" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="N33" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="O33" s="12"/>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="12"/>
+      <c r="L33" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="M33" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="N33" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="O33" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="P33" s="18" t="n">
+        <v>37260</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5637,40 +5699,40 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="G2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="E2" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="H2" s="17" t="s">
         <v>154</v>
       </c>
       <c r="XEV2" s="3"/>
@@ -5684,612 +5746,576 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="A3" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E3" s="19" t="n">
+      <c r="D3" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E3" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="19" t="n">
+      <c r="G3" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H3" s="19" t="s">
-        <v>172</v>
+      <c r="H3" s="18" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="C4" s="19" t="s">
+      <c r="A4" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="C4" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E4" s="19" t="n">
+      <c r="D4" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E4" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="19" t="n">
+      <c r="G4" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H4" s="19" t="s">
-        <v>177</v>
+      <c r="H4" s="18" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>262</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="C5" s="19" t="s">
+      <c r="E5" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="D5" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E5" s="19" t="n">
+      <c r="D6" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E6" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G6" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H5" s="19" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E6" s="19" t="n">
+      <c r="H6" s="18" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E7" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F7" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G7" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H6" s="19" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="C7" s="19" t="s">
+      <c r="H7" s="18" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="C8" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D7" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E7" s="19" t="n">
+      <c r="D8" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E8" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F8" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G8" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H7" s="19" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E8" s="19" t="n">
+      <c r="H8" s="18" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E9" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G9" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H8" s="19" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="C9" s="19" t="s">
+      <c r="H9" s="18" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="C10" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="D9" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E9" s="19" t="n">
+      <c r="D10" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E10" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G10" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H9" s="19" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E10" s="19" t="n">
+      <c r="H10" s="18" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E11" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F11" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G11" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H10" s="19" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>274</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="C11" s="19" t="s">
+      <c r="H11" s="18" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="C12" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E11" s="19" t="n">
+      <c r="D12" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E12" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F12" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G12" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H11" s="19" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E12" s="19" t="n">
+      <c r="H12" s="18" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E13" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F13" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G13" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H12" s="19" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>279</v>
-      </c>
-      <c r="C13" s="19" t="s">
+      <c r="H13" s="18" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="D13" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E13" s="19" t="n">
+      <c r="D14" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E14" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F14" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="19" t="n">
+      <c r="G14" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H13" s="19" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>280</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E14" s="19" t="n">
+      <c r="H14" s="18" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E15" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F15" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G15" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H14" s="19" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="C15" s="19" t="s">
+      <c r="H15" s="18" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="C16" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E15" s="19" t="n">
+      <c r="D16" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E16" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F16" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="19" t="n">
+      <c r="G16" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H15" s="19" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E16" s="19" t="n">
+      <c r="H16" s="18" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E17" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F17" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="19" t="n">
+      <c r="G17" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H16" s="19" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="C17" s="19" t="s">
+      <c r="H17" s="18" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="C18" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="D17" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E17" s="19" t="n">
+      <c r="D18" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E18" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F18" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="19" t="n">
+      <c r="G18" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H17" s="19" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
-        <v>288</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>289</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E18" s="19" t="n">
+      <c r="H18" s="18" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E19" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F19" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="19" t="n">
+      <c r="G19" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H18" s="19" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
-        <v>290</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="C19" s="19" t="s">
+      <c r="H19" s="18" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C20" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="D19" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E19" s="19" t="n">
+      <c r="D20" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E20" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F20" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="19" t="n">
+      <c r="G20" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H19" s="19" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E20" s="19" t="n">
+      <c r="H20" s="18" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E21" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F21" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="19" t="n">
+      <c r="G21" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H20" s="19" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
-        <v>294</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>295</v>
-      </c>
-      <c r="C21" s="19" t="s">
+      <c r="H21" s="18" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="C22" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D21" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E21" s="19" t="n">
+      <c r="D22" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E22" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F21" s="19" t="n">
+      <c r="F22" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="19" t="n">
+      <c r="G22" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H21" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="XEV21" s="0"/>
-      <c r="XEW21" s="0"/>
-      <c r="XEX21" s="0"/>
-      <c r="XEY21" s="0"/>
-      <c r="XEZ21" s="0"/>
-      <c r="XFA21" s="0"/>
-      <c r="XFB21" s="0"/>
-      <c r="XFC21" s="0"/>
-      <c r="XFD21" s="0"/>
-    </row>
-    <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
-        <v>296</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>297</v>
-      </c>
-      <c r="C22" s="19" t="s">
+      <c r="H22" s="18" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="C23" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D22" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E22" s="19" t="n">
+      <c r="D23" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E23" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F23" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="19" t="n">
+      <c r="G23" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H22" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="XEV22" s="0"/>
-      <c r="XEW22" s="0"/>
-      <c r="XEX22" s="0"/>
-      <c r="XEY22" s="0"/>
-      <c r="XEZ22" s="0"/>
-      <c r="XFA22" s="0"/>
-      <c r="XFB22" s="0"/>
-      <c r="XFC22" s="0"/>
-      <c r="XFD22" s="0"/>
-    </row>
-    <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
-        <v>298</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="C23" s="19" t="s">
+      <c r="H23" s="18" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="C24" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D23" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E23" s="19" t="n">
+      <c r="D24" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E24" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F23" s="19" t="n">
+      <c r="F24" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="19" t="n">
+      <c r="G24" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H23" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="XEV23" s="0"/>
-      <c r="XEW23" s="0"/>
-      <c r="XEX23" s="0"/>
-      <c r="XEY23" s="0"/>
-      <c r="XEZ23" s="0"/>
-      <c r="XFA23" s="0"/>
-      <c r="XFB23" s="0"/>
-      <c r="XFC23" s="0"/>
-      <c r="XFD23" s="0"/>
-    </row>
-    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E24" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F24" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="19" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="H24" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="XEV24" s="0"/>
-      <c r="XEW24" s="0"/>
-      <c r="XEX24" s="0"/>
-      <c r="XEY24" s="0"/>
-      <c r="XEZ24" s="0"/>
-      <c r="XFA24" s="0"/>
-      <c r="XFB24" s="0"/>
-      <c r="XFC24" s="0"/>
-      <c r="XFD24" s="0"/>
+      <c r="H24" s="18" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H25" s="12"/>
@@ -6359,264 +6385,264 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
+      <c r="A1" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="22" t="s">
-        <v>303</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>304</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="G2" s="22" t="s">
+      <c r="D2" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="E2" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="F2" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="G2" s="20" t="s">
         <v>309</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="H2" s="20" t="s">
         <v>310</v>
       </c>
-      <c r="L2" s="22" t="s">
+      <c r="I2" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="M2" s="22" t="s">
+      <c r="J2" s="20" t="s">
         <v>312</v>
       </c>
-      <c r="N2" s="22" t="s">
+      <c r="K2" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="L2" s="20" t="s">
         <v>314</v>
       </c>
-      <c r="P2" s="22" t="s">
+      <c r="M2" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="Q2" s="22" t="s">
+      <c r="N2" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="R2" s="22" t="s">
+      <c r="O2" s="20" t="s">
         <v>317</v>
       </c>
+      <c r="P2" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q2" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="R2" s="20" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="23" t="s">
-        <v>318</v>
-      </c>
-      <c r="D3" s="23" t="n">
+      <c r="C3" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="D3" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="23" t="n">
+      <c r="E3" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="23" t="b">
+      <c r="F3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G3" s="23" t="s">
-        <v>319</v>
-      </c>
-      <c r="H3" s="23" t="b">
+      <c r="G3" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="H3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I3" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="J3" s="23" t="b">
+      <c r="I3" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="J3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K3" s="23" t="s">
-        <v>321</v>
-      </c>
-      <c r="L3" s="23" t="b">
+      <c r="K3" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="L3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M3" s="23" t="s">
-        <v>322</v>
-      </c>
-      <c r="N3" s="23" t="n">
+      <c r="M3" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="N3" s="21" t="n">
         <v>6.5</v>
       </c>
-      <c r="O3" s="23" t="n">
+      <c r="O3" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="P3" s="23" t="n">
+      <c r="P3" s="21" t="n">
         <v>400</v>
       </c>
-      <c r="Q3" s="23" t="n">
+      <c r="Q3" s="21" t="n">
         <v>350</v>
       </c>
-      <c r="R3" s="23" t="n">
+      <c r="R3" s="21" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="B4" s="23" t="s">
+      <c r="A4" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="B4" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="23" t="s">
-        <v>318</v>
-      </c>
-      <c r="D4" s="23" t="n">
+      <c r="C4" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="D4" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="23" t="n">
+      <c r="E4" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F4" s="23" t="b">
+      <c r="F4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G4" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="H4" s="23" t="b">
+      <c r="G4" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="H4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I4" s="23" t="s">
-        <v>325</v>
-      </c>
-      <c r="J4" s="23" t="b">
+      <c r="I4" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="J4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K4" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="L4" s="23" t="b">
+      <c r="K4" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="L4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M4" s="23" t="s">
-        <v>327</v>
-      </c>
-      <c r="N4" s="23" t="n">
+      <c r="M4" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="N4" s="21" t="n">
         <v>6.5</v>
       </c>
-      <c r="O4" s="23" t="n">
+      <c r="O4" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="P4" s="23" t="n">
+      <c r="P4" s="21" t="n">
         <v>400</v>
       </c>
-      <c r="Q4" s="23" t="n">
+      <c r="Q4" s="21" t="n">
         <v>350</v>
       </c>
-      <c r="R4" s="23" t="n">
+      <c r="R4" s="21" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="5" s="20" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23" t="s">
+    <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B5" s="23" t="s">
-        <v>328</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>329</v>
-      </c>
-      <c r="D5" s="23" t="n">
+      <c r="B5" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="D5" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E5" s="23" t="n">
+      <c r="E5" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F5" s="23" t="b">
+      <c r="F5" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G5" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="H5" s="23" t="b">
+      <c r="G5" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="H5" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I5" s="23" t="s">
-        <v>325</v>
-      </c>
-      <c r="J5" s="23" t="b">
+      <c r="I5" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="J5" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K5" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="L5" s="23" t="b">
+      <c r="K5" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="L5" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M5" s="23" t="s">
-        <v>327</v>
-      </c>
-      <c r="N5" s="23" t="n">
+      <c r="M5" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="N5" s="21" t="n">
         <v>6.5</v>
       </c>
-      <c r="O5" s="23" t="n">
+      <c r="O5" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="P5" s="23" t="n">
+      <c r="P5" s="21" t="n">
         <v>400</v>
       </c>
-      <c r="Q5" s="23" t="n">
+      <c r="Q5" s="21" t="n">
         <v>350</v>
       </c>
-      <c r="R5" s="23" t="n">
+      <c r="R5" s="21" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="6" s="20" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" s="12" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -6627,11 +6653,8 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
-      <c r="O6" s="12"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
@@ -6689,312 +6712,309 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
+      <c r="A1" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>330</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>331</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="H2" s="22" t="s">
+      <c r="D2" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="E2" s="20" t="s">
         <v>333</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="F2" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="G2" s="20" t="s">
         <v>335</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="H2" s="20" t="s">
         <v>336</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>339</v>
       </c>
       <c r="XFB2" s="3"/>
       <c r="XFC2" s="3"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>337</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>338</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="E3" s="23" t="s">
+      <c r="A3" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" s="21" t="s">
         <v>340</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="C3" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="G3" s="23" t="b">
+      <c r="D3" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="G3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="23" t="s">
-        <v>342</v>
-      </c>
-      <c r="I3" s="23" t="n">
+      <c r="H3" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="I3" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J3" s="23" t="n">
+      <c r="J3" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K3" s="23" t="n">
+      <c r="K3" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="B4" s="23" t="s">
+      <c r="A4" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E4" s="21" t="s">
         <v>343</v>
       </c>
-      <c r="C4" s="23" t="s">
-        <v>338</v>
-      </c>
-      <c r="D4" s="23" t="s">
+      <c r="F4" s="21" t="s">
         <v>344</v>
       </c>
-      <c r="E4" s="23" t="s">
-        <v>340</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>341</v>
-      </c>
-      <c r="G4" s="23" t="b">
+      <c r="G4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="I4" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="D5" s="21" t="s">
         <v>342</v>
       </c>
-      <c r="I4" s="23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J4" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" s="23" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23" t="s">
-        <v>345</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>346</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>338</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>340</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>347</v>
-      </c>
-      <c r="G5" s="23" t="b">
+      <c r="E5" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="G5" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H5" s="23" t="s">
-        <v>348</v>
-      </c>
-      <c r="I5" s="23" t="n">
+      <c r="H5" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="I5" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="23" t="n">
+      <c r="J5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="23" t="n">
+      <c r="K5" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="23" t="s">
-        <v>349</v>
-      </c>
-      <c r="B6" s="23" t="s">
+      <c r="A6" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="F6" s="21" t="s">
         <v>350</v>
       </c>
-      <c r="C6" s="23" t="s">
-        <v>338</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>344</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>340</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>347</v>
-      </c>
-      <c r="G6" s="23" t="b">
+      <c r="G6" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H6" s="23" t="s">
-        <v>348</v>
-      </c>
-      <c r="I6" s="23" t="n">
+      <c r="H6" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="I6" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J6" s="23" t="n">
+      <c r="J6" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="23" t="n">
+      <c r="K6" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>351</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>338</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>352</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>340</v>
-      </c>
-      <c r="F7" s="23" t="s">
+      <c r="A7" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="C7" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="G7" s="23" t="b">
+      <c r="D7" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="G7" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H7" s="23" t="s">
-        <v>342</v>
-      </c>
-      <c r="I7" s="23" t="n">
+      <c r="H7" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="I7" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="J7" s="23" t="n">
+      <c r="J7" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="23" t="n">
+      <c r="K7" s="21" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23" t="s">
-        <v>353</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>354</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>338</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>352</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>340</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>347</v>
-      </c>
-      <c r="G8" s="23" t="b">
+      <c r="A8" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="G8" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H8" s="23" t="s">
-        <v>348</v>
-      </c>
-      <c r="I8" s="23" t="n">
+      <c r="H8" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="I8" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="J8" s="23" t="n">
+      <c r="J8" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="23" t="n">
+      <c r="K8" s="21" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23" t="s">
-        <v>251</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>338</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>355</v>
-      </c>
-      <c r="F9" s="23" t="s">
+      <c r="A9" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="G9" s="23" t="b">
+      <c r="D9" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="G9" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H9" s="23" t="s">
-        <v>342</v>
-      </c>
-      <c r="I9" s="23" t="n">
+      <c r="H9" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="I9" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="J9" s="23" t="n">
+      <c r="J9" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="23" t="n">
+      <c r="K9" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="XFB9" s="0"/>
-      <c r="XFC9" s="0"/>
-      <c r="XFD9" s="0"/>
     </row>
     <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -793,6 +793,9 @@
     <t xml:space="preserve">CAM06</t>
   </si>
   <si>
+    <t xml:space="preserve">GIM01</t>
+  </si>
+  <si>
     <t xml:space="preserve">SIYI A8 Mini</t>
   </si>
   <si>
@@ -1136,9 +1139,6 @@
   </si>
   <si>
     <t xml:space="preserve">(Min=-320.0, Max=320.0, Speed=270)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIM01</t>
   </si>
   <si>
     <t xml:space="preserve">(Min=-30.0, Max=30.0, Speed=100)</t>
@@ -2549,7 +2549,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -2570,31 +2570,31 @@
         <v>2</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
@@ -2604,28 +2604,28 @@
         <v>161</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I3" s="21" t="n">
         <v>0.4</v>
@@ -2639,10 +2639,10 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>369</v>
+        <v>254</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C4" s="21" t="b">
         <f aca="false">TRUE()</f>
@@ -5626,7 +5626,7 @@
         <v>253</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>161</v>
+        <v>254</v>
       </c>
       <c r="F33" s="18" t="s">
         <v>162</v>
@@ -5653,10 +5653,10 @@
         <v>166</v>
       </c>
       <c r="N33" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O33" s="18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P33" s="18" t="n">
         <v>37260</v>
@@ -5721,16 +5721,16 @@
         <v>117</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>154</v>
@@ -5747,16 +5747,16 @@
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C3" s="18" t="s">
         <v>124</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E3" s="18" t="n">
         <v>0.167</v>
@@ -5773,16 +5773,16 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C4" s="18" t="s">
         <v>124</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E4" s="18" t="n">
         <v>0.167</v>
@@ -5799,16 +5799,16 @@
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>124</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>0.167</v>
@@ -5825,16 +5825,16 @@
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>124</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E6" s="18" t="n">
         <v>0.167</v>
@@ -5851,16 +5851,16 @@
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>126</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>0.167</v>
@@ -5877,16 +5877,16 @@
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>126</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E8" s="18" t="n">
         <v>0.167</v>
@@ -5903,16 +5903,16 @@
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>134</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>0.167</v>
@@ -5929,16 +5929,16 @@
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>134</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E10" s="18" t="n">
         <v>0.167</v>
@@ -5955,16 +5955,16 @@
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>136</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E11" s="18" t="n">
         <v>0.167</v>
@@ -5981,16 +5981,16 @@
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>136</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E12" s="18" t="n">
         <v>0.167</v>
@@ -6007,16 +6007,16 @@
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>138</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E13" s="18" t="n">
         <v>0.167</v>
@@ -6033,16 +6033,16 @@
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C14" s="18" t="s">
         <v>138</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E14" s="18" t="n">
         <v>0.167</v>
@@ -6059,16 +6059,16 @@
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C15" s="18" t="s">
         <v>140</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E15" s="18" t="n">
         <v>0.167</v>
@@ -6085,16 +6085,16 @@
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C16" s="18" t="s">
         <v>140</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E16" s="18" t="n">
         <v>0.167</v>
@@ -6111,16 +6111,16 @@
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C17" s="18" t="s">
         <v>142</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E17" s="18" t="n">
         <v>0.167</v>
@@ -6137,16 +6137,16 @@
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C18" s="18" t="s">
         <v>142</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E18" s="18" t="n">
         <v>0.167</v>
@@ -6163,16 +6163,16 @@
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>144</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E19" s="18" t="n">
         <v>0.167</v>
@@ -6189,16 +6189,16 @@
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>144</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>0.167</v>
@@ -6215,16 +6215,16 @@
     </row>
     <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>146</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E21" s="18" t="n">
         <v>0.167</v>
@@ -6241,16 +6241,16 @@
     </row>
     <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C22" s="18" t="s">
         <v>146</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E22" s="18" t="n">
         <v>0.167</v>
@@ -6267,16 +6267,16 @@
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>146</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E23" s="18" t="n">
         <v>0.167</v>
@@ -6293,16 +6293,16 @@
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="18" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>146</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E24" s="18" t="n">
         <v>0.167</v>
@@ -6386,7 +6386,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -6417,49 +6417,49 @@
         <v>49</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L2" s="20" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M2" s="20" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N2" s="20" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O2" s="20" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P2" s="20" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q2" s="20" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="R2" s="20" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6470,7 +6470,7 @@
         <v>43</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D3" s="21" t="n">
         <v>8</v>
@@ -6483,28 +6483,28 @@
         <v>1</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N3" s="21" t="n">
         <v>6.5</v>
@@ -6524,13 +6524,13 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>47</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D4" s="21" t="n">
         <v>8</v>
@@ -6543,28 +6543,28 @@
         <v>1</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K4" s="21" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="M4" s="21" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N4" s="21" t="n">
         <v>6.5</v>
@@ -6587,10 +6587,10 @@
         <v>116</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D5" s="21" t="n">
         <v>8</v>
@@ -6603,28 +6603,28 @@
         <v>1</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H5" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J5" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L5" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="M5" s="21" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N5" s="21" t="n">
         <v>6.5</v>
@@ -6713,7 +6713,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -6737,28 +6737,28 @@
         <v>49</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="XFB2" s="3"/>
       <c r="XFC2" s="3"/>
@@ -6769,26 +6769,26 @@
         <v>160</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I3" s="21" t="n">
         <v>0.5</v>
@@ -6805,26 +6805,26 @@
         <v>169</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I4" s="21" t="n">
         <v>0.5</v>
@@ -6838,29 +6838,29 @@
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G5" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I5" s="21" t="n">
         <v>0.5</v>
@@ -6874,29 +6874,29 @@
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G6" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I6" s="21" t="n">
         <v>0.5</v>
@@ -6913,26 +6913,26 @@
         <v>194</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G7" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I7" s="21" t="n">
         <v>0.8</v>
@@ -6946,29 +6946,29 @@
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>356</v>
       </c>
-      <c r="B8" s="21" t="s">
-        <v>357</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>355</v>
-      </c>
       <c r="E8" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G8" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I8" s="21" t="n">
         <v>0.8</v>
@@ -6985,26 +6985,26 @@
         <v>253</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G9" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I9" s="21" t="n">
         <v>0.8</v>

--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="374">
   <si>
     <t xml:space="preserve">GENERAL CONFIGURATION</t>
   </si>
@@ -794,6 +794,9 @@
   </si>
   <si>
     <t xml:space="preserve">GIM01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(X=0.0, Y=0.0, Z=-0.05)</t>
   </si>
   <si>
     <t xml:space="preserve">SIYI A8 Mini</t>
@@ -2549,7 +2552,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -2570,31 +2573,31 @@
         <v>2</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
@@ -2604,28 +2607,28 @@
         <v>161</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I3" s="21" t="n">
         <v>0.4</v>
@@ -2642,28 +2645,28 @@
         <v>254</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I4" s="21" t="n">
         <v>0.4</v>
@@ -5632,7 +5635,7 @@
         <v>162</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>163</v>
+        <v>255</v>
       </c>
       <c r="H33" s="18" t="s">
         <v>164</v>
@@ -5653,10 +5656,10 @@
         <v>166</v>
       </c>
       <c r="N33" s="18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O33" s="18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P33" s="18" t="n">
         <v>37260</v>
@@ -5721,16 +5724,16 @@
         <v>117</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>154</v>
@@ -5747,16 +5750,16 @@
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C3" s="18" t="s">
         <v>124</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E3" s="18" t="n">
         <v>0.167</v>
@@ -5773,16 +5776,16 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C4" s="18" t="s">
         <v>124</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E4" s="18" t="n">
         <v>0.167</v>
@@ -5799,16 +5802,16 @@
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>124</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>0.167</v>
@@ -5825,16 +5828,16 @@
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>124</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E6" s="18" t="n">
         <v>0.167</v>
@@ -5851,16 +5854,16 @@
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>126</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>0.167</v>
@@ -5877,16 +5880,16 @@
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>126</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E8" s="18" t="n">
         <v>0.167</v>
@@ -5903,16 +5906,16 @@
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>134</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>0.167</v>
@@ -5929,16 +5932,16 @@
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>134</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E10" s="18" t="n">
         <v>0.167</v>
@@ -5955,16 +5958,16 @@
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>136</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E11" s="18" t="n">
         <v>0.167</v>
@@ -5981,16 +5984,16 @@
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>136</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E12" s="18" t="n">
         <v>0.167</v>
@@ -6007,16 +6010,16 @@
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>138</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E13" s="18" t="n">
         <v>0.167</v>
@@ -6033,16 +6036,16 @@
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C14" s="18" t="s">
         <v>138</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E14" s="18" t="n">
         <v>0.167</v>
@@ -6059,16 +6062,16 @@
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C15" s="18" t="s">
         <v>140</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E15" s="18" t="n">
         <v>0.167</v>
@@ -6085,16 +6088,16 @@
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C16" s="18" t="s">
         <v>140</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E16" s="18" t="n">
         <v>0.167</v>
@@ -6111,16 +6114,16 @@
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C17" s="18" t="s">
         <v>142</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E17" s="18" t="n">
         <v>0.167</v>
@@ -6137,16 +6140,16 @@
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C18" s="18" t="s">
         <v>142</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E18" s="18" t="n">
         <v>0.167</v>
@@ -6163,16 +6166,16 @@
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>144</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E19" s="18" t="n">
         <v>0.167</v>
@@ -6189,16 +6192,16 @@
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>144</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>0.167</v>
@@ -6215,16 +6218,16 @@
     </row>
     <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>146</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E21" s="18" t="n">
         <v>0.167</v>
@@ -6241,16 +6244,16 @@
     </row>
     <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C22" s="18" t="s">
         <v>146</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E22" s="18" t="n">
         <v>0.167</v>
@@ -6267,16 +6270,16 @@
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>146</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E23" s="18" t="n">
         <v>0.167</v>
@@ -6293,16 +6296,16 @@
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="18" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>146</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E24" s="18" t="n">
         <v>0.167</v>
@@ -6386,7 +6389,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -6417,49 +6420,49 @@
         <v>49</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L2" s="20" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M2" s="20" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N2" s="20" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O2" s="20" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P2" s="20" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q2" s="20" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R2" s="20" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6470,7 +6473,7 @@
         <v>43</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D3" s="21" t="n">
         <v>8</v>
@@ -6483,28 +6486,28 @@
         <v>1</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N3" s="21" t="n">
         <v>6.5</v>
@@ -6524,13 +6527,13 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>47</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D4" s="21" t="n">
         <v>8</v>
@@ -6543,28 +6546,28 @@
         <v>1</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K4" s="21" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="M4" s="21" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N4" s="21" t="n">
         <v>6.5</v>
@@ -6587,10 +6590,10 @@
         <v>116</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D5" s="21" t="n">
         <v>8</v>
@@ -6603,28 +6606,28 @@
         <v>1</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H5" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J5" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L5" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="M5" s="21" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N5" s="21" t="n">
         <v>6.5</v>
@@ -6713,7 +6716,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -6737,28 +6740,28 @@
         <v>49</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="XFB2" s="3"/>
       <c r="XFC2" s="3"/>
@@ -6769,26 +6772,26 @@
         <v>160</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I3" s="21" t="n">
         <v>0.5</v>
@@ -6805,26 +6808,26 @@
         <v>169</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I4" s="21" t="n">
         <v>0.5</v>
@@ -6838,29 +6841,29 @@
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G5" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I5" s="21" t="n">
         <v>0.5</v>
@@ -6874,29 +6877,29 @@
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G6" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I6" s="21" t="n">
         <v>0.5</v>
@@ -6913,26 +6916,26 @@
         <v>194</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G7" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I7" s="21" t="n">
         <v>0.8</v>
@@ -6946,29 +6949,29 @@
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>357</v>
       </c>
-      <c r="B8" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>356</v>
-      </c>
       <c r="E8" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G8" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I8" s="21" t="n">
         <v>0.8</v>
@@ -6985,26 +6988,26 @@
         <v>253</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G9" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I9" s="21" t="n">
         <v>0.8</v>

--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="375">
   <si>
     <t xml:space="preserve">GENERAL CONFIGURATION</t>
   </si>
@@ -932,6 +932,9 @@
   </si>
   <si>
     <t xml:space="preserve">Tracking Window 1 Multi-Window Hardware (Single)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(240x135)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTIWINDOW19</t>
@@ -1157,10 +1160,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="h:mm:ss"/>
     <numFmt numFmtId="166" formatCode="0"/>
+    <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -1323,7 +1327,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1409,6 +1413,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1892,7 +1900,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="21" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="21" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.44"/>
@@ -2537,7 +2545,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD17"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="2" width="29.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="40.25"/>
@@ -2552,7 +2560,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -2573,31 +2581,31 @@
         <v>2</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
@@ -2607,28 +2615,28 @@
         <v>161</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>367</v>
-      </c>
-      <c r="C3" s="21" t="b">
+        <v>368</v>
+      </c>
+      <c r="C3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="E3" s="21" t="b">
+        <v>369</v>
+      </c>
+      <c r="E3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>369</v>
-      </c>
-      <c r="G3" s="21" t="b">
+        <v>370</v>
+      </c>
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I3" s="21" t="n">
         <v>0.4</v>
@@ -2647,26 +2655,26 @@
       <c r="B4" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="C4" s="21" t="b">
+      <c r="C4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>371</v>
-      </c>
-      <c r="E4" s="21" t="b">
+        <v>372</v>
+      </c>
+      <c r="E4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>372</v>
-      </c>
-      <c r="G4" s="21" t="b">
+        <v>373</v>
+      </c>
+      <c r="G4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I4" s="21" t="n">
         <v>0.4</v>
@@ -2714,7 +2722,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="33.54"/>
@@ -2805,7 +2813,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:BM1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="38.38"/>
@@ -3257,7 +3265,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD21"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="38.28"/>
@@ -3784,7 +3792,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD25"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="38.28"/>
@@ -4208,7 +4216,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:S33"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="45.28"/>
@@ -5641,13 +5649,13 @@
         <v>164</v>
       </c>
       <c r="I33" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J33" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K33" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L33" s="18" t="s">
         <v>165</v>
@@ -5688,7 +5696,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD33"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="57.21"/>
@@ -6227,7 +6235,7 @@
         <v>146</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="E21" s="18" t="n">
         <v>0.167</v>
@@ -6244,16 +6252,16 @@
     </row>
     <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C22" s="18" t="s">
         <v>146</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="E22" s="18" t="n">
         <v>0.167</v>
@@ -6270,16 +6278,16 @@
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>146</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="E23" s="18" t="n">
         <v>0.167</v>
@@ -6296,16 +6304,16 @@
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="18" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>146</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="E24" s="18" t="n">
         <v>0.167</v>
@@ -6370,7 +6378,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:R20"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="34.63"/>
@@ -6389,7 +6397,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -6420,49 +6428,49 @@
         <v>49</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L2" s="20" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M2" s="20" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N2" s="20" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O2" s="20" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P2" s="20" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q2" s="20" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="R2" s="20" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6473,7 +6481,7 @@
         <v>43</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D3" s="21" t="n">
         <v>8</v>
@@ -6481,33 +6489,33 @@
       <c r="E3" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="21" t="b">
+      <c r="F3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="H3" s="21" t="b">
+        <v>325</v>
+      </c>
+      <c r="H3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="J3" s="21" t="b">
+        <v>326</v>
+      </c>
+      <c r="J3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="L3" s="21" t="b">
+        <v>327</v>
+      </c>
+      <c r="L3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N3" s="21" t="n">
         <v>6.5</v>
@@ -6527,13 +6535,13 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>47</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D4" s="21" t="n">
         <v>8</v>
@@ -6541,33 +6549,33 @@
       <c r="E4" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F4" s="21" t="b">
+      <c r="F4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>329</v>
-      </c>
-      <c r="H4" s="21" t="b">
+        <v>330</v>
+      </c>
+      <c r="H4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>330</v>
-      </c>
-      <c r="J4" s="21" t="b">
+        <v>331</v>
+      </c>
+      <c r="J4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K4" s="21" t="s">
-        <v>331</v>
-      </c>
-      <c r="L4" s="21" t="b">
+        <v>332</v>
+      </c>
+      <c r="L4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="M4" s="21" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N4" s="21" t="n">
         <v>6.5</v>
@@ -6590,10 +6598,10 @@
         <v>116</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D5" s="21" t="n">
         <v>8</v>
@@ -6601,33 +6609,33 @@
       <c r="E5" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F5" s="21" t="b">
+      <c r="F5" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>329</v>
-      </c>
-      <c r="H5" s="21" t="b">
+        <v>330</v>
+      </c>
+      <c r="H5" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>330</v>
-      </c>
-      <c r="J5" s="21" t="b">
+        <v>331</v>
+      </c>
+      <c r="J5" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>331</v>
-      </c>
-      <c r="L5" s="21" t="b">
+        <v>332</v>
+      </c>
+      <c r="L5" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="M5" s="21" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N5" s="21" t="n">
         <v>6.5</v>
@@ -6699,7 +6707,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD22"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="63.93"/>
@@ -6716,7 +6724,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -6743,25 +6751,25 @@
         <v>258</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="XFB2" s="3"/>
       <c r="XFC2" s="3"/>
@@ -6772,26 +6780,26 @@
         <v>160</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="G3" s="21" t="b">
+        <v>347</v>
+      </c>
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I3" s="21" t="n">
         <v>0.5</v>
@@ -6808,26 +6816,26 @@
         <v>169</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="G4" s="21" t="b">
+        <v>347</v>
+      </c>
+      <c r="G4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I4" s="21" t="n">
         <v>0.5</v>
@@ -6841,29 +6849,29 @@
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>352</v>
-      </c>
-      <c r="G5" s="21" t="b">
+        <v>353</v>
+      </c>
+      <c r="G5" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I5" s="21" t="n">
         <v>0.5</v>
@@ -6877,29 +6885,29 @@
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>352</v>
-      </c>
-      <c r="G6" s="21" t="b">
+        <v>353</v>
+      </c>
+      <c r="G6" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I6" s="21" t="n">
         <v>0.5</v>
@@ -6916,26 +6924,26 @@
         <v>194</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="G7" s="21" t="b">
+        <v>347</v>
+      </c>
+      <c r="G7" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I7" s="21" t="n">
         <v>0.8</v>
@@ -6949,29 +6957,29 @@
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>358</v>
       </c>
-      <c r="B8" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>343</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>357</v>
-      </c>
       <c r="E8" s="21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>352</v>
-      </c>
-      <c r="G8" s="21" t="b">
+        <v>353</v>
+      </c>
+      <c r="G8" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I8" s="21" t="n">
         <v>0.8</v>
@@ -6991,23 +6999,23 @@
         <v>256</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="G9" s="21" t="b">
+        <v>347</v>
+      </c>
+      <c r="G9" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I9" s="21" t="n">
         <v>0.8</v>

--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -1166,7 +1166,7 @@
     <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1234,6 +1234,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1327,7 +1333,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1401,6 +1407,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2559,130 +2569,130 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>362</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>363</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>364</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>365</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>366</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>367</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="21" t="s">
         <v>340</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="21" t="s">
         <v>342</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>368</v>
       </c>
-      <c r="C3" s="22" t="b">
+      <c r="C3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="22" t="s">
         <v>369</v>
       </c>
-      <c r="E3" s="22" t="b">
+      <c r="E3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="22" t="s">
         <v>370</v>
       </c>
-      <c r="G3" s="22" t="b">
+      <c r="G3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="22" t="s">
         <v>371</v>
       </c>
-      <c r="I3" s="21" t="n">
+      <c r="I3" s="22" t="n">
         <v>0.4</v>
       </c>
-      <c r="J3" s="21" t="n">
+      <c r="J3" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="21" t="n">
+      <c r="K3" s="22" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="22" t="s">
         <v>256</v>
       </c>
-      <c r="C4" s="22" t="b">
+      <c r="C4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="22" t="s">
         <v>372</v>
       </c>
-      <c r="E4" s="22" t="b">
+      <c r="E4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="22" t="s">
         <v>373</v>
       </c>
-      <c r="G4" s="22" t="b">
+      <c r="G4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="22" t="s">
         <v>374</v>
       </c>
-      <c r="I4" s="21" t="n">
+      <c r="I4" s="22" t="n">
         <v>0.4</v>
       </c>
-      <c r="J4" s="21" t="n">
+      <c r="J4" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K4" s="21" t="n">
+      <c r="K4" s="22" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4223,7 +4233,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="12" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="36.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="9" style="2" width="27.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="2" width="27.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="34.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="21.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="16.23"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="19" min="17" style="12" width="11"/>
@@ -4340,7 +4352,7 @@
       <c r="L3" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="M3" s="18" t="s">
+      <c r="M3" s="19" t="s">
         <v>166</v>
       </c>
       <c r="N3" s="18"/>
@@ -4384,7 +4396,7 @@
       <c r="L4" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="M4" s="18" t="s">
+      <c r="M4" s="19" t="s">
         <v>174</v>
       </c>
       <c r="N4" s="18"/>
@@ -4428,7 +4440,7 @@
       <c r="L5" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="M5" s="18" t="s">
+      <c r="M5" s="19" t="s">
         <v>179</v>
       </c>
       <c r="N5" s="18"/>
@@ -4472,7 +4484,7 @@
       <c r="L6" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="M6" s="18" t="s">
+      <c r="M6" s="19" t="s">
         <v>185</v>
       </c>
       <c r="N6" s="18"/>
@@ -4516,7 +4528,7 @@
       <c r="L7" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="M7" s="18" t="s">
+      <c r="M7" s="19" t="s">
         <v>191</v>
       </c>
       <c r="N7" s="18"/>
@@ -4560,7 +4572,7 @@
       <c r="L8" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="M8" s="18" t="s">
+      <c r="M8" s="19" t="s">
         <v>166</v>
       </c>
       <c r="N8" s="18"/>
@@ -4604,7 +4616,7 @@
       <c r="L9" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="M9" s="18" t="s">
+      <c r="M9" s="19" t="s">
         <v>166</v>
       </c>
       <c r="N9" s="18"/>
@@ -4648,7 +4660,7 @@
       <c r="L10" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="M10" s="18" t="s">
+      <c r="M10" s="19" t="s">
         <v>174</v>
       </c>
       <c r="N10" s="18"/>
@@ -4692,7 +4704,7 @@
       <c r="L11" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="M11" s="18" t="s">
+      <c r="M11" s="19" t="s">
         <v>179</v>
       </c>
       <c r="N11" s="18"/>
@@ -4736,7 +4748,7 @@
       <c r="L12" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="M12" s="18" t="s">
+      <c r="M12" s="19" t="s">
         <v>166</v>
       </c>
       <c r="N12" s="18"/>
@@ -4780,7 +4792,7 @@
       <c r="L13" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="M13" s="18" t="s">
+      <c r="M13" s="19" t="s">
         <v>174</v>
       </c>
       <c r="N13" s="18"/>
@@ -4824,7 +4836,7 @@
       <c r="L14" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="M14" s="18" t="s">
+      <c r="M14" s="19" t="s">
         <v>179</v>
       </c>
       <c r="N14" s="18"/>
@@ -4868,7 +4880,7 @@
       <c r="L15" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="M15" s="18" t="s">
+      <c r="M15" s="19" t="s">
         <v>185</v>
       </c>
       <c r="N15" s="18"/>
@@ -4912,7 +4924,7 @@
       <c r="L16" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="M16" s="18" t="s">
+      <c r="M16" s="19" t="s">
         <v>191</v>
       </c>
       <c r="N16" s="18"/>
@@ -4956,7 +4968,7 @@
       <c r="L17" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="M17" s="18" t="s">
+      <c r="M17" s="19" t="s">
         <v>214</v>
       </c>
       <c r="N17" s="18"/>
@@ -5000,7 +5012,7 @@
       <c r="L18" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="M18" s="18" t="s">
+      <c r="M18" s="19" t="s">
         <v>218</v>
       </c>
       <c r="N18" s="18"/>
@@ -5044,7 +5056,7 @@
       <c r="L19" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="M19" s="18" t="s">
+      <c r="M19" s="19" t="s">
         <v>222</v>
       </c>
       <c r="N19" s="18"/>
@@ -5088,7 +5100,7 @@
       <c r="L20" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="M20" s="18" t="s">
+      <c r="M20" s="19" t="s">
         <v>226</v>
       </c>
       <c r="N20" s="18"/>
@@ -5132,7 +5144,7 @@
       <c r="L21" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="M21" s="18" t="s">
+      <c r="M21" s="19" t="s">
         <v>166</v>
       </c>
       <c r="N21" s="18"/>
@@ -5176,7 +5188,7 @@
       <c r="L22" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="M22" s="18" t="s">
+      <c r="M22" s="19" t="s">
         <v>174</v>
       </c>
       <c r="N22" s="18"/>
@@ -5220,7 +5232,7 @@
       <c r="L23" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="M23" s="18" t="s">
+      <c r="M23" s="19" t="s">
         <v>179</v>
       </c>
       <c r="N23" s="18"/>
@@ -5264,7 +5276,7 @@
       <c r="L24" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="M24" s="18" t="s">
+      <c r="M24" s="19" t="s">
         <v>166</v>
       </c>
       <c r="N24" s="18"/>
@@ -5308,7 +5320,7 @@
       <c r="L25" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="M25" s="18" t="s">
+      <c r="M25" s="19" t="s">
         <v>174</v>
       </c>
       <c r="N25" s="18"/>
@@ -5352,7 +5364,7 @@
       <c r="L26" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="M26" s="18" t="s">
+      <c r="M26" s="19" t="s">
         <v>179</v>
       </c>
       <c r="N26" s="18"/>
@@ -5396,7 +5408,7 @@
       <c r="L27" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="M27" s="18" t="s">
+      <c r="M27" s="19" t="s">
         <v>185</v>
       </c>
       <c r="N27" s="18"/>
@@ -5440,7 +5452,7 @@
       <c r="L28" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="M28" s="18" t="s">
+      <c r="M28" s="19" t="s">
         <v>191</v>
       </c>
       <c r="N28" s="18"/>
@@ -5484,7 +5496,7 @@
       <c r="L29" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="M29" s="18" t="s">
+      <c r="M29" s="19" t="s">
         <v>214</v>
       </c>
       <c r="N29" s="18"/>
@@ -5528,7 +5540,7 @@
       <c r="L30" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="M30" s="18" t="s">
+      <c r="M30" s="19" t="s">
         <v>218</v>
       </c>
       <c r="N30" s="18"/>
@@ -5572,7 +5584,7 @@
       <c r="L31" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="M31" s="18" t="s">
+      <c r="M31" s="19" t="s">
         <v>222</v>
       </c>
       <c r="N31" s="18"/>
@@ -5616,7 +5628,7 @@
       <c r="L32" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="M32" s="18" t="s">
+      <c r="M32" s="19" t="s">
         <v>226</v>
       </c>
       <c r="N32" s="18"/>
@@ -5660,7 +5672,7 @@
       <c r="L33" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="M33" s="18" t="s">
+      <c r="M33" s="19" t="s">
         <v>166</v>
       </c>
       <c r="N33" s="18" t="s">
@@ -5704,7 +5716,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="12" width="27.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="27.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="32.56"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16375" min="9" style="2" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16376" style="3" width="10.49"/>
   </cols>
@@ -5778,7 +5790,7 @@
       <c r="G3" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="19" t="s">
         <v>174</v>
       </c>
     </row>
@@ -5804,7 +5816,7 @@
       <c r="G4" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="19" t="s">
         <v>179</v>
       </c>
     </row>
@@ -5830,7 +5842,7 @@
       <c r="G5" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="19" t="s">
         <v>185</v>
       </c>
     </row>
@@ -5856,7 +5868,7 @@
       <c r="G6" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="19" t="s">
         <v>191</v>
       </c>
     </row>
@@ -5882,7 +5894,7 @@
       <c r="G7" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="19" t="s">
         <v>174</v>
       </c>
     </row>
@@ -5908,7 +5920,7 @@
       <c r="G8" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="H8" s="19" t="s">
         <v>179</v>
       </c>
     </row>
@@ -5934,7 +5946,7 @@
       <c r="G9" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="19" t="s">
         <v>174</v>
       </c>
     </row>
@@ -5960,7 +5972,7 @@
       <c r="G10" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="19" t="s">
         <v>179</v>
       </c>
     </row>
@@ -5986,7 +5998,7 @@
       <c r="G11" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="H11" s="19" t="s">
         <v>185</v>
       </c>
     </row>
@@ -6012,7 +6024,7 @@
       <c r="G12" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H12" s="18" t="s">
+      <c r="H12" s="19" t="s">
         <v>191</v>
       </c>
     </row>
@@ -6038,7 +6050,7 @@
       <c r="G13" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H13" s="18" t="s">
+      <c r="H13" s="19" t="s">
         <v>214</v>
       </c>
     </row>
@@ -6064,7 +6076,7 @@
       <c r="G14" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H14" s="18" t="s">
+      <c r="H14" s="19" t="s">
         <v>218</v>
       </c>
     </row>
@@ -6090,7 +6102,7 @@
       <c r="G15" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H15" s="18" t="s">
+      <c r="H15" s="19" t="s">
         <v>174</v>
       </c>
     </row>
@@ -6116,7 +6128,7 @@
       <c r="G16" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H16" s="18" t="s">
+      <c r="H16" s="19" t="s">
         <v>179</v>
       </c>
     </row>
@@ -6142,7 +6154,7 @@
       <c r="G17" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H17" s="18" t="s">
+      <c r="H17" s="19" t="s">
         <v>185</v>
       </c>
     </row>
@@ -6168,7 +6180,7 @@
       <c r="G18" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H18" s="18" t="s">
+      <c r="H18" s="19" t="s">
         <v>191</v>
       </c>
     </row>
@@ -6194,7 +6206,7 @@
       <c r="G19" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H19" s="18" t="s">
+      <c r="H19" s="19" t="s">
         <v>214</v>
       </c>
     </row>
@@ -6220,7 +6232,7 @@
       <c r="G20" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H20" s="18" t="s">
+      <c r="H20" s="19" t="s">
         <v>218</v>
       </c>
     </row>
@@ -6246,7 +6258,7 @@
       <c r="G21" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H21" s="18" t="s">
+      <c r="H21" s="19" t="s">
         <v>174</v>
       </c>
     </row>
@@ -6272,7 +6284,7 @@
       <c r="G22" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H22" s="18" t="s">
+      <c r="H22" s="19" t="s">
         <v>179</v>
       </c>
     </row>
@@ -6298,7 +6310,7 @@
       <c r="G23" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H23" s="18" t="s">
+      <c r="H23" s="19" t="s">
         <v>185</v>
       </c>
     </row>
@@ -6324,7 +6336,7 @@
       <c r="G24" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H24" s="18" t="s">
+      <c r="H24" s="19" t="s">
         <v>191</v>
       </c>
     </row>
@@ -6396,260 +6408,260 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>310</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>311</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>312</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>313</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="21" t="s">
         <v>314</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="21" t="s">
         <v>315</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="L2" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="M2" s="21" t="s">
         <v>318</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="N2" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="O2" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="P2" s="20" t="s">
+      <c r="P2" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="Q2" s="20" t="s">
+      <c r="Q2" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="R2" s="21" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="22" t="s">
         <v>324</v>
       </c>
-      <c r="D3" s="21" t="n">
+      <c r="D3" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="21" t="n">
+      <c r="E3" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="22" t="b">
+      <c r="F3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="22" t="s">
         <v>325</v>
       </c>
-      <c r="H3" s="22" t="b">
+      <c r="H3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="22" t="s">
         <v>326</v>
       </c>
-      <c r="J3" s="22" t="b">
+      <c r="J3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K3" s="21" t="s">
+      <c r="K3" s="22" t="s">
         <v>327</v>
       </c>
-      <c r="L3" s="22" t="b">
+      <c r="L3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M3" s="21" t="s">
+      <c r="M3" s="22" t="s">
         <v>328</v>
       </c>
-      <c r="N3" s="21" t="n">
+      <c r="N3" s="22" t="n">
         <v>6.5</v>
       </c>
-      <c r="O3" s="21" t="n">
+      <c r="O3" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="P3" s="21" t="n">
+      <c r="P3" s="22" t="n">
         <v>400</v>
       </c>
-      <c r="Q3" s="21" t="n">
+      <c r="Q3" s="22" t="n">
         <v>350</v>
       </c>
-      <c r="R3" s="21" t="n">
+      <c r="R3" s="22" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>329</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="22" t="s">
         <v>324</v>
       </c>
-      <c r="D4" s="21" t="n">
+      <c r="D4" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="21" t="n">
+      <c r="E4" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="F4" s="22" t="b">
+      <c r="F4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="22" t="s">
         <v>330</v>
       </c>
-      <c r="H4" s="22" t="b">
+      <c r="H4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="22" t="s">
         <v>331</v>
       </c>
-      <c r="J4" s="22" t="b">
+      <c r="J4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K4" s="21" t="s">
+      <c r="K4" s="22" t="s">
         <v>332</v>
       </c>
-      <c r="L4" s="22" t="b">
+      <c r="L4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M4" s="21" t="s">
+      <c r="M4" s="22" t="s">
         <v>333</v>
       </c>
-      <c r="N4" s="21" t="n">
+      <c r="N4" s="22" t="n">
         <v>6.5</v>
       </c>
-      <c r="O4" s="21" t="n">
+      <c r="O4" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="P4" s="21" t="n">
+      <c r="P4" s="22" t="n">
         <v>400</v>
       </c>
-      <c r="Q4" s="21" t="n">
+      <c r="Q4" s="22" t="n">
         <v>350</v>
       </c>
-      <c r="R4" s="21" t="n">
+      <c r="R4" s="22" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="22" t="s">
         <v>334</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="22" t="s">
         <v>335</v>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D5" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E5" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="F5" s="22" t="b">
+      <c r="F5" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="22" t="s">
         <v>330</v>
       </c>
-      <c r="H5" s="22" t="b">
+      <c r="H5" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="22" t="s">
         <v>331</v>
       </c>
-      <c r="J5" s="22" t="b">
+      <c r="J5" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K5" s="21" t="s">
+      <c r="K5" s="22" t="s">
         <v>332</v>
       </c>
-      <c r="L5" s="22" t="b">
+      <c r="L5" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M5" s="21" t="s">
+      <c r="M5" s="22" t="s">
         <v>333</v>
       </c>
-      <c r="N5" s="21" t="n">
+      <c r="N5" s="22" t="n">
         <v>6.5</v>
       </c>
-      <c r="O5" s="21" t="n">
+      <c r="O5" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="P5" s="21" t="n">
+      <c r="P5" s="22" t="n">
         <v>400</v>
       </c>
-      <c r="Q5" s="21" t="n">
+      <c r="Q5" s="22" t="n">
         <v>350</v>
       </c>
-      <c r="R5" s="21" t="n">
+      <c r="R5" s="22" t="n">
         <v>25</v>
       </c>
     </row>
@@ -6723,52 +6735,52 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>336</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>337</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>338</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>339</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="21" t="s">
         <v>340</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="21" t="s">
         <v>342</v>
       </c>
       <c r="XFB2" s="3"/>
@@ -6776,254 +6788,254 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>343</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="22" t="s">
         <v>345</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="22" t="s">
         <v>346</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="22" t="s">
         <v>347</v>
       </c>
-      <c r="G3" s="22" t="b">
+      <c r="G3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="22" t="s">
         <v>348</v>
       </c>
-      <c r="I3" s="21" t="n">
+      <c r="I3" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J3" s="21" t="n">
+      <c r="J3" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K3" s="21" t="n">
+      <c r="K3" s="22" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="22" t="s">
         <v>349</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="22" t="s">
         <v>350</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="22" t="s">
         <v>346</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="22" t="s">
         <v>347</v>
       </c>
-      <c r="G4" s="22" t="b">
+      <c r="G4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="22" t="s">
         <v>348</v>
       </c>
-      <c r="I4" s="21" t="n">
+      <c r="I4" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" s="21" t="n">
+      <c r="J4" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K4" s="21" t="n">
+      <c r="K4" s="22" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
         <v>351</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="22" t="s">
         <v>352</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="22" t="s">
         <v>345</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="22" t="s">
         <v>346</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="22" t="s">
         <v>353</v>
       </c>
-      <c r="G5" s="22" t="b">
+      <c r="G5" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="22" t="s">
         <v>354</v>
       </c>
-      <c r="I5" s="21" t="n">
+      <c r="I5" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="21" t="n">
+      <c r="J5" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="21" t="n">
+      <c r="K5" s="22" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="22" t="s">
         <v>355</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="22" t="s">
         <v>356</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="22" t="s">
         <v>350</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="22" t="s">
         <v>346</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="22" t="s">
         <v>353</v>
       </c>
-      <c r="G6" s="22" t="b">
+      <c r="G6" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="22" t="s">
         <v>354</v>
       </c>
-      <c r="I6" s="21" t="n">
+      <c r="I6" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J6" s="21" t="n">
+      <c r="J6" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="21" t="n">
+      <c r="K6" s="22" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="22" t="s">
         <v>194</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="22" t="s">
         <v>357</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="22" t="s">
         <v>358</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="22" t="s">
         <v>346</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="22" t="s">
         <v>347</v>
       </c>
-      <c r="G7" s="22" t="b">
+      <c r="G7" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="22" t="s">
         <v>348</v>
       </c>
-      <c r="I7" s="21" t="n">
+      <c r="I7" s="22" t="n">
         <v>0.8</v>
       </c>
-      <c r="J7" s="21" t="n">
+      <c r="J7" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="21" t="n">
+      <c r="K7" s="22" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="22" t="s">
         <v>359</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="22" t="s">
         <v>360</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="22" t="s">
         <v>358</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="22" t="s">
         <v>346</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="22" t="s">
         <v>353</v>
       </c>
-      <c r="G8" s="22" t="b">
+      <c r="G8" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="22" t="s">
         <v>354</v>
       </c>
-      <c r="I8" s="21" t="n">
+      <c r="I8" s="22" t="n">
         <v>0.8</v>
       </c>
-      <c r="J8" s="21" t="n">
+      <c r="J8" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="21" t="n">
+      <c r="K8" s="22" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="22" t="s">
         <v>253</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="22" t="s">
         <v>256</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="22" t="s">
         <v>345</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="22" t="s">
         <v>361</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="22" t="s">
         <v>347</v>
       </c>
-      <c r="G9" s="22" t="b">
+      <c r="G9" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="22" t="s">
         <v>348</v>
       </c>
-      <c r="I9" s="21" t="n">
+      <c r="I9" s="22" t="n">
         <v>0.8</v>
       </c>
-      <c r="J9" s="21" t="n">
+      <c r="J9" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="21" t="n">
+      <c r="K9" s="22" t="n">
         <v>6</v>
       </c>
     </row>

--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="377">
   <si>
     <t xml:space="preserve">GENERAL CONFIGURATION</t>
   </si>
@@ -262,6 +262,9 @@
     <t xml:space="preserve">BatteryCapacity [mAh]</t>
   </si>
   <si>
+    <t xml:space="preserve">InferenceStreamURL</t>
+  </si>
+  <si>
     <t xml:space="preserve">AGENT00</t>
   </si>
   <si>
@@ -280,6 +283,9 @@
     <t xml:space="preserve">(Roll=0.0, Pitch=0.0, Yaw=0.0)</t>
   </si>
   <si>
+    <t xml:space="preserve">tcp://127.0.0.1:5500</t>
+  </si>
+  <si>
     <t xml:space="preserve">AGENT01</t>
   </si>
   <si>
@@ -490,10 +496,10 @@
     <t xml:space="preserve">RefFocal [mm]</t>
   </si>
   <si>
-    <t xml:space="preserve">SrcStreamURL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DstStreamURL</t>
+    <t xml:space="preserve">SourceStreamURL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InterfaceStreamURL</t>
   </si>
   <si>
     <t xml:space="preserve">Hardware</t>
@@ -1236,7 +1242,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1406,11 +1412,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1561,9 +1567,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table2" displayName="Table2" ref="A2:J2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A2:J2"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table2" displayName="Table2" ref="A2:K2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A2:K2"/>
+  <tableColumns count="11">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Name"/>
     <tableColumn id="3" name="AgentTeamID"/>
@@ -1574,6 +1580,7 @@
     <tableColumn id="8" name="MaxAltitude [m]"/>
     <tableColumn id="9" name="SafetyRadius [m]"/>
     <tableColumn id="10" name="BatteryCapacity [mAh]"/>
+    <tableColumn id="11" name="InferenceStreamURL"/>
   </tableColumns>
 </table>
 </file>
@@ -2570,7 +2577,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -2591,62 +2598,62 @@
         <v>2</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="I3" s="22" t="n">
         <v>0.4</v>
@@ -2660,31 +2667,31 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="22" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I4" s="22" t="n">
         <v>0.4</v>
@@ -3285,12 +3292,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="29.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="36.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="2" width="26.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="29.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="26.66"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="12" style="12" width="11"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16379" min="17" style="2" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16382" min="16380" style="3" width="10.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="2" width="10.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="2" width="29.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="26.66"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="17" min="13" style="12" width="11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16380" min="18" style="2" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16381" style="3" width="10.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="10.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3306,8 +3313,7 @@
       <c r="H1" s="16"/>
       <c r="I1" s="16"/>
       <c r="J1" s="16"/>
-      <c r="XFC1" s="3"/>
-      <c r="XFD1" s="3"/>
+      <c r="K1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
@@ -3340,438 +3346,473 @@
       <c r="J2" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="L2" s="12"/>
+      <c r="K2" s="18" t="s">
+        <v>77</v>
+      </c>
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
-      <c r="XEZ2" s="3"/>
+      <c r="Q2" s="12"/>
       <c r="XFA2" s="3"/>
       <c r="XFB2" s="3"/>
       <c r="XFC2" s="3"/>
-      <c r="XFD2" s="3"/>
+      <c r="XFD2" s="0"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="B3" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="E3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="E3" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="F3" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="H3" s="18" t="n">
+      <c r="G3" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I3" s="18" t="n">
+      <c r="I3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J3" s="19" t="n">
         <v>12000</v>
       </c>
-      <c r="XFC3" s="3"/>
-      <c r="XFD3" s="3"/>
+      <c r="K3" s="19" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="H4" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I4" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="19" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K4" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="G4" s="18" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="G5" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="I5" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J5" s="19" t="n">
         <v>12000</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="18" t="s">
+      <c r="K5" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I6" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H5" s="18" t="n">
+      <c r="G15" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I15" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J15" s="19" t="n">
         <v>12000</v>
       </c>
-      <c r="XFC5" s="3"/>
-      <c r="XFD5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H6" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I6" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="18" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I7" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" s="18" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H8" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I8" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="18" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H13" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>12000</v>
-      </c>
-      <c r="XFC15" s="3"/>
-      <c r="XFD15" s="3"/>
+      <c r="K15" s="19" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3781,7 +3822,7 @@
     <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3835,16 +3876,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
@@ -3859,22 +3900,22 @@
       <c r="XFD2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="18" t="n">
+      <c r="A3" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G3" s="2"/>
@@ -3884,22 +3925,22 @@
       <c r="XEY3" s="3"/>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D4" s="18" t="n">
+      <c r="A4" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G4" s="2"/>
@@ -3909,22 +3950,22 @@
       <c r="XEY4" s="3"/>
     </row>
     <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D5" s="18" t="n">
+      <c r="A5" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G5" s="2"/>
@@ -3939,22 +3980,22 @@
       <c r="XFD5" s="3"/>
     </row>
     <row r="6" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D6" s="18" t="n">
+      <c r="A6" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G6" s="2"/>
@@ -3964,22 +4005,22 @@
       <c r="XEY6" s="3"/>
     </row>
     <row r="7" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="D7" s="18" t="n">
+      <c r="A7" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G7" s="2"/>
@@ -3989,22 +4030,22 @@
       <c r="XEY7" s="3"/>
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D8" s="18" t="n">
+      <c r="A8" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G8" s="2"/>
@@ -4014,22 +4055,22 @@
       <c r="XEY8" s="3"/>
     </row>
     <row r="9" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D9" s="18" t="n">
+      <c r="A9" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G9" s="2"/>
@@ -4039,22 +4080,22 @@
       <c r="XEY9" s="3"/>
     </row>
     <row r="10" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="D10" s="18" t="n">
+      <c r="A10" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G10" s="2"/>
@@ -4064,22 +4105,22 @@
       <c r="XEY10" s="3"/>
     </row>
     <row r="11" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="D11" s="18" t="n">
+      <c r="A11" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D11" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G11" s="2"/>
@@ -4089,22 +4130,22 @@
       <c r="XEY11" s="3"/>
     </row>
     <row r="12" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="D12" s="18" t="n">
+      <c r="A12" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D12" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G12" s="2"/>
@@ -4114,22 +4155,22 @@
       <c r="XEY12" s="3"/>
     </row>
     <row r="13" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="D13" s="18" t="n">
+      <c r="A13" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D13" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G13" s="2"/>
@@ -4139,22 +4180,22 @@
       <c r="XEY13" s="3"/>
     </row>
     <row r="14" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="D14" s="18" t="n">
+      <c r="A14" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D14" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G14" s="2"/>
@@ -4164,22 +4205,22 @@
       <c r="XEY14" s="3"/>
     </row>
     <row r="15" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="D15" s="18" t="n">
+      <c r="A15" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="F15" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G15" s="2"/>
@@ -4225,7 +4266,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:T33"/>
   <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
@@ -4234,12 +4275,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="12" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="36.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="2" width="27.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="34.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="30.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="21.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="16.23"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="19" min="17" style="12" width="11"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="20" style="2" width="11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="21" style="2" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4270,16 +4311,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G2" s="17" t="s">
         <v>72</v>
@@ -4288,1402 +4329,1408 @@
         <v>73</v>
       </c>
       <c r="I2" s="17" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L2" s="17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M2" s="17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N2" s="17" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O2" s="17" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P2" s="17" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q2" s="12"/>
       <c r="R2" s="12"/>
       <c r="S2" s="12"/>
+      <c r="T2" s="0"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="C3" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="E3" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="F3" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="I3" s="18" t="n">
+      <c r="G3" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K3" s="18" t="n">
+      <c r="K3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="L3" s="18" t="s">
+      <c r="L3" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+    </row>
+    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="I4" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K4" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="M4" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+    </row>
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I5" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="M5" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+    </row>
+    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="I6" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+    </row>
+    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+    </row>
+    <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="G8" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="M3" s="19" t="s">
+      <c r="H8" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="N3" s="18"/>
-      <c r="O3" s="18"/>
-      <c r="P3" s="18"/>
-    </row>
-    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="I8" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="M8" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G4" s="18" t="s">
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="T8" s="0"/>
+    </row>
+    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+    </row>
+    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="E10" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F10" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="G10" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="I10" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J10" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K4" s="18" t="n">
+      <c r="K10" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="L4" s="18" t="s">
+      <c r="L10" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+    </row>
+    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+    </row>
+    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+    </row>
+    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G13" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="M4" s="19" t="s">
+      <c r="H13" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="18"/>
-    </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="I13" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="M13" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="H5" s="18" t="s">
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+    </row>
+    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K14" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+    </row>
+    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F15" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="G15" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+    </row>
+    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="I16" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J16" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K5" s="18" t="n">
+      <c r="K16" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="L5" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="M5" s="19" t="s">
+      <c r="L16" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="M16" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+    </row>
+    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G17" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-    </row>
-    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="H17" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J17" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K17" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="M17" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+    </row>
+    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+    </row>
+    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J19" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K19" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="M19" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+    </row>
+    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K20" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="M20" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+    </row>
+    <row r="21" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I21" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="M21" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="T21" s="0"/>
+    </row>
+    <row r="22" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="M22" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="19"/>
+      <c r="T22" s="0"/>
+    </row>
+    <row r="23" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="M23" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="I6" s="18" t="n">
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="19"/>
+      <c r="T23" s="0"/>
+    </row>
+    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="M24" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+    </row>
+    <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="I25" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="J25" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K6" s="18" t="n">
+      <c r="K25" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="L6" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="M6" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-    </row>
-    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+      <c r="L25" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="M25" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+    </row>
+    <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J26" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K26" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="M26" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+    </row>
+    <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="M27" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="I7" s="18" t="n">
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+    </row>
+    <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="I28" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J28" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K7" s="18" t="n">
+      <c r="K28" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="L7" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="M7" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="N7" s="18"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="18"/>
-    </row>
-    <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="L28" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="M28" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G8" s="18" t="s">
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+    </row>
+    <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E29" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="F29" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K29" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L29" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="M29" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+    </row>
+    <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F30" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="G30" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I30" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J30" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="18" t="n">
+      <c r="K30" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="L8" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="M8" s="19" t="s">
+      <c r="L30" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="M30" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+    </row>
+    <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J31" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K31" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L31" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="M31" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="N31" s="19"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="19"/>
+    </row>
+    <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="H32" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18"/>
-      <c r="P8" s="18"/>
-    </row>
-    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="H9" s="18" t="s">
+      <c r="I32" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J32" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K32" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L32" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="M32" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+    </row>
+    <row r="33" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="F33" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="I9" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="M9" s="19" t="s">
+      <c r="G33" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="H33" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
-    </row>
-    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L10" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="M10" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
-      <c r="P10" s="18"/>
-    </row>
-    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="M11" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="18"/>
-    </row>
-    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="M12" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="N12" s="18"/>
-      <c r="O12" s="18"/>
-      <c r="P12" s="18"/>
-    </row>
-    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K13" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L13" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="M13" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="18"/>
-    </row>
-    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L14" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="M14" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="18"/>
-    </row>
-    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="M15" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="N15" s="18"/>
-      <c r="O15" s="18"/>
-      <c r="P15" s="18"/>
-    </row>
-    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L16" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="M16" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="N16" s="18"/>
-      <c r="O16" s="18"/>
-      <c r="P16" s="18"/>
-    </row>
-    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J17" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K17" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L17" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="M17" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18"/>
-    </row>
-    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="M18" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
-      <c r="P18" s="18"/>
-    </row>
-    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="I19" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J19" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K19" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L19" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="M19" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18"/>
-      <c r="P19" s="18"/>
-    </row>
-    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="I20" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J20" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K20" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L20" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="M20" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="N20" s="18"/>
-      <c r="O20" s="18"/>
-      <c r="P20" s="18"/>
-    </row>
-    <row r="21" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>228</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="H21" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="I21" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L21" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="M21" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="N21" s="18"/>
-      <c r="O21" s="18"/>
-      <c r="P21" s="18"/>
-    </row>
-    <row r="22" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="I22" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="M22" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="N22" s="18"/>
-      <c r="O22" s="18"/>
-      <c r="P22" s="18"/>
-    </row>
-    <row r="23" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="H23" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="I23" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="M23" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
-      <c r="P23" s="18"/>
-    </row>
-    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="I24" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L24" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="M24" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="N24" s="18"/>
-      <c r="O24" s="18"/>
-      <c r="P24" s="18"/>
-    </row>
-    <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G25" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="H25" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="I25" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J25" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K25" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L25" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="M25" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="N25" s="18"/>
-      <c r="O25" s="18"/>
-      <c r="P25" s="18"/>
-    </row>
-    <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="H26" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="I26" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K26" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L26" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="M26" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="N26" s="18"/>
-      <c r="O26" s="18"/>
-      <c r="P26" s="18"/>
-    </row>
-    <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="C27" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G27" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="H27" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="I27" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K27" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="M27" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="N27" s="18"/>
-      <c r="O27" s="18"/>
-      <c r="P27" s="18"/>
-    </row>
-    <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="I28" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J28" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K28" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L28" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="M28" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="N28" s="18"/>
-      <c r="O28" s="18"/>
-      <c r="P28" s="18"/>
-    </row>
-    <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G29" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="H29" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="I29" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J29" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K29" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L29" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="M29" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="N29" s="18"/>
-      <c r="O29" s="18"/>
-      <c r="P29" s="18"/>
-    </row>
-    <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G30" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="H30" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="I30" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K30" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L30" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="M30" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="N30" s="18"/>
-      <c r="O30" s="18"/>
-      <c r="P30" s="18"/>
-    </row>
-    <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="C31" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G31" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="H31" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="I31" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J31" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K31" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L31" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="M31" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="N31" s="18"/>
-      <c r="O31" s="18"/>
-      <c r="P31" s="18"/>
-    </row>
-    <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="B32" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="C32" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F32" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="H32" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="I32" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J32" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K32" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L32" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="M32" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
-    </row>
-    <row r="33" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="C33" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="D33" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="F33" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="H33" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="I33" s="18" t="n">
+      <c r="I33" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="J33" s="18" t="n">
+      <c r="J33" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="K33" s="18" t="n">
+      <c r="K33" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="L33" s="18" t="s">
-        <v>165</v>
+      <c r="L33" s="19" t="s">
+        <v>167</v>
       </c>
       <c r="M33" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="N33" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="O33" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="P33" s="18" t="n">
+        <v>168</v>
+      </c>
+      <c r="N33" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="O33" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="P33" s="19" t="n">
         <v>37260</v>
       </c>
+      <c r="T33" s="0"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5741,22 +5788,22 @@
         <v>2</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>261</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>154</v>
+        <v>263</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>156</v>
       </c>
       <c r="XEV2" s="3"/>
       <c r="XEW2" s="3"/>
@@ -5769,575 +5816,575 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>262</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="B3" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E3" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="18" t="n">
+      <c r="G3" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>265</v>
-      </c>
-      <c r="B4" s="18" t="s">
+      <c r="A4" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="G4" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="E5" s="18" t="n">
+      <c r="A5" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E5" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>269</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>270</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="E6" s="18" t="n">
+      <c r="A6" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E6" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="E7" s="18" t="n">
+      <c r="A7" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E7" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="E8" s="18" t="n">
+      <c r="A8" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E8" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="G8" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>275</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="E9" s="18" t="n">
+      <c r="A9" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E9" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="18" t="n">
+      <c r="G9" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>278</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="E10" s="18" t="n">
+      <c r="A10" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E10" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="18" t="n">
+      <c r="G10" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>279</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="E11" s="18" t="n">
+      <c r="A11" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E11" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="G11" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>281</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="E12" s="18" t="n">
+      <c r="A12" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E12" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>283</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>284</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="E13" s="18" t="n">
+      <c r="A13" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E13" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>285</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>286</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="E14" s="18" t="n">
+      <c r="A14" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E14" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="E15" s="18" t="n">
+      <c r="A15" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E15" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="F15" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>290</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="E16" s="18" t="n">
+      <c r="A16" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E16" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>292</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="E17" s="18" t="n">
+      <c r="A17" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E17" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F17" s="18" t="n">
+      <c r="F17" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="E18" s="18" t="n">
+      <c r="A18" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E18" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="18" t="n">
+      <c r="G18" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H18" s="19" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="E19" s="18" t="n">
+      <c r="A19" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E19" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F19" s="18" t="n">
+      <c r="F19" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="18" t="n">
+      <c r="G19" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="E20" s="18" t="n">
+      <c r="A20" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E20" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F20" s="18" t="n">
+      <c r="F20" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="18" t="n">
+      <c r="G20" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="D21" s="18" t="s">
+      <c r="A21" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="B21" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="E21" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F21" s="18" t="n">
+      <c r="F21" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="18" t="n">
+      <c r="G21" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="B22" s="18" t="s">
+      <c r="A22" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" s="19" t="s">
         <v>303</v>
       </c>
-      <c r="C22" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="E22" s="18" t="n">
+      <c r="E22" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F22" s="18" t="n">
+      <c r="F22" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="18" t="n">
+      <c r="G22" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18" t="s">
-        <v>304</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="E23" s="18" t="n">
+      <c r="A23" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="E23" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F23" s="18" t="n">
+      <c r="F23" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="18" t="n">
+      <c r="G23" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="E24" s="18" t="n">
+      <c r="A24" s="19" t="s">
+        <v>308</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="E24" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F24" s="18" t="n">
+      <c r="F24" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="18" t="n">
+      <c r="G24" s="19" t="n">
         <v>0.583</v>
       </c>
       <c r="H24" s="19" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6409,7 +6456,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -6440,60 +6487,60 @@
         <v>49</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M2" s="21" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N2" s="21" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O2" s="21" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P2" s="21" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q2" s="21" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="R2" s="21" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>43</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D3" s="22" t="n">
         <v>8</v>
@@ -6506,28 +6553,28 @@
         <v>1</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K3" s="22" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="M3" s="22" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N3" s="22" t="n">
         <v>6.5</v>
@@ -6547,13 +6594,13 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="22" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>47</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D4" s="22" t="n">
         <v>8</v>
@@ -6566,28 +6613,28 @@
         <v>1</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K4" s="22" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="M4" s="22" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N4" s="22" t="n">
         <v>6.5</v>
@@ -6607,13 +6654,13 @@
     </row>
     <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D5" s="22" t="n">
         <v>8</v>
@@ -6626,28 +6673,28 @@
         <v>1</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H5" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J5" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="K5" s="22" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L5" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="M5" s="22" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N5" s="22" t="n">
         <v>6.5</v>
@@ -6736,7 +6783,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -6760,28 +6807,28 @@
         <v>49</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="XFB2" s="3"/>
       <c r="XFC2" s="3"/>
@@ -6789,29 +6836,29 @@
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="I3" s="22" t="n">
         <v>0.5</v>
@@ -6825,29 +6872,29 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="22" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B4" s="22" t="s">
+        <v>351</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="F4" s="22" t="s">
         <v>349</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>344</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>350</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>346</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>347</v>
       </c>
       <c r="G4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="I4" s="22" t="n">
         <v>0.5</v>
@@ -6861,29 +6908,29 @@
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G5" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I5" s="22" t="n">
         <v>0.5</v>
@@ -6897,29 +6944,29 @@
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="F6" s="22" t="s">
         <v>355</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>344</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>350</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>346</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>353</v>
       </c>
       <c r="G6" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I6" s="22" t="n">
         <v>0.5</v>
@@ -6933,29 +6980,29 @@
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G7" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="I7" s="22" t="n">
         <v>0.8</v>
@@ -6969,29 +7016,29 @@
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B8" s="22" t="s">
+        <v>362</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>360</v>
       </c>
-      <c r="C8" s="22" t="s">
-        <v>344</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>358</v>
-      </c>
       <c r="E8" s="22" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G8" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I8" s="22" t="n">
         <v>0.8</v>
@@ -7005,29 +7052,29 @@
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G9" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="I9" s="22" t="n">
         <v>0.8</v>

--- a/config/Configuration-Test.xlsx
+++ b/config/Configuration-Test.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="379">
   <si>
     <t xml:space="preserve">GENERAL CONFIGURATION</t>
   </si>
@@ -803,6 +803,30 @@
   </si>
   <si>
     <t xml:space="preserve">(X=0.0, Y=0.0, Z=-0.05)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">rtsp://</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">192.168.144.25:8554/main.264</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">udp://10.153.82.216:6000</t>
   </si>
   <si>
     <t xml:space="preserve">SIYI A8 Mini</t>
@@ -1242,7 +1266,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1339,7 +1363,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1409,10 +1433,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2576,130 +2596,130 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="A1" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>365</v>
-      </c>
-      <c r="E2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>366</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>368</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>369</v>
       </c>
-      <c r="I2" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="J2" s="21" t="s">
-        <v>343</v>
-      </c>
-      <c r="K2" s="21" t="s">
+      <c r="G2" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="I2" s="20" t="s">
         <v>344</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>346</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>370</v>
-      </c>
-      <c r="C3" s="23" t="b">
+      <c r="B3" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D3" s="22" t="s">
-        <v>371</v>
-      </c>
-      <c r="E3" s="23" t="b">
+      <c r="D3" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="E3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F3" s="22" t="s">
-        <v>372</v>
-      </c>
-      <c r="G3" s="23" t="b">
+      <c r="F3" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="22" t="s">
-        <v>373</v>
-      </c>
-      <c r="I3" s="22" t="n">
+      <c r="H3" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="I3" s="21" t="n">
         <v>0.4</v>
       </c>
-      <c r="J3" s="22" t="n">
+      <c r="J3" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="22" t="n">
+      <c r="K3" s="21" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="B4" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="C4" s="23" t="b">
+      <c r="B4" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="C4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D4" s="22" t="s">
-        <v>374</v>
-      </c>
-      <c r="E4" s="23" t="b">
+      <c r="D4" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="E4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F4" s="22" t="s">
-        <v>375</v>
-      </c>
-      <c r="G4" s="23" t="b">
+      <c r="F4" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="G4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="22" t="s">
-        <v>376</v>
-      </c>
-      <c r="I4" s="22" t="n">
+      <c r="H4" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="I4" s="21" t="n">
         <v>0.4</v>
       </c>
-      <c r="J4" s="22" t="n">
+      <c r="J4" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="K4" s="22" t="n">
+      <c r="K4" s="21" t="n">
         <v>15</v>
       </c>
     </row>
@@ -3296,8 +3316,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="26.66"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="17" min="13" style="12" width="11"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16380" min="18" style="2" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16381" style="3" width="10.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="10.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16381" style="3" width="10.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3346,7 +3365,7 @@
       <c r="J2" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="17" t="s">
         <v>77</v>
       </c>
       <c r="M2" s="12"/>
@@ -3357,460 +3376,460 @@
       <c r="XFA2" s="3"/>
       <c r="XFB2" s="3"/>
       <c r="XFC2" s="3"/>
-      <c r="XFD2" s="0"/>
+      <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H3" s="19" t="n">
+      <c r="H3" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I3" s="19" t="n">
+      <c r="I3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="J3" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H4" s="19" t="n">
+      <c r="H4" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="I4" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H6" s="19" t="n">
+      <c r="H6" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="I6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J6" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="K6" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H7" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I7" s="19" t="n">
+      <c r="I7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J7" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="K7" s="19" t="s">
+      <c r="K7" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H8" s="19" t="n">
+      <c r="H8" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I8" s="19" t="n">
+      <c r="I8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J8" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="K8" s="19" t="s">
+      <c r="K8" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="K9" s="19" t="s">
+      <c r="K9" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="K10" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="K11" s="19" t="s">
+      <c r="K11" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H12" s="19" t="n">
+      <c r="H12" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I12" s="19" t="n">
+      <c r="I12" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="19" t="n">
+      <c r="J12" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="K12" s="19" t="s">
+      <c r="K12" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H13" s="19" t="n">
+      <c r="H13" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I13" s="19" t="n">
+      <c r="I13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="19" t="n">
+      <c r="J13" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="K13" s="19" t="s">
+      <c r="K13" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="19" t="n">
+      <c r="H14" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I14" s="19" t="n">
+      <c r="I14" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J14" s="19" t="n">
+      <c r="J14" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="K14" s="19" t="s">
+      <c r="K14" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H15" s="19" t="n">
+      <c r="H15" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I15" s="19" t="n">
+      <c r="I15" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J15" s="19" t="n">
+      <c r="J15" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="K15" s="19" t="s">
+      <c r="K15" s="18" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3900,22 +3919,22 @@
       <c r="XFD2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="D3" s="19" t="n">
+      <c r="D3" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="19" t="n">
+      <c r="E3" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G3" s="2"/>
@@ -3925,22 +3944,22 @@
       <c r="XEY3" s="3"/>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D4" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G4" s="2"/>
@@ -3950,22 +3969,22 @@
       <c r="XEY4" s="3"/>
     </row>
     <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G5" s="2"/>
@@ -3980,22 +3999,22 @@
       <c r="XFD5" s="3"/>
     </row>
     <row r="6" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G6" s="2"/>
@@ -4005,22 +4024,22 @@
       <c r="XEY6" s="3"/>
     </row>
     <row r="7" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G7" s="2"/>
@@ -4030,22 +4049,22 @@
       <c r="XEY7" s="3"/>
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G8" s="2"/>
@@ -4055,22 +4074,22 @@
       <c r="XEY8" s="3"/>
     </row>
     <row r="9" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G9" s="2"/>
@@ -4080,22 +4099,22 @@
       <c r="XEY9" s="3"/>
     </row>
     <row r="10" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G10" s="2"/>
@@ -4105,22 +4124,22 @@
       <c r="XEY10" s="3"/>
     </row>
     <row r="11" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G11" s="2"/>
@@ -4130,22 +4149,22 @@
       <c r="XEY11" s="3"/>
     </row>
     <row r="12" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G12" s="2"/>
@@ -4155,22 +4174,22 @@
       <c r="XEY12" s="3"/>
     </row>
     <row r="13" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G13" s="2"/>
@@ -4180,22 +4199,22 @@
       <c r="XEY13" s="3"/>
     </row>
     <row r="14" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G14" s="2"/>
@@ -4205,22 +4224,22 @@
       <c r="XEY14" s="3"/>
     </row>
     <row r="15" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G15" s="2"/>
@@ -4274,7 +4293,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="12" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="36.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="2" width="27.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="2" width="27.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="37.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="30.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="21.7"/>
@@ -4355,1382 +4375,1382 @@
       <c r="Q2" s="12"/>
       <c r="R2" s="12"/>
       <c r="S2" s="12"/>
-      <c r="T2" s="0"/>
+      <c r="T2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I3" s="19" t="n">
+      <c r="I3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="J3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K3" s="19" t="n">
+      <c r="K3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L3" s="19" t="s">
+      <c r="L3" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="M3" s="19" t="s">
+      <c r="M3" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
-      <c r="P3" s="19"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="I4" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K4" s="19" t="n">
+      <c r="K4" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L4" s="19" t="s">
+      <c r="L4" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="M4" s="19" t="s">
+      <c r="M4" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K5" s="19" t="n">
+      <c r="K5" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L5" s="19" t="s">
+      <c r="L5" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="M5" s="19" t="s">
+      <c r="M5" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="I6" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J6" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K6" s="19" t="n">
+      <c r="K6" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="L6" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="M6" s="19" t="s">
+      <c r="M6" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="I7" s="19" t="n">
+      <c r="I7" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J7" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K7" s="19" t="n">
+      <c r="K7" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L7" s="19" t="s">
+      <c r="L7" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="M7" s="19" t="s">
+      <c r="M7" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18"/>
     </row>
     <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I8" s="19" t="n">
+      <c r="I8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="19" t="n">
+      <c r="K8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="L8" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="M8" s="19" t="s">
+      <c r="M8" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="T8" s="0"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+      <c r="T8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="19" t="n">
+      <c r="K9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L9" s="19" t="s">
+      <c r="L9" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="M9" s="19" t="s">
+      <c r="M9" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="18"/>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K10" s="19" t="n">
+      <c r="K10" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="M10" s="19" t="s">
+      <c r="M10" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K11" s="19" t="n">
+      <c r="K11" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L11" s="19" t="s">
+      <c r="L11" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="M11" s="19" t="s">
+      <c r="M11" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H12" s="19" t="s">
+      <c r="H12" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I12" s="19" t="n">
+      <c r="I12" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="19" t="n">
+      <c r="J12" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K12" s="19" t="n">
+      <c r="K12" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L12" s="19" t="s">
+      <c r="L12" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="M12" s="19" t="s">
+      <c r="M12" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="18"/>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="H13" s="19" t="s">
+      <c r="H13" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="I13" s="19" t="n">
+      <c r="I13" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J13" s="19" t="n">
+      <c r="J13" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K13" s="19" t="n">
+      <c r="K13" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L13" s="19" t="s">
+      <c r="L13" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="M13" s="19" t="s">
+      <c r="M13" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="18"/>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="H14" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I14" s="19" t="n">
+      <c r="I14" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J14" s="19" t="n">
+      <c r="J14" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K14" s="19" t="n">
+      <c r="K14" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L14" s="19" t="s">
+      <c r="L14" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="18"/>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="H15" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I15" s="19" t="n">
+      <c r="I15" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J15" s="19" t="n">
+      <c r="J15" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K15" s="19" t="n">
+      <c r="K15" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="19" t="s">
+      <c r="L15" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="M15" s="19" t="s">
+      <c r="M15" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="18"/>
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="H16" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="I16" s="19" t="n">
+      <c r="I16" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J16" s="19" t="n">
+      <c r="J16" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K16" s="19" t="n">
+      <c r="K16" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L16" s="19" t="s">
+      <c r="L16" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="M16" s="19" t="s">
+      <c r="M16" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="18"/>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="H17" s="19" t="s">
+      <c r="H17" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I17" s="19" t="n">
+      <c r="I17" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J17" s="19" t="n">
+      <c r="J17" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K17" s="19" t="n">
+      <c r="K17" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L17" s="19" t="s">
+      <c r="L17" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="M17" s="19" t="s">
+      <c r="M17" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="18"/>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H18" s="19" t="s">
+      <c r="H18" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I18" s="19" t="n">
+      <c r="I18" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J18" s="19" t="n">
+      <c r="J18" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K18" s="19" t="n">
+      <c r="K18" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L18" s="19" t="s">
+      <c r="L18" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="M18" s="19" t="s">
+      <c r="M18" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="18"/>
     </row>
     <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="H19" s="19" t="s">
+      <c r="H19" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="I19" s="19" t="n">
+      <c r="I19" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J19" s="19" t="n">
+      <c r="J19" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K19" s="19" t="n">
+      <c r="K19" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L19" s="19" t="s">
+      <c r="L19" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="M19" s="19" t="s">
+      <c r="M19" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="H20" s="19" t="s">
+      <c r="H20" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I20" s="19" t="n">
+      <c r="I20" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J20" s="19" t="n">
+      <c r="J20" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K20" s="19" t="n">
+      <c r="K20" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L20" s="19" t="s">
+      <c r="L20" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="M20" s="19" t="s">
+      <c r="M20" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="18"/>
     </row>
     <row r="21" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F21" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H21" s="19" t="s">
+      <c r="H21" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I21" s="19" t="n">
+      <c r="I21" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="19" t="n">
+      <c r="J21" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K21" s="19" t="n">
+      <c r="K21" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L21" s="19" t="s">
+      <c r="L21" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="M21" s="19" t="s">
+      <c r="M21" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="T21" s="0"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="18"/>
+      <c r="T21" s="3"/>
     </row>
     <row r="22" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F22" s="19" t="s">
+      <c r="F22" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H22" s="19" t="s">
+      <c r="H22" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I22" s="19" t="n">
+      <c r="I22" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J22" s="19" t="n">
+      <c r="J22" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K22" s="19" t="n">
+      <c r="K22" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L22" s="19" t="s">
+      <c r="L22" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="M22" s="19" t="s">
+      <c r="M22" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="T22" s="0"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+      <c r="T22" s="3"/>
     </row>
     <row r="23" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F23" s="19" t="s">
+      <c r="F23" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H23" s="19" t="s">
+      <c r="H23" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I23" s="19" t="n">
+      <c r="I23" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="19" t="n">
+      <c r="J23" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K23" s="19" t="n">
+      <c r="K23" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="M23" s="19" t="s">
+      <c r="M23" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="T23" s="0"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="18"/>
+      <c r="T23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F24" s="19" t="s">
+      <c r="F24" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H24" s="19" t="s">
+      <c r="H24" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I24" s="19" t="n">
+      <c r="I24" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J24" s="19" t="n">
+      <c r="J24" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K24" s="19" t="n">
+      <c r="K24" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L24" s="19" t="s">
+      <c r="L24" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="18"/>
     </row>
     <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="18" t="s">
         <v>237</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F25" s="19" t="s">
+      <c r="F25" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G25" s="19" t="s">
+      <c r="G25" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="H25" s="19" t="s">
+      <c r="H25" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="I25" s="19" t="n">
+      <c r="I25" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="19" t="n">
+      <c r="J25" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K25" s="19" t="n">
+      <c r="K25" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L25" s="19" t="s">
+      <c r="L25" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="M25" s="19" t="s">
+      <c r="M25" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
     </row>
     <row r="26" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F26" s="19" t="s">
+      <c r="F26" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G26" s="19" t="s">
+      <c r="G26" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="H26" s="19" t="s">
+      <c r="H26" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I26" s="19" t="n">
+      <c r="I26" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J26" s="19" t="n">
+      <c r="J26" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K26" s="19" t="n">
+      <c r="K26" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L26" s="19" t="s">
+      <c r="L26" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="M26" s="19" t="s">
+      <c r="M26" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="19"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="18"/>
     </row>
     <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="E27" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F27" s="19" t="s">
+      <c r="F27" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="G27" s="19" t="s">
+      <c r="G27" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H27" s="19" t="s">
+      <c r="H27" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I27" s="19" t="n">
+      <c r="I27" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J27" s="19" t="n">
+      <c r="J27" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K27" s="19" t="n">
+      <c r="K27" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L27" s="19" t="s">
+      <c r="L27" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="M27" s="19" t="s">
+      <c r="M27" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
     </row>
     <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="18" t="s">
         <v>243</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F28" s="19" t="s">
+      <c r="F28" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G28" s="19" t="s">
+      <c r="G28" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="H28" s="19" t="s">
+      <c r="H28" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="I28" s="19" t="n">
+      <c r="I28" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J28" s="19" t="n">
+      <c r="J28" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K28" s="19" t="n">
+      <c r="K28" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="19" t="s">
+      <c r="L28" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="M28" s="19" t="s">
+      <c r="M28" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
     </row>
     <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F29" s="19" t="s">
+      <c r="F29" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G29" s="19" t="s">
+      <c r="G29" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="H29" s="19" t="s">
+      <c r="H29" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I29" s="19" t="n">
+      <c r="I29" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J29" s="19" t="n">
+      <c r="J29" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K29" s="19" t="n">
+      <c r="K29" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L29" s="19" t="s">
+      <c r="L29" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="M29" s="19" t="s">
+      <c r="M29" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
-      <c r="P29" s="19"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="18"/>
     </row>
     <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E30" s="19" t="s">
+      <c r="E30" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F30" s="19" t="s">
+      <c r="F30" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="G30" s="19" t="s">
+      <c r="G30" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H30" s="19" t="s">
+      <c r="H30" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I30" s="19" t="n">
+      <c r="I30" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J30" s="19" t="n">
+      <c r="J30" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K30" s="19" t="n">
+      <c r="K30" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L30" s="19" t="s">
+      <c r="L30" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="M30" s="19" t="s">
+      <c r="M30" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
+      <c r="P30" s="18"/>
     </row>
     <row r="31" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="E31" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F31" s="19" t="s">
+      <c r="F31" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G31" s="19" t="s">
+      <c r="G31" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="H31" s="19" t="s">
+      <c r="H31" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="I31" s="19" t="n">
+      <c r="I31" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J31" s="19" t="n">
+      <c r="J31" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K31" s="19" t="n">
+      <c r="K31" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L31" s="19" t="s">
+      <c r="L31" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="M31" s="19" t="s">
+      <c r="M31" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
-      <c r="P31" s="19"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="18"/>
     </row>
     <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="18" t="s">
         <v>252</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F32" s="19" t="s">
+      <c r="F32" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G32" s="19" t="s">
+      <c r="G32" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="H32" s="19" t="s">
+      <c r="H32" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I32" s="19" t="n">
+      <c r="I32" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J32" s="19" t="n">
+      <c r="J32" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K32" s="19" t="n">
+      <c r="K32" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L32" s="19" t="s">
+      <c r="L32" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="M32" s="19" t="s">
+      <c r="M32" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
     </row>
     <row r="33" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
+      <c r="A33" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="B33" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="18" t="s">
         <v>255</v>
       </c>
-      <c r="E33" s="19" t="s">
+      <c r="E33" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="F33" s="19" t="s">
+      <c r="F33" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="G33" s="19" t="s">
+      <c r="G33" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="H33" s="19" t="s">
+      <c r="H33" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I33" s="19" t="n">
+      <c r="I33" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="J33" s="19" t="n">
+      <c r="J33" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="K33" s="19" t="n">
+      <c r="K33" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="L33" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="M33" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="N33" s="19" t="s">
+      <c r="L33" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="O33" s="19" t="s">
+      <c r="M33" s="18" t="s">
         <v>259</v>
       </c>
-      <c r="P33" s="19" t="n">
+      <c r="N33" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="O33" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="P33" s="18" t="n">
         <v>37260</v>
       </c>
-      <c r="T33" s="0"/>
+      <c r="T33" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5791,18 +5811,18 @@
         <v>119</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>263</v>
-      </c>
-      <c r="H2" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="H2" s="17" t="s">
         <v>156</v>
       </c>
       <c r="XEV2" s="3"/>
@@ -5816,574 +5836,574 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="A3" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E3" s="19" t="n">
+      <c r="D3" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E3" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="19" t="n">
+      <c r="G3" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="18" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="B4" s="19" t="s">
+      <c r="A4" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="E4" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F4" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="C5" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E4" s="19" t="n">
+      <c r="D5" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E5" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F5" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="19" t="n">
+      <c r="G5" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H5" s="18" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H8" s="18" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E5" s="19" t="n">
+    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E9" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G9" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H9" s="18" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H11" s="18" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E6" s="19" t="n">
+    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E12" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F12" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G12" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H12" s="18" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>274</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E7" s="19" t="n">
+    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E13" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F13" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G13" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H13" s="18" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H15" s="18" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E8" s="19" t="n">
+    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E16" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F16" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G16" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H16" s="18" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E9" s="19" t="n">
+    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E17" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F17" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G17" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H17" s="18" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="18" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="18" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="18" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="18" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H21" s="18" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>279</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>280</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E10" s="19" t="n">
+    <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="E22" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F22" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G22" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H22" s="18" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E11" s="19" t="n">
+    <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>309</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="E23" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F23" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G23" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H23" s="18" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E12" s="19" t="n">
+    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>311</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="E24" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F24" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G24" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="H12" s="19" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>288</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>289</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>290</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="H15" s="19" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E16" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F16" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>294</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E17" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F17" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="H17" s="19" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
-        <v>295</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>296</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E18" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F18" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="19" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="H18" s="19" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
-        <v>297</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>298</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E19" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F19" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="19" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="H19" s="19" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E20" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F20" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="19" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="H20" s="19" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>302</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>303</v>
-      </c>
-      <c r="E21" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F21" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="19" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
-        <v>304</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>305</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>303</v>
-      </c>
-      <c r="E22" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F22" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="19" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
-        <v>306</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>307</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>303</v>
-      </c>
-      <c r="E23" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F23" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="19" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="H23" s="19" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>308</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>309</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>303</v>
-      </c>
-      <c r="E24" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F24" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="19" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="H24" s="19" t="s">
+      <c r="H24" s="18" t="s">
         <v>193</v>
       </c>
     </row>
@@ -6455,260 +6475,260 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
+      <c r="A1" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>311</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>312</v>
-      </c>
-      <c r="F2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>314</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>317</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>318</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>320</v>
       </c>
-      <c r="N2" s="21" t="s">
+      <c r="L2" s="20" t="s">
         <v>321</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="M2" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="P2" s="21" t="s">
+      <c r="N2" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="Q2" s="21" t="s">
+      <c r="O2" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="R2" s="21" t="s">
+      <c r="P2" s="20" t="s">
         <v>325</v>
       </c>
+      <c r="Q2" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="R2" s="20" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="22" t="s">
-        <v>326</v>
-      </c>
-      <c r="D3" s="22" t="n">
+      <c r="C3" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="D3" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="22" t="n">
+      <c r="E3" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="23" t="b">
+      <c r="F3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G3" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="H3" s="23" t="b">
+      <c r="G3" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="H3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I3" s="22" t="s">
-        <v>328</v>
-      </c>
-      <c r="J3" s="23" t="b">
+      <c r="I3" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="J3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K3" s="22" t="s">
-        <v>329</v>
-      </c>
-      <c r="L3" s="23" t="b">
+      <c r="K3" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="L3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M3" s="22" t="s">
-        <v>330</v>
-      </c>
-      <c r="N3" s="22" t="n">
+      <c r="M3" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="N3" s="21" t="n">
         <v>6.5</v>
       </c>
-      <c r="O3" s="22" t="n">
+      <c r="O3" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="P3" s="22" t="n">
+      <c r="P3" s="21" t="n">
         <v>400</v>
       </c>
-      <c r="Q3" s="22" t="n">
+      <c r="Q3" s="21" t="n">
         <v>350</v>
       </c>
-      <c r="R3" s="22" t="n">
+      <c r="R3" s="21" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
-        <v>331</v>
-      </c>
-      <c r="B4" s="22" t="s">
+      <c r="A4" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="B4" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="22" t="s">
-        <v>326</v>
-      </c>
-      <c r="D4" s="22" t="n">
+      <c r="C4" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="D4" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="22" t="n">
+      <c r="E4" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F4" s="23" t="b">
+      <c r="F4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G4" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="H4" s="23" t="b">
+      <c r="G4" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="H4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I4" s="22" t="s">
-        <v>333</v>
-      </c>
-      <c r="J4" s="23" t="b">
+      <c r="I4" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="J4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K4" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="L4" s="23" t="b">
+      <c r="K4" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="L4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M4" s="22" t="s">
-        <v>335</v>
-      </c>
-      <c r="N4" s="22" t="n">
+      <c r="M4" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="N4" s="21" t="n">
         <v>6.5</v>
       </c>
-      <c r="O4" s="22" t="n">
+      <c r="O4" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="P4" s="22" t="n">
+      <c r="P4" s="21" t="n">
         <v>400</v>
       </c>
-      <c r="Q4" s="22" t="n">
+      <c r="Q4" s="21" t="n">
         <v>350</v>
       </c>
-      <c r="R4" s="22" t="n">
+      <c r="R4" s="21" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="B5" s="22" t="s">
-        <v>336</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="D5" s="22" t="n">
+      <c r="B5" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="D5" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="E5" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F5" s="23" t="b">
+      <c r="F5" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G5" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="H5" s="23" t="b">
+      <c r="G5" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="H5" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I5" s="22" t="s">
-        <v>333</v>
-      </c>
-      <c r="J5" s="23" t="b">
+      <c r="I5" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="J5" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K5" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="L5" s="23" t="b">
+      <c r="K5" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="L5" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M5" s="22" t="s">
-        <v>335</v>
-      </c>
-      <c r="N5" s="22" t="n">
+      <c r="M5" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="N5" s="21" t="n">
         <v>6.5</v>
       </c>
-      <c r="O5" s="22" t="n">
+      <c r="O5" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="P5" s="22" t="n">
+      <c r="P5" s="21" t="n">
         <v>400</v>
       </c>
-      <c r="Q5" s="22" t="n">
+      <c r="Q5" s="21" t="n">
         <v>350</v>
       </c>
-      <c r="R5" s="22" t="n">
+      <c r="R5" s="21" t="n">
         <v>25</v>
       </c>
     </row>
@@ -6782,307 +6802,307 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="A1" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>260</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>338</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="G2" s="21" t="s">
+      <c r="D2" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="E2" s="20" t="s">
         <v>340</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>342</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>343</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>344</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>346</v>
       </c>
       <c r="XFB2" s="3"/>
       <c r="XFC2" s="3"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>345</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>346</v>
-      </c>
-      <c r="D3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>347</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>348</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>349</v>
       </c>
-      <c r="G3" s="23" t="b">
+      <c r="E3" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="I3" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="E4" s="21" t="s">
         <v>350</v>
       </c>
-      <c r="I3" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J3" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" s="22" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="B4" s="22" t="s">
+      <c r="F4" s="21" t="s">
         <v>351</v>
       </c>
-      <c r="C4" s="22" t="s">
-        <v>346</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>348</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>349</v>
-      </c>
-      <c r="G4" s="23" t="b">
+      <c r="G4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="I4" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>350</v>
       </c>
-      <c r="I4" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J4" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" s="22" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
-        <v>353</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>354</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>346</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>347</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>348</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>355</v>
-      </c>
-      <c r="G5" s="23" t="b">
+      <c r="F5" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="G5" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H5" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="I5" s="22" t="n">
+      <c r="H5" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="I5" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="22" t="n">
+      <c r="J5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="22" t="n">
+      <c r="K5" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="F6" s="21" t="s">
         <v>357</v>
       </c>
-      <c r="B6" s="22" t="s">
-        <v>358</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>346</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>348</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>355</v>
-      </c>
-      <c r="G6" s="23" t="b">
+      <c r="G6" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H6" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="I6" s="22" t="n">
+      <c r="H6" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="I6" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J6" s="22" t="n">
+      <c r="J6" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="22" t="n">
+      <c r="K6" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>359</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>346</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>360</v>
-      </c>
-      <c r="E7" s="22" t="s">
+      <c r="B7" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="C7" s="21" t="s">
         <v>348</v>
       </c>
-      <c r="F7" s="22" t="s">
-        <v>349</v>
-      </c>
-      <c r="G7" s="23" t="b">
+      <c r="D7" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="G7" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="I7" s="21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J7" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="21" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="E8" s="21" t="s">
         <v>350</v>
       </c>
-      <c r="I7" s="22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J7" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" s="22" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
-        <v>361</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>346</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>360</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>348</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>355</v>
-      </c>
-      <c r="G8" s="23" t="b">
+      <c r="F8" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="G8" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H8" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="I8" s="22" t="n">
+      <c r="H8" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="I8" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="J8" s="22" t="n">
+      <c r="J8" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="22" t="n">
+      <c r="K8" s="21" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>346</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>347</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>363</v>
-      </c>
-      <c r="F9" s="22" t="s">
+      <c r="B9" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>349</v>
       </c>
-      <c r="G9" s="23" t="b">
+      <c r="E9" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="G9" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H9" s="22" t="s">
-        <v>350</v>
-      </c>
-      <c r="I9" s="22" t="n">
+      <c r="H9" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="I9" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="J9" s="22" t="n">
+      <c r="J9" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="22" t="n">
+      <c r="K9" s="21" t="n">
         <v>6</v>
       </c>
     </row>
